--- a/dataset/Part 11_2_ Lending and Outstanding Loans.xlsx
+++ b/dataset/Part 11_2_ Lending and Outstanding Loans.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143739F1-800E-4A50-BA0A-4B02B627DBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F77286-B660-4CBC-92CB-241F72567345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="778">
   <si>
     <t>ID</t>
   </si>
@@ -2174,6 +2174,198 @@
   </si>
   <si>
     <t>1 BARSH VITRA</t>
+  </si>
+  <si>
+    <t>3887ae8e-56b6-4062-b360-b1dcd5dc79d6</t>
+  </si>
+  <si>
+    <t>b6f62bd0-72a8-4b89-83e7-c344c26dbc19</t>
+  </si>
+  <si>
+    <t>JAHILE SAKINX</t>
+  </si>
+  <si>
+    <t>193c4bfd-b476-44d0-93c0-b8ca34d8e69e</t>
+  </si>
+  <si>
+    <t>e67ce574-428d-42b6-b54c-09a36cfe7f54</t>
+  </si>
+  <si>
+    <t>BIRAMI JACH KO LAGI XIMEKI LAI</t>
+  </si>
+  <si>
+    <t>cd2c84ce-f139-46c4-b537-88a54c79ebb7</t>
+  </si>
+  <si>
+    <t>BIDESH JANE KO LAGI DEYAKO</t>
+  </si>
+  <si>
+    <t>bc5d3991-b39c-4923-b8c8-928ff6a0a825</t>
+  </si>
+  <si>
+    <t>UDDHOG CHALAUNE</t>
+  </si>
+  <si>
+    <t>3YEARS</t>
+  </si>
+  <si>
+    <t>1b161143-dbb1-4f3b-b07f-05936f5ce755</t>
+  </si>
+  <si>
+    <t>XORA BIDESH  PATHAUNW KO LAGI</t>
+  </si>
+  <si>
+    <t>5a56b014-dc70-4061-b579-f4a5705a2030</t>
+  </si>
+  <si>
+    <t>b5e64397-6e9e-40ae-b8d5-96e9255760c4</t>
+  </si>
+  <si>
+    <t>INTEREST</t>
+  </si>
+  <si>
+    <t>0cd46ce2-b6f1-44ea-8289-926c5a818471</t>
+  </si>
+  <si>
+    <t>CHHIMEKI LAI BIDESH JANA KO LAGI</t>
+  </si>
+  <si>
+    <t>38e316e0-eff7-4fdd-9971-133c46a26264</t>
+  </si>
+  <si>
+    <t>AAMAJU LAI GHAR BANAUDA DIYAKO</t>
+  </si>
+  <si>
+    <t>JAHILE SAKX TAHILE</t>
+  </si>
+  <si>
+    <t>DIDI KO XORA BIDESH PATHAUNA</t>
+  </si>
+  <si>
+    <t>JAHILE HUNX</t>
+  </si>
+  <si>
+    <t>b69e1a3d-6b54-4639-b7ff-0d7b99e297cf</t>
+  </si>
+  <si>
+    <t>a2c587c5-6357-4455-8518-2961125a430b</t>
+  </si>
+  <si>
+    <t>BAINILAI BAHIRA PATHAUNA</t>
+  </si>
+  <si>
+    <t>RIN TIRNA LAI</t>
+  </si>
+  <si>
+    <t>BAIDSHIK ROJGAAR</t>
+  </si>
+  <si>
+    <t>9362ff65-4ee6-4764-9ac4-e5a5fa7b6586</t>
+  </si>
+  <si>
+    <t>f4192c28-aea9-4c73-ba57-45ec56d598f2</t>
+  </si>
+  <si>
+    <t>BAIDESIK YATRA</t>
+  </si>
+  <si>
+    <t>3bd809ac-6aae-442c-9057-e349d18822e4</t>
+  </si>
+  <si>
+    <t>BYAPAR</t>
+  </si>
+  <si>
+    <t>1c4b61da-32e4-4c65-877e-9d4cd943b81f</t>
+  </si>
+  <si>
+    <t>f1b4db85-846c-42d3-b1c7-7bd644e8b4d9</t>
+  </si>
+  <si>
+    <t>BAIDESIK</t>
+  </si>
+  <si>
+    <t>952f0c33-e251-4cef-9557-3867db9ff3e6</t>
+  </si>
+  <si>
+    <t>3aa9d2cc-03ae-4ccc-9ccd-776b35db43a7</t>
+  </si>
+  <si>
+    <t>aa4dc137-e941-4837-ab35-eaf47bdd2a64</t>
+  </si>
+  <si>
+    <t>JAHILE SAKCHHA</t>
+  </si>
+  <si>
+    <t>669f0633-444a-408e-b356-a34e7bdc4aab</t>
+  </si>
+  <si>
+    <t>XEMIKILAI BIRAMI HUDA</t>
+  </si>
+  <si>
+    <t>1 MAHINA BHITRA MA</t>
+  </si>
+  <si>
+    <t>56453207-4d3d-4ebd-923e-df5005f48f32</t>
+  </si>
+  <si>
+    <t>GAU KO VAUJU LAI</t>
+  </si>
+  <si>
+    <t>JAHILE SAKCH</t>
+  </si>
+  <si>
+    <t>279e7337-4bb3-4954-9559-97bd14925fb9</t>
+  </si>
+  <si>
+    <t>MAITI GHAR TIRA</t>
+  </si>
+  <si>
+    <t>XIMIKI LAI BIDESH JAN KO LAGI</t>
+  </si>
+  <si>
+    <t>0d33c29d-c199-4470-b682-1637a95fd13f</t>
+  </si>
+  <si>
+    <t>3 YEAR</t>
+  </si>
+  <si>
+    <t>5ff8e763-c6b4-4f22-a85e-ad5a606ed179</t>
+  </si>
+  <si>
+    <t>GHARAISHI KHARCHA KO LAGI</t>
+  </si>
+  <si>
+    <t>0251dd88-0808-4850-af25-895508d530e9</t>
+  </si>
+  <si>
+    <t>AUSADHI UPCHARKO LAGI</t>
+  </si>
+  <si>
+    <t>6b128734-48e4-4d59-b538-9c76a75585ef</t>
+  </si>
+  <si>
+    <t>7d0e35ea-15d2-4e80-8dd3-27dede3247de</t>
+  </si>
+  <si>
+    <t>BIDESHJANA VANERA</t>
+  </si>
+  <si>
+    <t>c71f4fa4-740b-4d00-ada8-5e5a0a81512e</t>
+  </si>
+  <si>
+    <t>BUSINESS GARNA</t>
+  </si>
+  <si>
+    <t>98afab77-920a-476f-9ab6-cb8bb69dfd94</t>
+  </si>
+  <si>
+    <t>GHAR BANAUNA LAGI</t>
+  </si>
+  <si>
+    <t>278928d7-c501-4bd4-ab21-97071e3b55ac</t>
+  </si>
+  <si>
+    <t>GHARBAARI PRAYOJAN KO LAGI</t>
   </si>
 </sst>
 </file>
@@ -2219,9 +2411,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2526,7 +2720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U243"/>
+  <dimension ref="A1:U292"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -17631,6 +17825,3137 @@
         <v>0</v>
       </c>
     </row>
+    <row r="244" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>11304</v>
+      </c>
+      <c r="B244" t="s">
+        <v>714</v>
+      </c>
+      <c r="C244">
+        <v>3115</v>
+      </c>
+      <c r="D244">
+        <v>31304</v>
+      </c>
+      <c r="E244">
+        <v>4</v>
+      </c>
+      <c r="F244">
+        <v>7</v>
+      </c>
+      <c r="G244" t="s">
+        <v>503</v>
+      </c>
+      <c r="H244" t="s">
+        <v>35</v>
+      </c>
+      <c r="I244">
+        <v>25</v>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244" t="s">
+        <v>479</v>
+      </c>
+      <c r="L244">
+        <v>54754</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244" s="2">
+        <v>66320</v>
+      </c>
+      <c r="O244">
+        <v>4</v>
+      </c>
+      <c r="P244">
+        <v>1000000</v>
+      </c>
+      <c r="Q244">
+        <v>24</v>
+      </c>
+      <c r="R244">
+        <v>120000</v>
+      </c>
+      <c r="S244">
+        <v>2</v>
+      </c>
+      <c r="T244">
+        <v>3</v>
+      </c>
+      <c r="U244">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="245" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>11309</v>
+      </c>
+      <c r="B245" t="s">
+        <v>715</v>
+      </c>
+      <c r="C245">
+        <v>3215</v>
+      </c>
+      <c r="D245">
+        <v>31304</v>
+      </c>
+      <c r="E245">
+        <v>4</v>
+      </c>
+      <c r="F245">
+        <v>9</v>
+      </c>
+      <c r="G245" t="s">
+        <v>503</v>
+      </c>
+      <c r="H245" t="s">
+        <v>35</v>
+      </c>
+      <c r="I245">
+        <v>25</v>
+      </c>
+      <c r="J245">
+        <v>1</v>
+      </c>
+      <c r="K245" t="s">
+        <v>99</v>
+      </c>
+      <c r="L245">
+        <v>54765</v>
+      </c>
+      <c r="M245">
+        <v>1</v>
+      </c>
+      <c r="N245" s="2">
+        <v>66322</v>
+      </c>
+      <c r="O245">
+        <v>5</v>
+      </c>
+      <c r="P245">
+        <v>500000</v>
+      </c>
+      <c r="Q245">
+        <v>24</v>
+      </c>
+      <c r="R245">
+        <v>72000</v>
+      </c>
+      <c r="S245" t="s">
+        <v>716</v>
+      </c>
+      <c r="T245">
+        <v>2</v>
+      </c>
+      <c r="U245">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="246" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>11315</v>
+      </c>
+      <c r="B246" t="s">
+        <v>717</v>
+      </c>
+      <c r="C246">
+        <v>3215</v>
+      </c>
+      <c r="D246">
+        <v>31304</v>
+      </c>
+      <c r="E246">
+        <v>4</v>
+      </c>
+      <c r="F246">
+        <v>9</v>
+      </c>
+      <c r="G246" t="s">
+        <v>503</v>
+      </c>
+      <c r="H246" t="s">
+        <v>35</v>
+      </c>
+      <c r="I246">
+        <v>26</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>54783</v>
+      </c>
+      <c r="M246">
+        <v>1</v>
+      </c>
+      <c r="N246" s="2">
+        <v>64438</v>
+      </c>
+      <c r="O246">
+        <v>4</v>
+      </c>
+      <c r="P246">
+        <v>2000000</v>
+      </c>
+      <c r="Q246">
+        <v>0</v>
+      </c>
+      <c r="R246">
+        <v>0</v>
+      </c>
+      <c r="S246">
+        <v>1</v>
+      </c>
+      <c r="T246">
+        <v>3</v>
+      </c>
+      <c r="U246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>11317</v>
+      </c>
+      <c r="B247" t="s">
+        <v>718</v>
+      </c>
+      <c r="C247">
+        <v>3215</v>
+      </c>
+      <c r="D247">
+        <v>31304</v>
+      </c>
+      <c r="E247">
+        <v>4</v>
+      </c>
+      <c r="F247">
+        <v>11</v>
+      </c>
+      <c r="G247" t="s">
+        <v>503</v>
+      </c>
+      <c r="H247" t="s">
+        <v>35</v>
+      </c>
+      <c r="I247">
+        <v>26</v>
+      </c>
+      <c r="J247">
+        <v>1</v>
+      </c>
+      <c r="K247" t="s">
+        <v>719</v>
+      </c>
+      <c r="L247">
+        <v>54792</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247" s="2">
+        <v>65168</v>
+      </c>
+      <c r="O247">
+        <v>4</v>
+      </c>
+      <c r="P247">
+        <v>250000</v>
+      </c>
+      <c r="Q247">
+        <v>1</v>
+      </c>
+      <c r="R247">
+        <v>18000</v>
+      </c>
+      <c r="S247">
+        <v>1</v>
+      </c>
+      <c r="T247">
+        <v>2</v>
+      </c>
+      <c r="U247">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="248" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>11337</v>
+      </c>
+      <c r="B248" t="s">
+        <v>720</v>
+      </c>
+      <c r="C248">
+        <v>3115</v>
+      </c>
+      <c r="D248">
+        <v>31304</v>
+      </c>
+      <c r="E248">
+        <v>4</v>
+      </c>
+      <c r="F248">
+        <v>12</v>
+      </c>
+      <c r="G248" t="s">
+        <v>503</v>
+      </c>
+      <c r="H248" t="s">
+        <v>35</v>
+      </c>
+      <c r="I248">
+        <v>51</v>
+      </c>
+      <c r="J248">
+        <v>1</v>
+      </c>
+      <c r="K248" t="s">
+        <v>721</v>
+      </c>
+      <c r="L248">
+        <v>54886</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+      <c r="N248" s="2">
+        <v>64651</v>
+      </c>
+      <c r="O248">
+        <v>4</v>
+      </c>
+      <c r="P248">
+        <v>1200000</v>
+      </c>
+      <c r="Q248">
+        <v>18</v>
+      </c>
+      <c r="S248" t="s">
+        <v>557</v>
+      </c>
+      <c r="T248">
+        <v>2</v>
+      </c>
+      <c r="U248">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="249" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>11338</v>
+      </c>
+      <c r="B249" t="s">
+        <v>722</v>
+      </c>
+      <c r="C249">
+        <v>3115</v>
+      </c>
+      <c r="D249">
+        <v>31304</v>
+      </c>
+      <c r="E249">
+        <v>4</v>
+      </c>
+      <c r="F249">
+        <v>13</v>
+      </c>
+      <c r="G249" t="s">
+        <v>503</v>
+      </c>
+      <c r="H249" t="s">
+        <v>35</v>
+      </c>
+      <c r="I249">
+        <v>51</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249" t="s">
+        <v>723</v>
+      </c>
+      <c r="L249">
+        <v>54889</v>
+      </c>
+      <c r="M249">
+        <v>2</v>
+      </c>
+      <c r="N249" s="2">
+        <v>62094</v>
+      </c>
+      <c r="O249">
+        <v>4</v>
+      </c>
+      <c r="P249">
+        <v>800000</v>
+      </c>
+      <c r="Q249">
+        <v>24</v>
+      </c>
+      <c r="R249">
+        <v>192000</v>
+      </c>
+      <c r="S249" t="s">
+        <v>724</v>
+      </c>
+      <c r="T249">
+        <v>3</v>
+      </c>
+      <c r="U249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>11338</v>
+      </c>
+      <c r="B250" t="s">
+        <v>722</v>
+      </c>
+      <c r="C250">
+        <v>3115</v>
+      </c>
+      <c r="D250">
+        <v>31304</v>
+      </c>
+      <c r="E250">
+        <v>4</v>
+      </c>
+      <c r="F250">
+        <v>13</v>
+      </c>
+      <c r="G250" t="s">
+        <v>503</v>
+      </c>
+      <c r="H250" t="s">
+        <v>35</v>
+      </c>
+      <c r="I250">
+        <v>51</v>
+      </c>
+      <c r="J250">
+        <v>1</v>
+      </c>
+      <c r="K250" t="s">
+        <v>255</v>
+      </c>
+      <c r="L250">
+        <v>54889</v>
+      </c>
+      <c r="M250">
+        <v>2</v>
+      </c>
+      <c r="N250" s="2">
+        <v>62125</v>
+      </c>
+      <c r="O250">
+        <v>5</v>
+      </c>
+      <c r="P250">
+        <v>300000</v>
+      </c>
+      <c r="Q250">
+        <v>24</v>
+      </c>
+      <c r="R250">
+        <v>72000</v>
+      </c>
+      <c r="S250" t="s">
+        <v>196</v>
+      </c>
+      <c r="T250">
+        <v>3</v>
+      </c>
+      <c r="U250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>11338</v>
+      </c>
+      <c r="B251" t="s">
+        <v>722</v>
+      </c>
+      <c r="C251">
+        <v>3115</v>
+      </c>
+      <c r="D251">
+        <v>31304</v>
+      </c>
+      <c r="E251">
+        <v>4</v>
+      </c>
+      <c r="F251">
+        <v>13</v>
+      </c>
+      <c r="G251" t="s">
+        <v>503</v>
+      </c>
+      <c r="H251" t="s">
+        <v>35</v>
+      </c>
+      <c r="I251">
+        <v>51</v>
+      </c>
+      <c r="J251">
+        <v>1</v>
+      </c>
+      <c r="K251" t="s">
+        <v>255</v>
+      </c>
+      <c r="L251">
+        <v>54889</v>
+      </c>
+      <c r="M251">
+        <v>2</v>
+      </c>
+      <c r="N251" s="2">
+        <v>63715</v>
+      </c>
+      <c r="O251">
+        <v>5</v>
+      </c>
+      <c r="P251">
+        <v>1000000</v>
+      </c>
+      <c r="Q251">
+        <v>24</v>
+      </c>
+      <c r="R251">
+        <v>240000</v>
+      </c>
+      <c r="S251" t="s">
+        <v>196</v>
+      </c>
+      <c r="T251">
+        <v>2</v>
+      </c>
+      <c r="U251">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="252" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>11357</v>
+      </c>
+      <c r="B252" t="s">
+        <v>725</v>
+      </c>
+      <c r="C252">
+        <v>3422</v>
+      </c>
+      <c r="D252">
+        <v>30608</v>
+      </c>
+      <c r="E252">
+        <v>11</v>
+      </c>
+      <c r="F252">
+        <v>26</v>
+      </c>
+      <c r="G252" t="s">
+        <v>503</v>
+      </c>
+      <c r="H252" t="s">
+        <v>35</v>
+      </c>
+      <c r="I252">
+        <v>93</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252" t="s">
+        <v>726</v>
+      </c>
+      <c r="L252">
+        <v>54977</v>
+      </c>
+      <c r="M252">
+        <v>2</v>
+      </c>
+      <c r="N252" s="2">
+        <v>66328</v>
+      </c>
+      <c r="O252">
+        <v>4</v>
+      </c>
+      <c r="P252">
+        <v>400000</v>
+      </c>
+      <c r="Q252">
+        <v>12</v>
+      </c>
+      <c r="R252">
+        <v>0</v>
+      </c>
+      <c r="S252">
+        <v>0</v>
+      </c>
+      <c r="T252">
+        <v>2</v>
+      </c>
+      <c r="U252">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="253" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>11382</v>
+      </c>
+      <c r="B253" t="s">
+        <v>727</v>
+      </c>
+      <c r="C253">
+        <v>3608</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>27</v>
+      </c>
+      <c r="G253" t="s">
+        <v>503</v>
+      </c>
+      <c r="H253" t="s">
+        <v>35</v>
+      </c>
+      <c r="I253">
+        <v>94</v>
+      </c>
+      <c r="J253">
+        <v>1</v>
+      </c>
+      <c r="K253" t="s">
+        <v>325</v>
+      </c>
+      <c r="L253">
+        <v>55079</v>
+      </c>
+      <c r="M253">
+        <v>1</v>
+      </c>
+      <c r="N253" s="2">
+        <v>66672</v>
+      </c>
+      <c r="O253">
+        <v>4</v>
+      </c>
+      <c r="P253">
+        <v>50000</v>
+      </c>
+      <c r="Q253">
+        <v>0</v>
+      </c>
+      <c r="R253">
+        <v>0</v>
+      </c>
+      <c r="S253">
+        <v>1</v>
+      </c>
+      <c r="T253">
+        <v>3</v>
+      </c>
+      <c r="U253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>11398</v>
+      </c>
+      <c r="B254" t="s">
+        <v>728</v>
+      </c>
+      <c r="C254">
+        <v>3608</v>
+      </c>
+      <c r="D254">
+        <v>30608</v>
+      </c>
+      <c r="E254">
+        <v>13</v>
+      </c>
+      <c r="F254">
+        <v>34</v>
+      </c>
+      <c r="G254" t="s">
+        <v>503</v>
+      </c>
+      <c r="H254" t="s">
+        <v>35</v>
+      </c>
+      <c r="I254">
+        <v>94</v>
+      </c>
+      <c r="J254">
+        <v>1</v>
+      </c>
+      <c r="K254" t="s">
+        <v>729</v>
+      </c>
+      <c r="L254">
+        <v>55141</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254" s="2">
+        <v>65845</v>
+      </c>
+      <c r="O254">
+        <v>4</v>
+      </c>
+      <c r="P254">
+        <v>150000</v>
+      </c>
+      <c r="Q254">
+        <v>18</v>
+      </c>
+      <c r="R254">
+        <v>0</v>
+      </c>
+      <c r="S254">
+        <v>4</v>
+      </c>
+      <c r="T254">
+        <v>2</v>
+      </c>
+      <c r="U254">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="255" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>11496</v>
+      </c>
+      <c r="B255" t="s">
+        <v>730</v>
+      </c>
+      <c r="C255">
+        <v>3113</v>
+      </c>
+      <c r="D255">
+        <v>31301</v>
+      </c>
+      <c r="E255">
+        <v>7</v>
+      </c>
+      <c r="F255">
+        <v>13</v>
+      </c>
+      <c r="G255" t="s">
+        <v>503</v>
+      </c>
+      <c r="H255" t="s">
+        <v>35</v>
+      </c>
+      <c r="I255">
+        <v>26</v>
+      </c>
+      <c r="J255">
+        <v>1</v>
+      </c>
+      <c r="K255" t="s">
+        <v>731</v>
+      </c>
+      <c r="L255">
+        <v>55580</v>
+      </c>
+      <c r="M255">
+        <v>1</v>
+      </c>
+      <c r="N255" s="2">
+        <v>66477</v>
+      </c>
+      <c r="O255">
+        <v>4</v>
+      </c>
+      <c r="P255">
+        <v>200000</v>
+      </c>
+      <c r="Q255">
+        <v>24</v>
+      </c>
+      <c r="R255">
+        <v>2000</v>
+      </c>
+      <c r="S255">
+        <v>1</v>
+      </c>
+      <c r="T255">
+        <v>3</v>
+      </c>
+      <c r="U255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>11505</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C256">
+        <v>3213</v>
+      </c>
+      <c r="D256">
+        <v>31301</v>
+      </c>
+      <c r="E256">
+        <v>7</v>
+      </c>
+      <c r="F256">
+        <v>22</v>
+      </c>
+      <c r="G256" t="s">
+        <v>503</v>
+      </c>
+      <c r="H256" t="s">
+        <v>35</v>
+      </c>
+      <c r="I256">
+        <v>26</v>
+      </c>
+      <c r="J256">
+        <v>1</v>
+      </c>
+      <c r="K256" t="s">
+        <v>733</v>
+      </c>
+      <c r="L256">
+        <v>55628</v>
+      </c>
+      <c r="M256">
+        <v>1</v>
+      </c>
+      <c r="N256" s="2">
+        <v>65594</v>
+      </c>
+      <c r="O256">
+        <v>5</v>
+      </c>
+      <c r="P256">
+        <v>50000</v>
+      </c>
+      <c r="Q256">
+        <v>0</v>
+      </c>
+      <c r="R256">
+        <v>0</v>
+      </c>
+      <c r="S256" t="s">
+        <v>734</v>
+      </c>
+      <c r="T256">
+        <v>3</v>
+      </c>
+      <c r="U256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>11505</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C257">
+        <v>3213</v>
+      </c>
+      <c r="D257">
+        <v>31301</v>
+      </c>
+      <c r="E257">
+        <v>7</v>
+      </c>
+      <c r="F257">
+        <v>22</v>
+      </c>
+      <c r="G257" t="s">
+        <v>503</v>
+      </c>
+      <c r="H257" t="s">
+        <v>35</v>
+      </c>
+      <c r="I257">
+        <v>26</v>
+      </c>
+      <c r="J257">
+        <v>1</v>
+      </c>
+      <c r="K257" t="s">
+        <v>735</v>
+      </c>
+      <c r="L257">
+        <v>55628</v>
+      </c>
+      <c r="M257">
+        <v>1</v>
+      </c>
+      <c r="N257" s="2">
+        <v>66478</v>
+      </c>
+      <c r="O257">
+        <v>5</v>
+      </c>
+      <c r="P257">
+        <v>50000</v>
+      </c>
+      <c r="Q257">
+        <v>0</v>
+      </c>
+      <c r="R257">
+        <v>0</v>
+      </c>
+      <c r="S257" t="s">
+        <v>736</v>
+      </c>
+      <c r="T257">
+        <v>3</v>
+      </c>
+      <c r="U257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>11533</v>
+      </c>
+      <c r="B258" t="s">
+        <v>737</v>
+      </c>
+      <c r="C258">
+        <v>3113</v>
+      </c>
+      <c r="D258">
+        <v>31301</v>
+      </c>
+      <c r="E258">
+        <v>7</v>
+      </c>
+      <c r="F258">
+        <v>24</v>
+      </c>
+      <c r="G258" t="s">
+        <v>503</v>
+      </c>
+      <c r="H258" t="s">
+        <v>35</v>
+      </c>
+      <c r="I258">
+        <v>51</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258" t="s">
+        <v>36</v>
+      </c>
+      <c r="L258">
+        <v>55798</v>
+      </c>
+      <c r="M258">
+        <v>3</v>
+      </c>
+      <c r="N258" s="2">
+        <v>66173</v>
+      </c>
+      <c r="O258">
+        <v>4</v>
+      </c>
+      <c r="P258">
+        <v>50000</v>
+      </c>
+      <c r="Q258">
+        <v>24</v>
+      </c>
+      <c r="S258">
+        <v>1</v>
+      </c>
+      <c r="T258">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>11533</v>
+      </c>
+      <c r="B259" t="s">
+        <v>737</v>
+      </c>
+      <c r="C259">
+        <v>3113</v>
+      </c>
+      <c r="D259">
+        <v>31301</v>
+      </c>
+      <c r="E259">
+        <v>7</v>
+      </c>
+      <c r="F259">
+        <v>24</v>
+      </c>
+      <c r="G259" t="s">
+        <v>503</v>
+      </c>
+      <c r="H259" t="s">
+        <v>35</v>
+      </c>
+      <c r="I259">
+        <v>51</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259" t="s">
+        <v>36</v>
+      </c>
+      <c r="L259">
+        <v>55798</v>
+      </c>
+      <c r="M259">
+        <v>3</v>
+      </c>
+      <c r="N259" s="2">
+        <v>66416</v>
+      </c>
+      <c r="O259">
+        <v>4</v>
+      </c>
+      <c r="P259">
+        <v>50000</v>
+      </c>
+      <c r="Q259">
+        <v>24</v>
+      </c>
+      <c r="S259">
+        <v>1</v>
+      </c>
+      <c r="T259">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>11533</v>
+      </c>
+      <c r="B260" t="s">
+        <v>737</v>
+      </c>
+      <c r="C260">
+        <v>3113</v>
+      </c>
+      <c r="D260">
+        <v>31301</v>
+      </c>
+      <c r="E260">
+        <v>7</v>
+      </c>
+      <c r="F260">
+        <v>24</v>
+      </c>
+      <c r="G260" t="s">
+        <v>503</v>
+      </c>
+      <c r="H260" t="s">
+        <v>35</v>
+      </c>
+      <c r="I260">
+        <v>51</v>
+      </c>
+      <c r="J260">
+        <v>1</v>
+      </c>
+      <c r="K260" t="s">
+        <v>36</v>
+      </c>
+      <c r="L260">
+        <v>55798</v>
+      </c>
+      <c r="M260">
+        <v>3</v>
+      </c>
+      <c r="N260" s="2">
+        <v>66597</v>
+      </c>
+      <c r="O260">
+        <v>4</v>
+      </c>
+      <c r="P260">
+        <v>50000</v>
+      </c>
+      <c r="Q260">
+        <v>24</v>
+      </c>
+      <c r="S260">
+        <v>0</v>
+      </c>
+      <c r="T260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>11553</v>
+      </c>
+      <c r="B261" t="s">
+        <v>738</v>
+      </c>
+      <c r="C261">
+        <v>3113</v>
+      </c>
+      <c r="D261">
+        <v>31301</v>
+      </c>
+      <c r="E261">
+        <v>7</v>
+      </c>
+      <c r="F261">
+        <v>4</v>
+      </c>
+      <c r="G261" t="s">
+        <v>503</v>
+      </c>
+      <c r="H261" t="s">
+        <v>35</v>
+      </c>
+      <c r="I261">
+        <v>53</v>
+      </c>
+      <c r="J261">
+        <v>1</v>
+      </c>
+      <c r="K261" t="s">
+        <v>739</v>
+      </c>
+      <c r="L261">
+        <v>55880</v>
+      </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
+      <c r="N261" s="2">
+        <v>66438</v>
+      </c>
+      <c r="O261">
+        <v>5</v>
+      </c>
+      <c r="P261">
+        <v>50000</v>
+      </c>
+      <c r="Q261">
+        <v>24</v>
+      </c>
+      <c r="R261">
+        <v>12000</v>
+      </c>
+      <c r="S261">
+        <v>1</v>
+      </c>
+      <c r="T261">
+        <v>3</v>
+      </c>
+      <c r="U261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>11553</v>
+      </c>
+      <c r="B262" t="s">
+        <v>738</v>
+      </c>
+      <c r="C262">
+        <v>3113</v>
+      </c>
+      <c r="D262">
+        <v>31301</v>
+      </c>
+      <c r="E262">
+        <v>7</v>
+      </c>
+      <c r="F262">
+        <v>4</v>
+      </c>
+      <c r="G262" t="s">
+        <v>503</v>
+      </c>
+      <c r="H262" t="s">
+        <v>35</v>
+      </c>
+      <c r="I262">
+        <v>53</v>
+      </c>
+      <c r="J262">
+        <v>1</v>
+      </c>
+      <c r="K262" t="s">
+        <v>740</v>
+      </c>
+      <c r="L262">
+        <v>55880</v>
+      </c>
+      <c r="M262">
+        <v>1</v>
+      </c>
+      <c r="N262" s="2">
+        <v>66244</v>
+      </c>
+      <c r="P262">
+        <v>100000</v>
+      </c>
+      <c r="Q262">
+        <v>24</v>
+      </c>
+      <c r="R262">
+        <v>24000</v>
+      </c>
+      <c r="S262">
+        <v>1</v>
+      </c>
+      <c r="T262">
+        <v>2</v>
+      </c>
+      <c r="U262">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>11553</v>
+      </c>
+      <c r="B263" t="s">
+        <v>738</v>
+      </c>
+      <c r="C263">
+        <v>3113</v>
+      </c>
+      <c r="D263">
+        <v>31301</v>
+      </c>
+      <c r="E263">
+        <v>7</v>
+      </c>
+      <c r="F263">
+        <v>4</v>
+      </c>
+      <c r="G263" t="s">
+        <v>503</v>
+      </c>
+      <c r="H263" t="s">
+        <v>35</v>
+      </c>
+      <c r="I263">
+        <v>53</v>
+      </c>
+      <c r="J263">
+        <v>1</v>
+      </c>
+      <c r="K263" t="s">
+        <v>741</v>
+      </c>
+      <c r="L263">
+        <v>55880</v>
+      </c>
+      <c r="M263">
+        <v>1</v>
+      </c>
+      <c r="N263" s="2">
+        <v>66465</v>
+      </c>
+      <c r="O263">
+        <v>5</v>
+      </c>
+      <c r="P263">
+        <v>50000</v>
+      </c>
+      <c r="Q263">
+        <v>24</v>
+      </c>
+      <c r="R263">
+        <v>12000</v>
+      </c>
+      <c r="S263">
+        <v>1</v>
+      </c>
+      <c r="T263">
+        <v>3</v>
+      </c>
+      <c r="U263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>11556</v>
+      </c>
+      <c r="B264" t="s">
+        <v>742</v>
+      </c>
+      <c r="C264">
+        <v>3213</v>
+      </c>
+      <c r="D264">
+        <v>31301</v>
+      </c>
+      <c r="E264">
+        <v>7</v>
+      </c>
+      <c r="F264">
+        <v>3</v>
+      </c>
+      <c r="G264" t="s">
+        <v>503</v>
+      </c>
+      <c r="H264" t="s">
+        <v>35</v>
+      </c>
+      <c r="I264">
+        <v>53</v>
+      </c>
+      <c r="J264">
+        <v>1</v>
+      </c>
+      <c r="K264" t="s">
+        <v>313</v>
+      </c>
+      <c r="L264">
+        <v>55893</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+      <c r="N264" s="2">
+        <v>66300</v>
+      </c>
+      <c r="O264">
+        <v>4</v>
+      </c>
+      <c r="P264">
+        <v>100000</v>
+      </c>
+      <c r="Q264">
+        <v>12</v>
+      </c>
+      <c r="R264">
+        <v>12000</v>
+      </c>
+      <c r="S264">
+        <v>1</v>
+      </c>
+      <c r="T264">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>11563</v>
+      </c>
+      <c r="B265" t="s">
+        <v>722</v>
+      </c>
+      <c r="C265">
+        <v>3115</v>
+      </c>
+      <c r="D265">
+        <v>31304</v>
+      </c>
+      <c r="E265">
+        <v>4</v>
+      </c>
+      <c r="F265">
+        <v>13</v>
+      </c>
+      <c r="G265" t="s">
+        <v>503</v>
+      </c>
+      <c r="H265" t="s">
+        <v>35</v>
+      </c>
+      <c r="I265">
+        <v>51</v>
+      </c>
+      <c r="J265">
+        <v>1</v>
+      </c>
+      <c r="K265" t="s">
+        <v>723</v>
+      </c>
+      <c r="L265">
+        <v>55930</v>
+      </c>
+      <c r="M265">
+        <v>2</v>
+      </c>
+      <c r="N265" s="2">
+        <v>62094</v>
+      </c>
+      <c r="O265">
+        <v>4</v>
+      </c>
+      <c r="P265">
+        <v>800000</v>
+      </c>
+      <c r="Q265">
+        <v>24</v>
+      </c>
+      <c r="R265">
+        <v>192000</v>
+      </c>
+      <c r="S265" t="s">
+        <v>724</v>
+      </c>
+      <c r="T265">
+        <v>3</v>
+      </c>
+      <c r="U265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>11563</v>
+      </c>
+      <c r="B266" t="s">
+        <v>722</v>
+      </c>
+      <c r="C266">
+        <v>3115</v>
+      </c>
+      <c r="D266">
+        <v>31304</v>
+      </c>
+      <c r="E266">
+        <v>4</v>
+      </c>
+      <c r="F266">
+        <v>13</v>
+      </c>
+      <c r="G266" t="s">
+        <v>503</v>
+      </c>
+      <c r="H266" t="s">
+        <v>35</v>
+      </c>
+      <c r="I266">
+        <v>51</v>
+      </c>
+      <c r="J266">
+        <v>1</v>
+      </c>
+      <c r="K266" t="s">
+        <v>255</v>
+      </c>
+      <c r="L266">
+        <v>55930</v>
+      </c>
+      <c r="M266">
+        <v>2</v>
+      </c>
+      <c r="N266" s="2">
+        <v>62125</v>
+      </c>
+      <c r="O266">
+        <v>5</v>
+      </c>
+      <c r="P266">
+        <v>300000</v>
+      </c>
+      <c r="Q266">
+        <v>24</v>
+      </c>
+      <c r="R266">
+        <v>72000</v>
+      </c>
+      <c r="S266" t="s">
+        <v>196</v>
+      </c>
+      <c r="T266">
+        <v>3</v>
+      </c>
+      <c r="U266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>11563</v>
+      </c>
+      <c r="B267" t="s">
+        <v>722</v>
+      </c>
+      <c r="C267">
+        <v>3115</v>
+      </c>
+      <c r="D267">
+        <v>31304</v>
+      </c>
+      <c r="E267">
+        <v>4</v>
+      </c>
+      <c r="F267">
+        <v>13</v>
+      </c>
+      <c r="G267" t="s">
+        <v>503</v>
+      </c>
+      <c r="H267" t="s">
+        <v>35</v>
+      </c>
+      <c r="I267">
+        <v>51</v>
+      </c>
+      <c r="J267">
+        <v>1</v>
+      </c>
+      <c r="K267" t="s">
+        <v>255</v>
+      </c>
+      <c r="L267">
+        <v>55930</v>
+      </c>
+      <c r="M267">
+        <v>2</v>
+      </c>
+      <c r="N267" s="2">
+        <v>63715</v>
+      </c>
+      <c r="O267">
+        <v>5</v>
+      </c>
+      <c r="P267">
+        <v>1000000</v>
+      </c>
+      <c r="Q267">
+        <v>24</v>
+      </c>
+      <c r="R267">
+        <v>240000</v>
+      </c>
+      <c r="S267" t="s">
+        <v>196</v>
+      </c>
+      <c r="T267">
+        <v>2</v>
+      </c>
+      <c r="U267">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>11564</v>
+      </c>
+      <c r="B268" t="s">
+        <v>720</v>
+      </c>
+      <c r="C268">
+        <v>3115</v>
+      </c>
+      <c r="D268">
+        <v>31304</v>
+      </c>
+      <c r="E268">
+        <v>4</v>
+      </c>
+      <c r="F268">
+        <v>12</v>
+      </c>
+      <c r="G268" t="s">
+        <v>503</v>
+      </c>
+      <c r="H268" t="s">
+        <v>35</v>
+      </c>
+      <c r="I268">
+        <v>51</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
+      </c>
+      <c r="K268" t="s">
+        <v>721</v>
+      </c>
+      <c r="L268">
+        <v>55938</v>
+      </c>
+      <c r="M268">
+        <v>1</v>
+      </c>
+      <c r="N268" s="2">
+        <v>64651</v>
+      </c>
+      <c r="O268">
+        <v>4</v>
+      </c>
+      <c r="P268">
+        <v>1200000</v>
+      </c>
+      <c r="Q268">
+        <v>18</v>
+      </c>
+      <c r="S268" t="s">
+        <v>557</v>
+      </c>
+      <c r="T268">
+        <v>2</v>
+      </c>
+      <c r="U268">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>11736</v>
+      </c>
+      <c r="B269" t="s">
+        <v>743</v>
+      </c>
+      <c r="C269">
+        <v>1207</v>
+      </c>
+      <c r="D269">
+        <v>11102</v>
+      </c>
+      <c r="E269">
+        <v>3</v>
+      </c>
+      <c r="F269">
+        <v>35</v>
+      </c>
+      <c r="G269" t="s">
+        <v>503</v>
+      </c>
+      <c r="H269" t="s">
+        <v>35</v>
+      </c>
+      <c r="I269">
+        <v>11</v>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269" t="s">
+        <v>744</v>
+      </c>
+      <c r="L269">
+        <v>56723</v>
+      </c>
+      <c r="M269">
+        <v>2</v>
+      </c>
+      <c r="N269" s="2">
+        <v>66267</v>
+      </c>
+      <c r="O269">
+        <v>5</v>
+      </c>
+      <c r="P269">
+        <v>115000</v>
+      </c>
+      <c r="Q269">
+        <v>0</v>
+      </c>
+      <c r="R269">
+        <v>0</v>
+      </c>
+      <c r="S269">
+        <v>2</v>
+      </c>
+      <c r="T269">
+        <v>3</v>
+      </c>
+      <c r="U269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>11737</v>
+      </c>
+      <c r="B270" t="s">
+        <v>745</v>
+      </c>
+      <c r="C270">
+        <v>1207</v>
+      </c>
+      <c r="D270">
+        <v>11102</v>
+      </c>
+      <c r="E270">
+        <v>3</v>
+      </c>
+      <c r="F270">
+        <v>36</v>
+      </c>
+      <c r="G270" t="s">
+        <v>503</v>
+      </c>
+      <c r="H270" t="s">
+        <v>35</v>
+      </c>
+      <c r="I270">
+        <v>11</v>
+      </c>
+      <c r="J270">
+        <v>1</v>
+      </c>
+      <c r="K270" t="s">
+        <v>746</v>
+      </c>
+      <c r="O270">
+        <v>4</v>
+      </c>
+      <c r="P270">
+        <v>50000</v>
+      </c>
+      <c r="Q270">
+        <v>12</v>
+      </c>
+      <c r="S270" t="s">
+        <v>215</v>
+      </c>
+      <c r="T270">
+        <v>3</v>
+      </c>
+      <c r="U270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>11743</v>
+      </c>
+      <c r="B271" t="s">
+        <v>747</v>
+      </c>
+      <c r="C271">
+        <v>1107</v>
+      </c>
+      <c r="D271">
+        <v>11102</v>
+      </c>
+      <c r="E271">
+        <v>3</v>
+      </c>
+      <c r="F271">
+        <v>43</v>
+      </c>
+      <c r="G271" t="s">
+        <v>503</v>
+      </c>
+      <c r="H271" t="s">
+        <v>35</v>
+      </c>
+      <c r="I271">
+        <v>11</v>
+      </c>
+      <c r="J271">
+        <v>1</v>
+      </c>
+      <c r="K271" t="s">
+        <v>744</v>
+      </c>
+      <c r="L271">
+        <v>56757</v>
+      </c>
+      <c r="M271">
+        <v>3</v>
+      </c>
+      <c r="N271" s="2">
+        <v>66446</v>
+      </c>
+      <c r="O271">
+        <v>4</v>
+      </c>
+      <c r="P271">
+        <v>250000</v>
+      </c>
+      <c r="Q271">
+        <v>0</v>
+      </c>
+      <c r="R271">
+        <v>0</v>
+      </c>
+      <c r="S271">
+        <v>2</v>
+      </c>
+      <c r="T271">
+        <v>3</v>
+      </c>
+      <c r="U271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>11746</v>
+      </c>
+      <c r="B272" t="s">
+        <v>748</v>
+      </c>
+      <c r="C272">
+        <v>1107</v>
+      </c>
+      <c r="D272">
+        <v>11102</v>
+      </c>
+      <c r="E272">
+        <v>3</v>
+      </c>
+      <c r="F272">
+        <v>44</v>
+      </c>
+      <c r="G272" t="s">
+        <v>503</v>
+      </c>
+      <c r="H272" t="s">
+        <v>35</v>
+      </c>
+      <c r="I272">
+        <v>11</v>
+      </c>
+      <c r="J272">
+        <v>1</v>
+      </c>
+      <c r="K272" t="s">
+        <v>749</v>
+      </c>
+      <c r="L272">
+        <v>56771</v>
+      </c>
+      <c r="M272">
+        <v>1</v>
+      </c>
+      <c r="N272" s="2">
+        <v>66267</v>
+      </c>
+      <c r="O272">
+        <v>5</v>
+      </c>
+      <c r="P272">
+        <v>150000</v>
+      </c>
+      <c r="Q272">
+        <v>12</v>
+      </c>
+      <c r="R272">
+        <v>1800</v>
+      </c>
+      <c r="S272">
+        <v>2</v>
+      </c>
+      <c r="T272">
+        <v>3</v>
+      </c>
+      <c r="U272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>11747</v>
+      </c>
+      <c r="B273" t="s">
+        <v>750</v>
+      </c>
+      <c r="C273">
+        <v>1107</v>
+      </c>
+      <c r="D273">
+        <v>11102</v>
+      </c>
+      <c r="E273">
+        <v>3</v>
+      </c>
+      <c r="F273">
+        <v>46</v>
+      </c>
+      <c r="G273" t="s">
+        <v>503</v>
+      </c>
+      <c r="H273" t="s">
+        <v>35</v>
+      </c>
+      <c r="I273">
+        <v>11</v>
+      </c>
+      <c r="J273">
+        <v>1</v>
+      </c>
+      <c r="K273" t="s">
+        <v>749</v>
+      </c>
+      <c r="L273">
+        <v>56778</v>
+      </c>
+      <c r="M273">
+        <v>3</v>
+      </c>
+      <c r="N273" s="2">
+        <v>65837</v>
+      </c>
+      <c r="O273">
+        <v>4</v>
+      </c>
+      <c r="P273">
+        <v>200000</v>
+      </c>
+      <c r="Q273">
+        <v>12</v>
+      </c>
+      <c r="R273">
+        <v>0</v>
+      </c>
+      <c r="S273">
+        <v>5</v>
+      </c>
+      <c r="T273">
+        <v>3</v>
+      </c>
+      <c r="U273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>11747</v>
+      </c>
+      <c r="B274" t="s">
+        <v>750</v>
+      </c>
+      <c r="C274">
+        <v>1107</v>
+      </c>
+      <c r="D274">
+        <v>11102</v>
+      </c>
+      <c r="E274">
+        <v>3</v>
+      </c>
+      <c r="F274">
+        <v>46</v>
+      </c>
+      <c r="G274" t="s">
+        <v>503</v>
+      </c>
+      <c r="H274" t="s">
+        <v>35</v>
+      </c>
+      <c r="I274">
+        <v>11</v>
+      </c>
+      <c r="J274">
+        <v>1</v>
+      </c>
+      <c r="K274" t="s">
+        <v>699</v>
+      </c>
+      <c r="L274">
+        <v>56776</v>
+      </c>
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="O274">
+        <v>5</v>
+      </c>
+      <c r="P274">
+        <v>25000</v>
+      </c>
+      <c r="Q274">
+        <v>0</v>
+      </c>
+      <c r="R274">
+        <v>0</v>
+      </c>
+      <c r="S274">
+        <v>1</v>
+      </c>
+      <c r="T274">
+        <v>3</v>
+      </c>
+      <c r="U274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>11748</v>
+      </c>
+      <c r="B275" t="s">
+        <v>751</v>
+      </c>
+      <c r="C275">
+        <v>1107</v>
+      </c>
+      <c r="D275">
+        <v>11102</v>
+      </c>
+      <c r="E275">
+        <v>3</v>
+      </c>
+      <c r="F275">
+        <v>47</v>
+      </c>
+      <c r="G275" t="s">
+        <v>503</v>
+      </c>
+      <c r="H275" t="s">
+        <v>35</v>
+      </c>
+      <c r="I275">
+        <v>11</v>
+      </c>
+      <c r="J275">
+        <v>1</v>
+      </c>
+      <c r="K275" t="s">
+        <v>746</v>
+      </c>
+      <c r="L275">
+        <v>56783</v>
+      </c>
+      <c r="M275">
+        <v>2</v>
+      </c>
+      <c r="N275" s="2">
+        <v>66090</v>
+      </c>
+      <c r="O275">
+        <v>5</v>
+      </c>
+      <c r="P275">
+        <v>150000</v>
+      </c>
+      <c r="Q275">
+        <v>0</v>
+      </c>
+      <c r="R275">
+        <v>0</v>
+      </c>
+      <c r="S275">
+        <v>3</v>
+      </c>
+      <c r="T275">
+        <v>3</v>
+      </c>
+      <c r="U275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>11883</v>
+      </c>
+      <c r="B276" t="s">
+        <v>752</v>
+      </c>
+      <c r="C276">
+        <v>4207</v>
+      </c>
+      <c r="D276">
+        <v>40806</v>
+      </c>
+      <c r="E276">
+        <v>14</v>
+      </c>
+      <c r="F276">
+        <v>24</v>
+      </c>
+      <c r="G276" t="s">
+        <v>503</v>
+      </c>
+      <c r="H276" t="s">
+        <v>35</v>
+      </c>
+      <c r="I276">
+        <v>26</v>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
+      <c r="K276" t="s">
+        <v>495</v>
+      </c>
+      <c r="L276">
+        <v>57568</v>
+      </c>
+      <c r="M276">
+        <v>2</v>
+      </c>
+      <c r="N276" s="2">
+        <v>65108</v>
+      </c>
+      <c r="O276">
+        <v>4</v>
+      </c>
+      <c r="P276">
+        <v>60000</v>
+      </c>
+      <c r="Q276">
+        <v>0</v>
+      </c>
+      <c r="R276">
+        <v>0</v>
+      </c>
+      <c r="S276" t="s">
+        <v>753</v>
+      </c>
+      <c r="T276">
+        <v>3</v>
+      </c>
+      <c r="U276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>11896</v>
+      </c>
+      <c r="B277" t="s">
+        <v>754</v>
+      </c>
+      <c r="C277">
+        <v>4107</v>
+      </c>
+      <c r="E277">
+        <v>14</v>
+      </c>
+      <c r="F277">
+        <v>29</v>
+      </c>
+      <c r="G277" t="s">
+        <v>503</v>
+      </c>
+      <c r="H277" t="s">
+        <v>35</v>
+      </c>
+      <c r="I277">
+        <v>26</v>
+      </c>
+      <c r="J277">
+        <v>1</v>
+      </c>
+      <c r="K277" t="s">
+        <v>755</v>
+      </c>
+      <c r="L277">
+        <v>57645</v>
+      </c>
+      <c r="M277">
+        <v>1</v>
+      </c>
+      <c r="N277" s="2">
+        <v>64745</v>
+      </c>
+      <c r="O277">
+        <v>4</v>
+      </c>
+      <c r="P277">
+        <v>400000</v>
+      </c>
+      <c r="Q277">
+        <v>0</v>
+      </c>
+      <c r="R277">
+        <v>0</v>
+      </c>
+      <c r="S277" t="s">
+        <v>756</v>
+      </c>
+      <c r="T277">
+        <v>3</v>
+      </c>
+      <c r="U277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>11901</v>
+      </c>
+      <c r="B278" t="s">
+        <v>757</v>
+      </c>
+      <c r="C278">
+        <v>4207</v>
+      </c>
+      <c r="D278">
+        <v>40806</v>
+      </c>
+      <c r="E278">
+        <v>14</v>
+      </c>
+      <c r="F278">
+        <v>34</v>
+      </c>
+      <c r="G278" t="s">
+        <v>503</v>
+      </c>
+      <c r="H278" t="s">
+        <v>35</v>
+      </c>
+      <c r="I278">
+        <v>26</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278" t="s">
+        <v>758</v>
+      </c>
+      <c r="L278">
+        <v>57680</v>
+      </c>
+      <c r="M278">
+        <v>3</v>
+      </c>
+      <c r="N278" s="2">
+        <v>65806</v>
+      </c>
+      <c r="O278">
+        <v>4</v>
+      </c>
+      <c r="P278">
+        <v>35000</v>
+      </c>
+      <c r="Q278">
+        <v>24</v>
+      </c>
+      <c r="R278">
+        <v>8400</v>
+      </c>
+      <c r="S278" t="s">
+        <v>759</v>
+      </c>
+      <c r="T278">
+        <v>3</v>
+      </c>
+      <c r="U278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>11903</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="C279">
+        <v>4207</v>
+      </c>
+      <c r="D279">
+        <v>40806</v>
+      </c>
+      <c r="E279">
+        <v>14</v>
+      </c>
+      <c r="F279">
+        <v>36</v>
+      </c>
+      <c r="G279" t="s">
+        <v>503</v>
+      </c>
+      <c r="H279" t="s">
+        <v>35</v>
+      </c>
+      <c r="I279">
+        <v>26</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279" t="s">
+        <v>761</v>
+      </c>
+      <c r="L279">
+        <v>57685</v>
+      </c>
+      <c r="M279">
+        <v>1</v>
+      </c>
+      <c r="N279" s="2">
+        <v>65107</v>
+      </c>
+      <c r="O279">
+        <v>5</v>
+      </c>
+      <c r="P279">
+        <v>300000</v>
+      </c>
+      <c r="Q279">
+        <v>0</v>
+      </c>
+      <c r="R279">
+        <v>0</v>
+      </c>
+      <c r="S279">
+        <v>1</v>
+      </c>
+      <c r="T279">
+        <v>3</v>
+      </c>
+      <c r="U279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>11903</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="C280">
+        <v>4207</v>
+      </c>
+      <c r="D280">
+        <v>40806</v>
+      </c>
+      <c r="E280">
+        <v>14</v>
+      </c>
+      <c r="F280">
+        <v>36</v>
+      </c>
+      <c r="G280" t="s">
+        <v>503</v>
+      </c>
+      <c r="H280" t="s">
+        <v>35</v>
+      </c>
+      <c r="I280">
+        <v>26</v>
+      </c>
+      <c r="J280">
+        <v>1</v>
+      </c>
+      <c r="K280" t="s">
+        <v>762</v>
+      </c>
+      <c r="L280">
+        <v>57685</v>
+      </c>
+      <c r="M280">
+        <v>1</v>
+      </c>
+      <c r="N280" s="2">
+        <v>66326</v>
+      </c>
+      <c r="O280">
+        <v>4</v>
+      </c>
+      <c r="P280">
+        <v>100000</v>
+      </c>
+      <c r="Q280">
+        <v>24</v>
+      </c>
+      <c r="R280">
+        <v>2000</v>
+      </c>
+      <c r="S280">
+        <v>1</v>
+      </c>
+      <c r="T280">
+        <v>3</v>
+      </c>
+      <c r="U280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>11911</v>
+      </c>
+      <c r="B281" t="s">
+        <v>763</v>
+      </c>
+      <c r="C281">
+        <v>7102</v>
+      </c>
+      <c r="D281">
+        <v>70210</v>
+      </c>
+      <c r="E281">
+        <v>6</v>
+      </c>
+      <c r="F281">
+        <v>15</v>
+      </c>
+      <c r="G281" t="s">
+        <v>503</v>
+      </c>
+      <c r="H281" t="s">
+        <v>35</v>
+      </c>
+      <c r="I281">
+        <v>71</v>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281" t="s">
+        <v>53</v>
+      </c>
+      <c r="L281">
+        <v>57724</v>
+      </c>
+      <c r="M281">
+        <v>1</v>
+      </c>
+      <c r="N281" s="2">
+        <v>66177</v>
+      </c>
+      <c r="O281">
+        <v>4</v>
+      </c>
+      <c r="P281">
+        <v>200000</v>
+      </c>
+      <c r="Q281">
+        <v>36</v>
+      </c>
+      <c r="R281">
+        <v>72000</v>
+      </c>
+      <c r="S281" t="s">
+        <v>764</v>
+      </c>
+      <c r="T281">
+        <v>3</v>
+      </c>
+      <c r="U281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>11915</v>
+      </c>
+      <c r="B282" t="s">
+        <v>765</v>
+      </c>
+      <c r="C282">
+        <v>7103</v>
+      </c>
+      <c r="D282">
+        <v>70403</v>
+      </c>
+      <c r="E282">
+        <v>7</v>
+      </c>
+      <c r="F282">
+        <v>19</v>
+      </c>
+      <c r="G282" t="s">
+        <v>503</v>
+      </c>
+      <c r="H282" t="s">
+        <v>35</v>
+      </c>
+      <c r="I282">
+        <v>71</v>
+      </c>
+      <c r="J282">
+        <v>1</v>
+      </c>
+      <c r="K282" t="s">
+        <v>766</v>
+      </c>
+      <c r="L282">
+        <v>57741</v>
+      </c>
+      <c r="M282">
+        <v>5</v>
+      </c>
+      <c r="N282" s="2">
+        <v>66250</v>
+      </c>
+      <c r="O282">
+        <v>4</v>
+      </c>
+      <c r="P282">
+        <v>400000</v>
+      </c>
+      <c r="Q282">
+        <v>24</v>
+      </c>
+      <c r="R282">
+        <v>24000</v>
+      </c>
+      <c r="S282" t="s">
+        <v>93</v>
+      </c>
+      <c r="T282">
+        <v>3</v>
+      </c>
+      <c r="U282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>11917</v>
+      </c>
+      <c r="B283" t="s">
+        <v>767</v>
+      </c>
+      <c r="C283">
+        <v>7103</v>
+      </c>
+      <c r="D283">
+        <v>70403</v>
+      </c>
+      <c r="E283">
+        <v>7</v>
+      </c>
+      <c r="F283">
+        <v>21</v>
+      </c>
+      <c r="G283" t="s">
+        <v>503</v>
+      </c>
+      <c r="H283" t="s">
+        <v>35</v>
+      </c>
+      <c r="I283">
+        <v>71</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283" t="s">
+        <v>768</v>
+      </c>
+      <c r="L283">
+        <v>57748</v>
+      </c>
+      <c r="M283">
+        <v>1</v>
+      </c>
+      <c r="N283" s="2">
+        <v>66271</v>
+      </c>
+      <c r="O283">
+        <v>4</v>
+      </c>
+      <c r="P283">
+        <v>200000</v>
+      </c>
+      <c r="Q283">
+        <v>0</v>
+      </c>
+      <c r="R283">
+        <v>0</v>
+      </c>
+      <c r="S283" t="s">
+        <v>764</v>
+      </c>
+      <c r="T283">
+        <v>3</v>
+      </c>
+      <c r="U283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>11920</v>
+      </c>
+      <c r="B284" t="s">
+        <v>769</v>
+      </c>
+      <c r="C284">
+        <v>7203</v>
+      </c>
+      <c r="D284">
+        <v>70403</v>
+      </c>
+      <c r="E284">
+        <v>7</v>
+      </c>
+      <c r="F284">
+        <v>24</v>
+      </c>
+      <c r="G284" t="s">
+        <v>503</v>
+      </c>
+      <c r="H284" t="s">
+        <v>35</v>
+      </c>
+      <c r="I284">
+        <v>71</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284" t="s">
+        <v>766</v>
+      </c>
+      <c r="L284">
+        <v>57761</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284" s="2">
+        <v>66268</v>
+      </c>
+      <c r="O284">
+        <v>4</v>
+      </c>
+      <c r="P284">
+        <v>100000</v>
+      </c>
+      <c r="Q284">
+        <v>24</v>
+      </c>
+      <c r="R284">
+        <v>24000</v>
+      </c>
+      <c r="S284" t="s">
+        <v>557</v>
+      </c>
+      <c r="T284">
+        <v>2</v>
+      </c>
+      <c r="U284">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>11921</v>
+      </c>
+      <c r="B285" t="s">
+        <v>770</v>
+      </c>
+      <c r="C285">
+        <v>7103</v>
+      </c>
+      <c r="D285">
+        <v>70403</v>
+      </c>
+      <c r="E285">
+        <v>7</v>
+      </c>
+      <c r="F285">
+        <v>25</v>
+      </c>
+      <c r="G285" t="s">
+        <v>503</v>
+      </c>
+      <c r="H285" t="s">
+        <v>35</v>
+      </c>
+      <c r="I285">
+        <v>71</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285" t="s">
+        <v>771</v>
+      </c>
+      <c r="L285">
+        <v>57766</v>
+      </c>
+      <c r="M285">
+        <v>1</v>
+      </c>
+      <c r="N285" s="2">
+        <v>66205</v>
+      </c>
+      <c r="O285">
+        <v>5</v>
+      </c>
+      <c r="P285">
+        <v>60000</v>
+      </c>
+      <c r="Q285">
+        <v>0</v>
+      </c>
+      <c r="R285">
+        <v>0</v>
+      </c>
+      <c r="S285" t="s">
+        <v>93</v>
+      </c>
+      <c r="T285">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>11936</v>
+      </c>
+      <c r="B286" t="s">
+        <v>772</v>
+      </c>
+      <c r="C286">
+        <v>3677</v>
+      </c>
+      <c r="D286">
+        <v>30608</v>
+      </c>
+      <c r="E286">
+        <v>28</v>
+      </c>
+      <c r="F286">
+        <v>63</v>
+      </c>
+      <c r="G286" t="s">
+        <v>503</v>
+      </c>
+      <c r="H286" t="s">
+        <v>35</v>
+      </c>
+      <c r="I286">
+        <v>94</v>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
+      <c r="K286" t="s">
+        <v>773</v>
+      </c>
+      <c r="L286">
+        <v>57839</v>
+      </c>
+      <c r="M286">
+        <v>2</v>
+      </c>
+      <c r="N286" s="2">
+        <v>66512</v>
+      </c>
+      <c r="O286">
+        <v>4</v>
+      </c>
+      <c r="P286">
+        <v>400000</v>
+      </c>
+      <c r="Q286">
+        <v>20</v>
+      </c>
+      <c r="R286">
+        <v>0</v>
+      </c>
+      <c r="S286" t="s">
+        <v>294</v>
+      </c>
+      <c r="T286">
+        <v>3</v>
+      </c>
+      <c r="U286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>11963</v>
+      </c>
+      <c r="B287" t="s">
+        <v>774</v>
+      </c>
+      <c r="C287">
+        <v>4107</v>
+      </c>
+      <c r="D287">
+        <v>40806</v>
+      </c>
+      <c r="E287">
+        <v>14</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+      <c r="G287" t="s">
+        <v>503</v>
+      </c>
+      <c r="H287" t="s">
+        <v>35</v>
+      </c>
+      <c r="I287">
+        <v>53</v>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287" t="s">
+        <v>532</v>
+      </c>
+      <c r="L287">
+        <v>57992</v>
+      </c>
+      <c r="M287">
+        <v>1</v>
+      </c>
+      <c r="N287" s="2">
+        <v>65806</v>
+      </c>
+      <c r="O287">
+        <v>5</v>
+      </c>
+      <c r="P287">
+        <v>200000</v>
+      </c>
+      <c r="Q287">
+        <v>10</v>
+      </c>
+      <c r="R287">
+        <v>20000</v>
+      </c>
+      <c r="S287">
+        <v>1</v>
+      </c>
+      <c r="T287">
+        <v>2</v>
+      </c>
+      <c r="U287">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>11963</v>
+      </c>
+      <c r="B288" t="s">
+        <v>774</v>
+      </c>
+      <c r="C288">
+        <v>4107</v>
+      </c>
+      <c r="D288">
+        <v>40806</v>
+      </c>
+      <c r="E288">
+        <v>14</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288" t="s">
+        <v>503</v>
+      </c>
+      <c r="H288" t="s">
+        <v>35</v>
+      </c>
+      <c r="I288">
+        <v>53</v>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288" t="s">
+        <v>775</v>
+      </c>
+      <c r="L288">
+        <v>57992</v>
+      </c>
+      <c r="M288">
+        <v>1</v>
+      </c>
+      <c r="N288" s="2">
+        <v>66348</v>
+      </c>
+      <c r="O288">
+        <v>5</v>
+      </c>
+      <c r="P288">
+        <v>400000</v>
+      </c>
+      <c r="Q288">
+        <v>0</v>
+      </c>
+      <c r="R288">
+        <v>0</v>
+      </c>
+      <c r="S288">
+        <v>1</v>
+      </c>
+      <c r="T288">
+        <v>2</v>
+      </c>
+      <c r="U288">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>11963</v>
+      </c>
+      <c r="B289" t="s">
+        <v>774</v>
+      </c>
+      <c r="C289">
+        <v>4107</v>
+      </c>
+      <c r="D289">
+        <v>40806</v>
+      </c>
+      <c r="E289">
+        <v>14</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+      <c r="G289" t="s">
+        <v>503</v>
+      </c>
+      <c r="H289" t="s">
+        <v>35</v>
+      </c>
+      <c r="I289">
+        <v>53</v>
+      </c>
+      <c r="J289">
+        <v>1</v>
+      </c>
+      <c r="K289" t="s">
+        <v>532</v>
+      </c>
+      <c r="L289">
+        <v>57992</v>
+      </c>
+      <c r="M289">
+        <v>1</v>
+      </c>
+      <c r="N289" s="2">
+        <v>65654</v>
+      </c>
+      <c r="O289">
+        <v>4</v>
+      </c>
+      <c r="P289">
+        <v>60000</v>
+      </c>
+      <c r="Q289">
+        <v>12</v>
+      </c>
+      <c r="R289">
+        <v>7200</v>
+      </c>
+      <c r="S289">
+        <v>1</v>
+      </c>
+      <c r="T289">
+        <v>2</v>
+      </c>
+      <c r="U289">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>11971</v>
+      </c>
+      <c r="B290" t="s">
+        <v>776</v>
+      </c>
+      <c r="C290">
+        <v>4207</v>
+      </c>
+      <c r="D290">
+        <v>40806</v>
+      </c>
+      <c r="E290">
+        <v>14</v>
+      </c>
+      <c r="F290">
+        <v>4</v>
+      </c>
+      <c r="G290" t="s">
+        <v>503</v>
+      </c>
+      <c r="H290" t="s">
+        <v>35</v>
+      </c>
+      <c r="I290">
+        <v>53</v>
+      </c>
+      <c r="J290">
+        <v>1</v>
+      </c>
+      <c r="K290" t="s">
+        <v>313</v>
+      </c>
+      <c r="L290">
+        <v>58034</v>
+      </c>
+      <c r="M290">
+        <v>4</v>
+      </c>
+      <c r="N290" s="2">
+        <v>66185</v>
+      </c>
+      <c r="O290">
+        <v>5</v>
+      </c>
+      <c r="P290">
+        <v>100000</v>
+      </c>
+      <c r="Q290">
+        <v>0</v>
+      </c>
+      <c r="R290">
+        <v>0</v>
+      </c>
+      <c r="S290">
+        <v>1</v>
+      </c>
+      <c r="T290">
+        <v>3</v>
+      </c>
+      <c r="U290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>11971</v>
+      </c>
+      <c r="B291" t="s">
+        <v>776</v>
+      </c>
+      <c r="C291">
+        <v>4207</v>
+      </c>
+      <c r="D291">
+        <v>40806</v>
+      </c>
+      <c r="E291">
+        <v>14</v>
+      </c>
+      <c r="F291">
+        <v>4</v>
+      </c>
+      <c r="G291" t="s">
+        <v>503</v>
+      </c>
+      <c r="H291" t="s">
+        <v>35</v>
+      </c>
+      <c r="I291">
+        <v>53</v>
+      </c>
+      <c r="J291">
+        <v>1</v>
+      </c>
+      <c r="K291" t="s">
+        <v>777</v>
+      </c>
+      <c r="L291">
+        <v>58034</v>
+      </c>
+      <c r="M291">
+        <v>4</v>
+      </c>
+      <c r="N291" s="2">
+        <v>66597</v>
+      </c>
+      <c r="O291">
+        <v>5</v>
+      </c>
+      <c r="P291">
+        <v>50000</v>
+      </c>
+      <c r="Q291">
+        <v>0</v>
+      </c>
+      <c r="R291">
+        <v>0</v>
+      </c>
+      <c r="S291">
+        <v>1</v>
+      </c>
+      <c r="T291">
+        <v>3</v>
+      </c>
+      <c r="U291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>11971</v>
+      </c>
+      <c r="B292" t="s">
+        <v>776</v>
+      </c>
+      <c r="C292">
+        <v>4207</v>
+      </c>
+      <c r="D292">
+        <v>40806</v>
+      </c>
+      <c r="E292">
+        <v>14</v>
+      </c>
+      <c r="F292">
+        <v>4</v>
+      </c>
+      <c r="G292" t="s">
+        <v>503</v>
+      </c>
+      <c r="H292" t="s">
+        <v>35</v>
+      </c>
+      <c r="I292">
+        <v>53</v>
+      </c>
+      <c r="J292">
+        <v>1</v>
+      </c>
+      <c r="K292" t="s">
+        <v>313</v>
+      </c>
+      <c r="L292">
+        <v>58034</v>
+      </c>
+      <c r="M292">
+        <v>4</v>
+      </c>
+      <c r="N292" s="2">
+        <v>65750</v>
+      </c>
+      <c r="O292">
+        <v>5</v>
+      </c>
+      <c r="P292">
+        <v>10000</v>
+      </c>
+      <c r="Q292">
+        <v>0</v>
+      </c>
+      <c r="R292">
+        <v>0</v>
+      </c>
+      <c r="S292">
+        <v>1</v>
+      </c>
+      <c r="T292">
+        <v>3</v>
+      </c>
+      <c r="U292">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataset/Part 11_2_ Lending and Outstanding Loans.xlsx
+++ b/dataset/Part 11_2_ Lending and Outstanding Loans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-28-today (1)\2025-11-28-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F77286-B660-4CBC-92CB-241F72567345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFA04AF-B0B8-49F6-B9B0-D5D14941D42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="805">
   <si>
     <t>ID</t>
   </si>
@@ -2366,6 +2366,87 @@
   </si>
   <si>
     <t>GHARBAARI PRAYOJAN KO LAGI</t>
+  </si>
+  <si>
+    <t>4293996c-58df-4fcb-9ce7-09bbadab789c</t>
+  </si>
+  <si>
+    <t>GHAR KHARCHA KO LAGI DEKO</t>
+  </si>
+  <si>
+    <t>bcec5310-7a57-4aa0-b614-c2c00f41732d</t>
+  </si>
+  <si>
+    <t>c2d301a1-3cae-446e-850c-8670132903d4</t>
+  </si>
+  <si>
+    <t>CHHIMEKI LAI</t>
+  </si>
+  <si>
+    <t>3d83cc67-1308-4834-b27d-4e687936f59c</t>
+  </si>
+  <si>
+    <t>ec790fbe-7ec5-4a6b-a044-63256ae525e5</t>
+  </si>
+  <si>
+    <t>4e38e751-154c-4c2d-8eb9-3995dd4293ae</t>
+  </si>
+  <si>
+    <t>XORIKO BIWAHA GARNA LAI</t>
+  </si>
+  <si>
+    <t>cffd6575-e724-46cf-9620-2c83b10cd2e6</t>
+  </si>
+  <si>
+    <t>GHAR BANAUNA LAI</t>
+  </si>
+  <si>
+    <t>58499b69-d22b-4d9e-8246-5a42ac197e8b</t>
+  </si>
+  <si>
+    <t>KAJKRIYA GARNALAI</t>
+  </si>
+  <si>
+    <t>196d4f18-28bc-4994-aa48-ea4085fd66cd</t>
+  </si>
+  <si>
+    <t>BIDESHA JANA KO LAGI</t>
+  </si>
+  <si>
+    <t>c6c0d4b5-5fe9-48e6-bbcd-ce96d947fef5</t>
+  </si>
+  <si>
+    <t>BIDESH PATHAUDA LEYAKO</t>
+  </si>
+  <si>
+    <t>995418d8-c41c-45c3-a495-f486fcf54dc9</t>
+  </si>
+  <si>
+    <t>DOJER KINNA</t>
+  </si>
+  <si>
+    <t>f540c823-0a38-45f7-a2ab-f89ed4b46343</t>
+  </si>
+  <si>
+    <t>2a844aeb-4585-4e4d-b317-1294ddfe704c</t>
+  </si>
+  <si>
+    <t>GHARAISHI KHARC</t>
+  </si>
+  <si>
+    <t>7203e045-085b-41a9-9d44-63b26a486ec4</t>
+  </si>
+  <si>
+    <t>10fb58ef-6769-42c6-bdf3-9be1963f6b8e</t>
+  </si>
+  <si>
+    <t>AFANTA LAI DEKO AAPAT PARERA</t>
+  </si>
+  <si>
+    <t>42d3c76e-729a-4c29-85ae-c28639fed3e0</t>
+  </si>
+  <si>
+    <t>76564c5a-a00a-427d-93bd-3d3243904019</t>
   </si>
 </sst>
 </file>
@@ -2720,7 +2801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U292"/>
+  <dimension ref="A1:U314"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -20956,6 +21037,1376 @@
         <v>0</v>
       </c>
     </row>
+    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>12106</v>
+      </c>
+      <c r="B293" t="s">
+        <v>778</v>
+      </c>
+      <c r="C293">
+        <v>1207</v>
+      </c>
+      <c r="D293">
+        <v>11102</v>
+      </c>
+      <c r="E293">
+        <v>3</v>
+      </c>
+      <c r="F293">
+        <v>55</v>
+      </c>
+      <c r="G293" t="s">
+        <v>503</v>
+      </c>
+      <c r="H293" t="s">
+        <v>35</v>
+      </c>
+      <c r="I293">
+        <v>14</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
+      <c r="K293" t="s">
+        <v>779</v>
+      </c>
+      <c r="L293">
+        <v>58733</v>
+      </c>
+      <c r="M293">
+        <v>1</v>
+      </c>
+      <c r="N293" s="2">
+        <v>66551</v>
+      </c>
+      <c r="O293">
+        <v>4</v>
+      </c>
+      <c r="P293">
+        <v>200000</v>
+      </c>
+      <c r="Q293">
+        <v>24</v>
+      </c>
+      <c r="R293">
+        <v>2</v>
+      </c>
+      <c r="S293">
+        <v>0</v>
+      </c>
+      <c r="T293">
+        <v>3</v>
+      </c>
+      <c r="U293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>12134</v>
+      </c>
+      <c r="B294" t="s">
+        <v>780</v>
+      </c>
+      <c r="C294">
+        <v>2616</v>
+      </c>
+      <c r="D294">
+        <v>20501</v>
+      </c>
+      <c r="E294">
+        <v>1</v>
+      </c>
+      <c r="F294">
+        <v>54</v>
+      </c>
+      <c r="G294" t="s">
+        <v>503</v>
+      </c>
+      <c r="H294" t="s">
+        <v>35</v>
+      </c>
+      <c r="I294">
+        <v>21</v>
+      </c>
+      <c r="J294">
+        <v>1</v>
+      </c>
+      <c r="K294" t="s">
+        <v>214</v>
+      </c>
+      <c r="L294">
+        <v>58878</v>
+      </c>
+      <c r="M294">
+        <v>1</v>
+      </c>
+      <c r="N294" s="2">
+        <v>66631</v>
+      </c>
+      <c r="O294">
+        <v>4</v>
+      </c>
+      <c r="P294">
+        <v>150000</v>
+      </c>
+      <c r="Q294">
+        <v>22</v>
+      </c>
+      <c r="R294">
+        <v>0</v>
+      </c>
+      <c r="S294">
+        <v>2</v>
+      </c>
+      <c r="T294">
+        <v>2</v>
+      </c>
+      <c r="U294">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>12207</v>
+      </c>
+      <c r="B295" t="s">
+        <v>781</v>
+      </c>
+      <c r="C295">
+        <v>7102</v>
+      </c>
+      <c r="D295">
+        <v>70210</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295">
+        <v>17</v>
+      </c>
+      <c r="G295" t="s">
+        <v>503</v>
+      </c>
+      <c r="H295" t="s">
+        <v>35</v>
+      </c>
+      <c r="I295">
+        <v>73</v>
+      </c>
+      <c r="J295">
+        <v>1</v>
+      </c>
+      <c r="K295" t="s">
+        <v>782</v>
+      </c>
+      <c r="L295">
+        <v>59217</v>
+      </c>
+      <c r="M295">
+        <v>1</v>
+      </c>
+      <c r="N295" s="2">
+        <v>65809</v>
+      </c>
+      <c r="O295">
+        <v>4</v>
+      </c>
+      <c r="P295">
+        <v>200000</v>
+      </c>
+      <c r="Q295">
+        <v>24</v>
+      </c>
+      <c r="R295">
+        <v>24</v>
+      </c>
+      <c r="S295">
+        <v>0</v>
+      </c>
+      <c r="T295">
+        <v>2</v>
+      </c>
+      <c r="U295">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="296" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>12256</v>
+      </c>
+      <c r="B296" t="s">
+        <v>783</v>
+      </c>
+      <c r="C296">
+        <v>7305</v>
+      </c>
+      <c r="D296">
+        <v>70502</v>
+      </c>
+      <c r="E296">
+        <v>5</v>
+      </c>
+      <c r="F296">
+        <v>38</v>
+      </c>
+      <c r="G296" t="s">
+        <v>503</v>
+      </c>
+      <c r="H296" t="s">
+        <v>35</v>
+      </c>
+      <c r="I296">
+        <v>71</v>
+      </c>
+      <c r="J296">
+        <v>1</v>
+      </c>
+      <c r="K296" t="s">
+        <v>766</v>
+      </c>
+      <c r="L296">
+        <v>59452</v>
+      </c>
+      <c r="M296">
+        <v>1</v>
+      </c>
+      <c r="N296" s="2">
+        <v>65876</v>
+      </c>
+      <c r="O296">
+        <v>3</v>
+      </c>
+      <c r="P296">
+        <v>250000</v>
+      </c>
+      <c r="Q296">
+        <v>24</v>
+      </c>
+      <c r="R296">
+        <v>60000</v>
+      </c>
+      <c r="S296" t="s">
+        <v>93</v>
+      </c>
+      <c r="T296">
+        <v>3</v>
+      </c>
+      <c r="U296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>13509</v>
+      </c>
+      <c r="B297" t="s">
+        <v>784</v>
+      </c>
+      <c r="C297">
+        <v>3416</v>
+      </c>
+      <c r="D297">
+        <v>30610</v>
+      </c>
+      <c r="E297">
+        <v>3</v>
+      </c>
+      <c r="F297">
+        <v>44</v>
+      </c>
+      <c r="G297" t="s">
+        <v>503</v>
+      </c>
+      <c r="H297" t="s">
+        <v>35</v>
+      </c>
+      <c r="I297">
+        <v>51</v>
+      </c>
+      <c r="J297">
+        <v>1</v>
+      </c>
+      <c r="K297" t="s">
+        <v>255</v>
+      </c>
+      <c r="L297">
+        <v>5948366</v>
+      </c>
+      <c r="M297">
+        <v>1</v>
+      </c>
+      <c r="N297" s="2">
+        <v>66567</v>
+      </c>
+      <c r="O297">
+        <v>5</v>
+      </c>
+      <c r="P297">
+        <v>100000</v>
+      </c>
+      <c r="Q297">
+        <v>0</v>
+      </c>
+      <c r="R297">
+        <v>0</v>
+      </c>
+      <c r="S297">
+        <v>0</v>
+      </c>
+      <c r="T297">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>13553</v>
+      </c>
+      <c r="B298" t="s">
+        <v>722</v>
+      </c>
+      <c r="C298">
+        <v>3115</v>
+      </c>
+      <c r="D298">
+        <v>31304</v>
+      </c>
+      <c r="E298">
+        <v>4</v>
+      </c>
+      <c r="F298">
+        <v>13</v>
+      </c>
+      <c r="G298" t="s">
+        <v>503</v>
+      </c>
+      <c r="H298" t="s">
+        <v>35</v>
+      </c>
+      <c r="I298">
+        <v>51</v>
+      </c>
+      <c r="J298">
+        <v>1</v>
+      </c>
+      <c r="K298" t="s">
+        <v>723</v>
+      </c>
+      <c r="L298">
+        <v>5948594</v>
+      </c>
+      <c r="M298">
+        <v>2</v>
+      </c>
+      <c r="N298" s="2">
+        <v>62094</v>
+      </c>
+      <c r="O298">
+        <v>4</v>
+      </c>
+      <c r="P298">
+        <v>800000</v>
+      </c>
+      <c r="Q298">
+        <v>24</v>
+      </c>
+      <c r="R298">
+        <v>192000</v>
+      </c>
+      <c r="S298" t="s">
+        <v>724</v>
+      </c>
+      <c r="T298">
+        <v>3</v>
+      </c>
+      <c r="U298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>13553</v>
+      </c>
+      <c r="B299" t="s">
+        <v>722</v>
+      </c>
+      <c r="C299">
+        <v>3115</v>
+      </c>
+      <c r="D299">
+        <v>31304</v>
+      </c>
+      <c r="E299">
+        <v>4</v>
+      </c>
+      <c r="F299">
+        <v>13</v>
+      </c>
+      <c r="G299" t="s">
+        <v>503</v>
+      </c>
+      <c r="H299" t="s">
+        <v>35</v>
+      </c>
+      <c r="I299">
+        <v>51</v>
+      </c>
+      <c r="J299">
+        <v>1</v>
+      </c>
+      <c r="K299" t="s">
+        <v>255</v>
+      </c>
+      <c r="L299">
+        <v>5948594</v>
+      </c>
+      <c r="M299">
+        <v>2</v>
+      </c>
+      <c r="N299" s="2">
+        <v>62125</v>
+      </c>
+      <c r="O299">
+        <v>5</v>
+      </c>
+      <c r="P299">
+        <v>300000</v>
+      </c>
+      <c r="Q299">
+        <v>24</v>
+      </c>
+      <c r="R299">
+        <v>72000</v>
+      </c>
+      <c r="S299" t="s">
+        <v>196</v>
+      </c>
+      <c r="T299">
+        <v>3</v>
+      </c>
+      <c r="U299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>13553</v>
+      </c>
+      <c r="B300" t="s">
+        <v>722</v>
+      </c>
+      <c r="C300">
+        <v>3115</v>
+      </c>
+      <c r="D300">
+        <v>31304</v>
+      </c>
+      <c r="E300">
+        <v>4</v>
+      </c>
+      <c r="F300">
+        <v>13</v>
+      </c>
+      <c r="G300" t="s">
+        <v>503</v>
+      </c>
+      <c r="H300" t="s">
+        <v>35</v>
+      </c>
+      <c r="I300">
+        <v>51</v>
+      </c>
+      <c r="J300">
+        <v>1</v>
+      </c>
+      <c r="K300" t="s">
+        <v>255</v>
+      </c>
+      <c r="L300">
+        <v>5948594</v>
+      </c>
+      <c r="M300">
+        <v>2</v>
+      </c>
+      <c r="N300" s="2">
+        <v>63715</v>
+      </c>
+      <c r="O300">
+        <v>5</v>
+      </c>
+      <c r="P300">
+        <v>1000000</v>
+      </c>
+      <c r="Q300">
+        <v>24</v>
+      </c>
+      <c r="R300">
+        <v>240000</v>
+      </c>
+      <c r="S300" t="s">
+        <v>196</v>
+      </c>
+      <c r="T300">
+        <v>2</v>
+      </c>
+      <c r="U300">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="301" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>13554</v>
+      </c>
+      <c r="B301" t="s">
+        <v>720</v>
+      </c>
+      <c r="C301">
+        <v>3115</v>
+      </c>
+      <c r="D301">
+        <v>31304</v>
+      </c>
+      <c r="E301">
+        <v>4</v>
+      </c>
+      <c r="F301">
+        <v>12</v>
+      </c>
+      <c r="G301" t="s">
+        <v>503</v>
+      </c>
+      <c r="H301" t="s">
+        <v>35</v>
+      </c>
+      <c r="I301">
+        <v>51</v>
+      </c>
+      <c r="J301">
+        <v>1</v>
+      </c>
+      <c r="K301" t="s">
+        <v>721</v>
+      </c>
+      <c r="L301">
+        <v>5948602</v>
+      </c>
+      <c r="M301">
+        <v>1</v>
+      </c>
+      <c r="N301" s="2">
+        <v>64651</v>
+      </c>
+      <c r="O301">
+        <v>4</v>
+      </c>
+      <c r="P301">
+        <v>1200000</v>
+      </c>
+      <c r="Q301">
+        <v>18</v>
+      </c>
+      <c r="S301" t="s">
+        <v>557</v>
+      </c>
+      <c r="T301">
+        <v>2</v>
+      </c>
+      <c r="U301">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="302" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>13572</v>
+      </c>
+      <c r="B302" t="s">
+        <v>785</v>
+      </c>
+      <c r="C302">
+        <v>2106</v>
+      </c>
+      <c r="D302">
+        <v>20514</v>
+      </c>
+      <c r="E302">
+        <v>6</v>
+      </c>
+      <c r="F302">
+        <v>46</v>
+      </c>
+      <c r="G302" t="s">
+        <v>503</v>
+      </c>
+      <c r="H302" t="s">
+        <v>35</v>
+      </c>
+      <c r="I302">
+        <v>24</v>
+      </c>
+      <c r="J302">
+        <v>1</v>
+      </c>
+      <c r="K302" t="s">
+        <v>786</v>
+      </c>
+      <c r="L302">
+        <v>5948691</v>
+      </c>
+      <c r="M302">
+        <v>12</v>
+      </c>
+      <c r="N302" s="2">
+        <v>66540</v>
+      </c>
+      <c r="O302">
+        <v>4</v>
+      </c>
+      <c r="P302">
+        <v>150000</v>
+      </c>
+      <c r="Q302">
+        <v>24</v>
+      </c>
+      <c r="R302">
+        <v>24</v>
+      </c>
+      <c r="S302">
+        <v>2</v>
+      </c>
+      <c r="T302">
+        <v>3</v>
+      </c>
+      <c r="U302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>13573</v>
+      </c>
+      <c r="B303" t="s">
+        <v>787</v>
+      </c>
+      <c r="C303">
+        <v>2206</v>
+      </c>
+      <c r="D303">
+        <v>20514</v>
+      </c>
+      <c r="E303">
+        <v>6</v>
+      </c>
+      <c r="F303">
+        <v>47</v>
+      </c>
+      <c r="G303" t="s">
+        <v>503</v>
+      </c>
+      <c r="H303" t="s">
+        <v>35</v>
+      </c>
+      <c r="I303">
+        <v>24</v>
+      </c>
+      <c r="J303">
+        <v>1</v>
+      </c>
+      <c r="K303" t="s">
+        <v>788</v>
+      </c>
+      <c r="L303">
+        <v>5948692</v>
+      </c>
+      <c r="M303">
+        <v>1</v>
+      </c>
+      <c r="N303" s="2">
+        <v>66236</v>
+      </c>
+      <c r="O303">
+        <v>4</v>
+      </c>
+      <c r="P303">
+        <v>200000</v>
+      </c>
+      <c r="Q303">
+        <v>24</v>
+      </c>
+      <c r="R303">
+        <v>0</v>
+      </c>
+      <c r="S303">
+        <v>1</v>
+      </c>
+      <c r="T303">
+        <v>3</v>
+      </c>
+      <c r="U303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>13575</v>
+      </c>
+      <c r="B304" t="s">
+        <v>789</v>
+      </c>
+      <c r="C304">
+        <v>2106</v>
+      </c>
+      <c r="D304">
+        <v>20514</v>
+      </c>
+      <c r="E304">
+        <v>2</v>
+      </c>
+      <c r="F304">
+        <v>49</v>
+      </c>
+      <c r="G304" t="s">
+        <v>503</v>
+      </c>
+      <c r="H304" t="s">
+        <v>35</v>
+      </c>
+      <c r="I304">
+        <v>24</v>
+      </c>
+      <c r="J304">
+        <v>1</v>
+      </c>
+      <c r="K304" t="s">
+        <v>790</v>
+      </c>
+      <c r="L304">
+        <v>5948706</v>
+      </c>
+      <c r="M304">
+        <v>1</v>
+      </c>
+      <c r="N304" s="2">
+        <v>64867</v>
+      </c>
+      <c r="O304">
+        <v>4</v>
+      </c>
+      <c r="P304">
+        <v>100000</v>
+      </c>
+      <c r="Q304">
+        <v>24</v>
+      </c>
+      <c r="R304">
+        <v>0</v>
+      </c>
+      <c r="S304">
+        <v>1</v>
+      </c>
+      <c r="T304">
+        <v>2</v>
+      </c>
+      <c r="U304">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="305" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>13578</v>
+      </c>
+      <c r="B305" t="s">
+        <v>791</v>
+      </c>
+      <c r="C305">
+        <v>2206</v>
+      </c>
+      <c r="D305">
+        <v>20514</v>
+      </c>
+      <c r="E305">
+        <v>2</v>
+      </c>
+      <c r="F305">
+        <v>52</v>
+      </c>
+      <c r="G305" t="s">
+        <v>503</v>
+      </c>
+      <c r="H305" t="s">
+        <v>35</v>
+      </c>
+      <c r="I305">
+        <v>24</v>
+      </c>
+      <c r="J305">
+        <v>1</v>
+      </c>
+      <c r="K305" t="s">
+        <v>792</v>
+      </c>
+      <c r="L305">
+        <v>5948721</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305" s="2">
+        <v>64836</v>
+      </c>
+      <c r="O305">
+        <v>4</v>
+      </c>
+      <c r="P305">
+        <v>360000</v>
+      </c>
+      <c r="Q305">
+        <v>24</v>
+      </c>
+      <c r="R305">
+        <v>0</v>
+      </c>
+      <c r="S305">
+        <v>4</v>
+      </c>
+      <c r="T305">
+        <v>2</v>
+      </c>
+      <c r="U305">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="306" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>13589</v>
+      </c>
+      <c r="B306" t="s">
+        <v>793</v>
+      </c>
+      <c r="C306">
+        <v>3504</v>
+      </c>
+      <c r="D306">
+        <v>30602</v>
+      </c>
+      <c r="E306">
+        <v>6</v>
+      </c>
+      <c r="F306">
+        <v>86</v>
+      </c>
+      <c r="G306" t="s">
+        <v>503</v>
+      </c>
+      <c r="H306" t="s">
+        <v>35</v>
+      </c>
+      <c r="I306">
+        <v>93</v>
+      </c>
+      <c r="J306">
+        <v>1</v>
+      </c>
+      <c r="K306" t="s">
+        <v>794</v>
+      </c>
+      <c r="L306">
+        <v>5948774</v>
+      </c>
+      <c r="M306">
+        <v>1</v>
+      </c>
+      <c r="N306" s="2">
+        <v>66481</v>
+      </c>
+      <c r="O306">
+        <v>4</v>
+      </c>
+      <c r="P306">
+        <v>150000</v>
+      </c>
+      <c r="Q306">
+        <v>24</v>
+      </c>
+      <c r="R306">
+        <v>0</v>
+      </c>
+      <c r="S306">
+        <v>2</v>
+      </c>
+      <c r="T306">
+        <v>2</v>
+      </c>
+      <c r="U306">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="307" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>13601</v>
+      </c>
+      <c r="B307" t="s">
+        <v>795</v>
+      </c>
+      <c r="C307">
+        <v>3603</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>67</v>
+      </c>
+      <c r="G307" t="s">
+        <v>503</v>
+      </c>
+      <c r="H307" t="s">
+        <v>35</v>
+      </c>
+      <c r="I307">
+        <v>11</v>
+      </c>
+      <c r="J307">
+        <v>1</v>
+      </c>
+      <c r="K307" t="s">
+        <v>796</v>
+      </c>
+      <c r="L307">
+        <v>5948829</v>
+      </c>
+      <c r="M307">
+        <v>1</v>
+      </c>
+      <c r="N307" s="2">
+        <v>65471</v>
+      </c>
+      <c r="O307">
+        <v>3</v>
+      </c>
+      <c r="P307">
+        <v>250000</v>
+      </c>
+      <c r="Q307">
+        <v>12</v>
+      </c>
+      <c r="R307">
+        <v>0</v>
+      </c>
+      <c r="T307">
+        <v>3</v>
+      </c>
+      <c r="U307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>13601</v>
+      </c>
+      <c r="B308" t="s">
+        <v>795</v>
+      </c>
+      <c r="C308">
+        <v>3603</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+      <c r="F308">
+        <v>67</v>
+      </c>
+      <c r="G308" t="s">
+        <v>503</v>
+      </c>
+      <c r="H308" t="s">
+        <v>35</v>
+      </c>
+      <c r="I308">
+        <v>11</v>
+      </c>
+      <c r="J308">
+        <v>1</v>
+      </c>
+      <c r="K308" t="s">
+        <v>749</v>
+      </c>
+      <c r="L308">
+        <v>5948829</v>
+      </c>
+      <c r="M308">
+        <v>1</v>
+      </c>
+      <c r="N308" s="2">
+        <v>66118</v>
+      </c>
+      <c r="O308">
+        <v>5</v>
+      </c>
+      <c r="P308">
+        <v>140000</v>
+      </c>
+      <c r="Q308">
+        <v>0</v>
+      </c>
+      <c r="R308">
+        <v>0</v>
+      </c>
+      <c r="S308">
+        <v>2</v>
+      </c>
+      <c r="T308">
+        <v>3</v>
+      </c>
+      <c r="U308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>13603</v>
+      </c>
+      <c r="B309" t="s">
+        <v>797</v>
+      </c>
+      <c r="C309">
+        <v>3676</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>69</v>
+      </c>
+      <c r="G309" t="s">
+        <v>503</v>
+      </c>
+      <c r="H309" t="s">
+        <v>35</v>
+      </c>
+      <c r="I309">
+        <v>11</v>
+      </c>
+      <c r="J309">
+        <v>1</v>
+      </c>
+      <c r="K309" t="s">
+        <v>749</v>
+      </c>
+      <c r="L309">
+        <v>5948837</v>
+      </c>
+      <c r="M309">
+        <v>2</v>
+      </c>
+      <c r="N309" s="2">
+        <v>66297</v>
+      </c>
+      <c r="O309">
+        <v>5</v>
+      </c>
+      <c r="P309">
+        <v>200000</v>
+      </c>
+      <c r="Q309">
+        <v>12</v>
+      </c>
+      <c r="R309">
+        <v>0</v>
+      </c>
+      <c r="S309" t="s">
+        <v>294</v>
+      </c>
+      <c r="T309">
+        <v>3</v>
+      </c>
+      <c r="U309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>13647</v>
+      </c>
+      <c r="B310" t="s">
+        <v>798</v>
+      </c>
+      <c r="C310">
+        <v>6310</v>
+      </c>
+      <c r="D310">
+        <v>61006</v>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+      <c r="F310">
+        <v>41</v>
+      </c>
+      <c r="G310" t="s">
+        <v>503</v>
+      </c>
+      <c r="H310" t="s">
+        <v>35</v>
+      </c>
+      <c r="I310">
+        <v>71</v>
+      </c>
+      <c r="J310">
+        <v>1</v>
+      </c>
+      <c r="K310" t="s">
+        <v>799</v>
+      </c>
+      <c r="L310">
+        <v>5949020</v>
+      </c>
+      <c r="M310">
+        <v>1</v>
+      </c>
+      <c r="N310" s="2">
+        <v>66364</v>
+      </c>
+      <c r="O310">
+        <v>4</v>
+      </c>
+      <c r="P310">
+        <v>100000</v>
+      </c>
+      <c r="Q310">
+        <v>24</v>
+      </c>
+      <c r="R310">
+        <v>24000</v>
+      </c>
+      <c r="S310" t="s">
+        <v>93</v>
+      </c>
+      <c r="T310">
+        <v>2</v>
+      </c>
+      <c r="U310">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="311" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>13721</v>
+      </c>
+      <c r="B311" t="s">
+        <v>800</v>
+      </c>
+      <c r="C311">
+        <v>6408</v>
+      </c>
+      <c r="D311">
+        <v>60608</v>
+      </c>
+      <c r="E311">
+        <v>1</v>
+      </c>
+      <c r="F311">
+        <v>50</v>
+      </c>
+      <c r="G311" t="s">
+        <v>503</v>
+      </c>
+      <c r="H311" t="s">
+        <v>35</v>
+      </c>
+      <c r="I311">
+        <v>71</v>
+      </c>
+      <c r="J311">
+        <v>1</v>
+      </c>
+      <c r="K311" t="s">
+        <v>766</v>
+      </c>
+      <c r="L311">
+        <v>5949340</v>
+      </c>
+      <c r="M311">
+        <v>1</v>
+      </c>
+      <c r="N311" s="2">
+        <v>66209</v>
+      </c>
+      <c r="O311">
+        <v>4</v>
+      </c>
+      <c r="P311">
+        <v>100000</v>
+      </c>
+      <c r="Q311">
+        <v>24</v>
+      </c>
+      <c r="R311">
+        <v>24000</v>
+      </c>
+      <c r="S311" t="s">
+        <v>764</v>
+      </c>
+      <c r="T311">
+        <v>3</v>
+      </c>
+      <c r="U311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>13743</v>
+      </c>
+      <c r="B312" t="s">
+        <v>801</v>
+      </c>
+      <c r="C312">
+        <v>3542</v>
+      </c>
+      <c r="D312">
+        <v>30802</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>44</v>
+      </c>
+      <c r="G312" t="s">
+        <v>503</v>
+      </c>
+      <c r="H312" t="s">
+        <v>35</v>
+      </c>
+      <c r="I312">
+        <v>56</v>
+      </c>
+      <c r="J312">
+        <v>1</v>
+      </c>
+      <c r="K312" t="s">
+        <v>802</v>
+      </c>
+      <c r="L312">
+        <v>5949430</v>
+      </c>
+      <c r="M312">
+        <v>3</v>
+      </c>
+      <c r="O312">
+        <v>4</v>
+      </c>
+      <c r="P312">
+        <v>800000</v>
+      </c>
+      <c r="Q312">
+        <v>0</v>
+      </c>
+      <c r="R312">
+        <v>0</v>
+      </c>
+      <c r="S312">
+        <v>0</v>
+      </c>
+      <c r="T312">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>13779</v>
+      </c>
+      <c r="B313" t="s">
+        <v>803</v>
+      </c>
+      <c r="C313">
+        <v>6316</v>
+      </c>
+      <c r="D313">
+        <v>61006</v>
+      </c>
+      <c r="E313">
+        <v>4</v>
+      </c>
+      <c r="F313">
+        <v>46</v>
+      </c>
+      <c r="G313" t="s">
+        <v>503</v>
+      </c>
+      <c r="H313" t="s">
+        <v>35</v>
+      </c>
+      <c r="I313">
+        <v>71</v>
+      </c>
+      <c r="J313">
+        <v>1</v>
+      </c>
+      <c r="K313" t="s">
+        <v>255</v>
+      </c>
+      <c r="L313">
+        <v>5949559</v>
+      </c>
+      <c r="M313">
+        <v>1</v>
+      </c>
+      <c r="N313" s="2">
+        <v>65876</v>
+      </c>
+      <c r="O313">
+        <v>4</v>
+      </c>
+      <c r="P313">
+        <v>200000</v>
+      </c>
+      <c r="Q313">
+        <v>24</v>
+      </c>
+      <c r="R313">
+        <v>48000</v>
+      </c>
+      <c r="S313" t="s">
+        <v>93</v>
+      </c>
+      <c r="T313">
+        <v>2</v>
+      </c>
+      <c r="U313">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="314" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>14006</v>
+      </c>
+      <c r="B314" t="s">
+        <v>804</v>
+      </c>
+      <c r="C314">
+        <v>3646</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>53</v>
+      </c>
+      <c r="G314" t="s">
+        <v>503</v>
+      </c>
+      <c r="H314" t="s">
+        <v>35</v>
+      </c>
+      <c r="I314">
+        <v>58</v>
+      </c>
+      <c r="J314">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataset/Part 11_2_ Lending and Outstanding Loans.xlsx
+++ b/dataset/Part 11_2_ Lending and Outstanding Loans.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-28-today (1)\2025-11-28-today\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-12-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFA04AF-B0B8-49F6-B9B0-D5D14941D42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EB96F1-EA1C-41E9-B4C8-84D10ED103E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="923">
   <si>
     <t>ID</t>
   </si>
@@ -2176,217 +2176,505 @@
     <t>1 BARSH VITRA</t>
   </si>
   <si>
+    <t>1cc6d87b-1221-4927-ab82-c9d38cf5cc6e</t>
+  </si>
+  <si>
+    <t>MONEY HAS BEEN GIVEN TO FRIEND</t>
+  </si>
+  <si>
+    <t>2068/5/9</t>
+  </si>
+  <si>
+    <t>CAN GIVE WHEN AVAILABLE</t>
+  </si>
+  <si>
     <t>3887ae8e-56b6-4062-b360-b1dcd5dc79d6</t>
   </si>
   <si>
+    <t>2081/7/28</t>
+  </si>
+  <si>
     <t>b6f62bd0-72a8-4b89-83e7-c344c26dbc19</t>
   </si>
   <si>
+    <t>2081/7/30</t>
+  </si>
+  <si>
     <t>JAHILE SAKINX</t>
   </si>
   <si>
     <t>193c4bfd-b476-44d0-93c0-b8ca34d8e69e</t>
   </si>
   <si>
+    <t>2076/6/2</t>
+  </si>
+  <si>
     <t>e67ce574-428d-42b6-b54c-09a36cfe7f54</t>
   </si>
   <si>
     <t>BIRAMI JACH KO LAGI XIMEKI LAI</t>
   </si>
   <si>
+    <t>2078/6/2</t>
+  </si>
+  <si>
+    <t>1b161143-dbb1-4f3b-b07f-05936f5ce755</t>
+  </si>
+  <si>
+    <t>XORA BIDESH  PATHAUNW KO LAGI</t>
+  </si>
+  <si>
+    <t>5a56b014-dc70-4061-b579-f4a5705a2030</t>
+  </si>
+  <si>
+    <t>b5e64397-6e9e-40ae-b8d5-96e9255760c4</t>
+  </si>
+  <si>
+    <t>INTEREST</t>
+  </si>
+  <si>
+    <t>2080/4/9</t>
+  </si>
+  <si>
+    <t>6bca216b-e79f-4b5b-80e6-f73284dd3b56</t>
+  </si>
+  <si>
+    <t>2081/6/9</t>
+  </si>
+  <si>
+    <t>b3b57498-6423-459c-992d-2c349bb3d0dc</t>
+  </si>
+  <si>
+    <t>c4bd0770-0d8c-4d53-ade6-a85947dd6073</t>
+  </si>
+  <si>
+    <t>2078/4/5</t>
+  </si>
+  <si>
+    <t>0cd46ce2-b6f1-44ea-8289-926c5a818471</t>
+  </si>
+  <si>
+    <t>CHHIMEKI LAI BIDESH JANA KO LAGI</t>
+  </si>
+  <si>
+    <t>38e316e0-eff7-4fdd-9971-133c46a26264</t>
+  </si>
+  <si>
+    <t>AAMAJU LAI GHAR BANAUDA DIYAKO</t>
+  </si>
+  <si>
+    <t>2079/8/2</t>
+  </si>
+  <si>
+    <t>JAHILE SAKX TAHILE</t>
+  </si>
+  <si>
+    <t>DIDI KO XORA BIDESH PATHAUNA</t>
+  </si>
+  <si>
+    <t>2082/1/2</t>
+  </si>
+  <si>
+    <t>JAHILE HUNX</t>
+  </si>
+  <si>
+    <t>b69e1a3d-6b54-4639-b7ff-0d7b99e297cf</t>
+  </si>
+  <si>
+    <t>2081/3/3</t>
+  </si>
+  <si>
+    <t>2081/11/1</t>
+  </si>
+  <si>
+    <t>2082/5/1</t>
+  </si>
+  <si>
+    <t>a2c587c5-6357-4455-8518-2961125a430b</t>
+  </si>
+  <si>
+    <t>BAINILAI BAHIRA PATHAUNA</t>
+  </si>
+  <si>
+    <t>2081/11/23</t>
+  </si>
+  <si>
+    <t>RIN TIRNA LAI</t>
+  </si>
+  <si>
+    <t>2081/5/13</t>
+  </si>
+  <si>
+    <t>BAIDSHIK ROJGAAR</t>
+  </si>
+  <si>
+    <t>9362ff65-4ee6-4764-9ac4-e5a5fa7b6586</t>
+  </si>
+  <si>
+    <t>2081/7/8</t>
+  </si>
+  <si>
+    <t>eaecab1e-c3c9-4e1a-8a70-496a669d0ade</t>
+  </si>
+  <si>
+    <t>CHHORI KO BIHE</t>
+  </si>
+  <si>
+    <t>2077/8/7</t>
+  </si>
+  <si>
+    <t>9e3fdc92-410c-460f-ba32-c4503536014e</t>
+  </si>
+  <si>
+    <t>PURAN LAGAUNA DIYEKO</t>
+  </si>
+  <si>
+    <t>2067/8/3</t>
+  </si>
+  <si>
+    <t>dab1d6fa-903a-4b1c-907b-2791805911fa</t>
+  </si>
+  <si>
+    <t>BIRAMI KO LAGI</t>
+  </si>
+  <si>
+    <t>2082/5/4</t>
+  </si>
+  <si>
+    <t>310e82d0-6fdc-41b2-9947-88519bb841cd</t>
+  </si>
+  <si>
+    <t>2078/1/2</t>
+  </si>
+  <si>
+    <t>f4192c28-aea9-4c73-ba57-45ec56d598f2</t>
+  </si>
+  <si>
+    <t>BAIDESIK YATRA</t>
+  </si>
+  <si>
+    <t>3bd809ac-6aae-442c-9057-e349d18822e4</t>
+  </si>
+  <si>
+    <t>BYAPAR</t>
+  </si>
+  <si>
+    <t>1c4b61da-32e4-4c65-877e-9d4cd943b81f</t>
+  </si>
+  <si>
+    <t>2081/12/1</t>
+  </si>
+  <si>
+    <t>f1b4db85-846c-42d3-b1c7-7bd644e8b4d9</t>
+  </si>
+  <si>
+    <t>BAIDESIK</t>
+  </si>
+  <si>
+    <t>952f0c33-e251-4cef-9557-3867db9ff3e6</t>
+  </si>
+  <si>
+    <t>2080/4/1</t>
+  </si>
+  <si>
+    <t>3aa9d2cc-03ae-4ccc-9ccd-776b35db43a7</t>
+  </si>
+  <si>
+    <t>2080/12/10</t>
+  </si>
+  <si>
+    <t>25650718-d519-456b-b84c-8bb6b7cad676</t>
+  </si>
+  <si>
+    <t>2080/10/20</t>
+  </si>
+  <si>
+    <t>b00c10e7-78bf-4d63-9de7-050de14db1bf</t>
+  </si>
+  <si>
+    <t>2075/4/23</t>
+  </si>
+  <si>
+    <t>d8009030-1722-4e33-9ac6-c7786e7f0472</t>
+  </si>
+  <si>
+    <t>JAHILE GARDA NI HUNX</t>
+  </si>
+  <si>
+    <t>33f6daf6-fa00-415e-9820-80f789a7dd5c</t>
+  </si>
+  <si>
+    <t>2075/2/16</t>
+  </si>
+  <si>
+    <t>RELATIVES PROMISED TO PAY ON TIME,BUT NO ONE HAS PAID YET.</t>
+  </si>
+  <si>
+    <t>aa4dc137-e941-4837-ab35-eaf47bdd2a64</t>
+  </si>
+  <si>
+    <t>2078/4/3</t>
+  </si>
+  <si>
+    <t>JAHILE SAKCHHA</t>
+  </si>
+  <si>
+    <t>669f0633-444a-408e-b356-a34e7bdc4aab</t>
+  </si>
+  <si>
+    <t>XEMIKILAI BIRAMI HUDA</t>
+  </si>
+  <si>
+    <t>2077/4/5</t>
+  </si>
+  <si>
+    <t>1 MAHINA BHITRA MA</t>
+  </si>
+  <si>
+    <t>56453207-4d3d-4ebd-923e-df5005f48f32</t>
+  </si>
+  <si>
+    <t>GAU KO VAUJU LAI</t>
+  </si>
+  <si>
+    <t>2080/3/1</t>
+  </si>
+  <si>
+    <t>JAHILE SAKCH</t>
+  </si>
+  <si>
+    <t>279e7337-4bb3-4954-9559-97bd14925fb9</t>
+  </si>
+  <si>
+    <t>MAITI GHAR TIRA</t>
+  </si>
+  <si>
+    <t>2078/4/2</t>
+  </si>
+  <si>
+    <t>XIMIKI LAI BIDESH JAN KO LAGI</t>
+  </si>
+  <si>
+    <t>2081/8/3</t>
+  </si>
+  <si>
+    <t>0d33c29d-c199-4470-b682-1637a95fd13f</t>
+  </si>
+  <si>
+    <t>3 YEAR</t>
+  </si>
+  <si>
+    <t>5ff8e763-c6b4-4f22-a85e-ad5a606ed179</t>
+  </si>
+  <si>
+    <t>GHARAISHI KHARCHA KO LAGI</t>
+  </si>
+  <si>
+    <t>2081/5/19</t>
+  </si>
+  <si>
+    <t>dcf4148d-facc-4cad-848b-d8f3676f9603</t>
+  </si>
+  <si>
+    <t>0251dd88-0808-4850-af25-895508d530e9</t>
+  </si>
+  <si>
+    <t>AUSADHI UPCHARKO LAGI</t>
+  </si>
+  <si>
+    <t>6b128734-48e4-4d59-b538-9c76a75585ef</t>
+  </si>
+  <si>
+    <t>2081/6/6</t>
+  </si>
+  <si>
+    <t>7d0e35ea-15d2-4e80-8dd3-27dede3247de</t>
+  </si>
+  <si>
+    <t>BIDESHJANA VANERA</t>
+  </si>
+  <si>
+    <t>2081/4/4</t>
+  </si>
+  <si>
+    <t>c71f4fa4-740b-4d00-ada8-5e5a0a81512e</t>
+  </si>
+  <si>
+    <t>BUSINESS GARNA</t>
+  </si>
+  <si>
+    <t>2082/2/5</t>
+  </si>
+  <si>
+    <t>98afab77-920a-476f-9ab6-cb8bb69dfd94</t>
+  </si>
+  <si>
+    <t>GHAR BANAUNA LAGI</t>
+  </si>
+  <si>
+    <t>2081/8/25</t>
+  </si>
+  <si>
+    <t>2079/10/1</t>
+  </si>
+  <si>
+    <t>278928d7-c501-4bd4-ab21-97071e3b55ac</t>
+  </si>
+  <si>
+    <t>GHARBAARI PRAYOJAN KO LAGI</t>
+  </si>
+  <si>
+    <t>44df9173-8c2d-45da-8553-5748936c0dce</t>
+  </si>
+  <si>
+    <t>4293996c-58df-4fcb-9ce7-09bbadab789c</t>
+  </si>
+  <si>
+    <t>GHAR KHARCHA KO LAGI DEKO</t>
+  </si>
+  <si>
+    <t>2082/3/16</t>
+  </si>
+  <si>
+    <t>bcec5310-7a57-4aa0-b614-c2c00f41732d</t>
+  </si>
+  <si>
+    <t>2082/6/4</t>
+  </si>
+  <si>
+    <t>c2d301a1-3cae-446e-850c-8670132903d4</t>
+  </si>
+  <si>
+    <t>CHHIMEKI LAI</t>
+  </si>
+  <si>
+    <t>c1481fb3-ddd3-41a0-aafe-f48020887796</t>
+  </si>
+  <si>
+    <t>2078/4/6</t>
+  </si>
+  <si>
+    <t>a7905352-5908-4703-bfa6-128a1b698ee0</t>
+  </si>
+  <si>
+    <t>CHEKO</t>
+  </si>
+  <si>
+    <t>3d83cc67-1308-4834-b27d-4e687936f59c</t>
+  </si>
+  <si>
+    <t>2080/5/10</t>
+  </si>
+  <si>
+    <t>3d6213ff-b887-4118-858b-eadd4c6d9eb9</t>
+  </si>
+  <si>
+    <t>2081/3/14</t>
+  </si>
+  <si>
+    <t>78454e73-fd52-4b7e-85f6-0d335c31739c</t>
+  </si>
+  <si>
+    <t>NATINI LAI BIDESH PATHAUN DIYA KO</t>
+  </si>
+  <si>
+    <t>2081/4/20</t>
+  </si>
+  <si>
+    <t>01b1a760-8903-4a3e-997e-69b5c00b6eeb</t>
+  </si>
+  <si>
+    <t>60d7cb31-de3c-4a8e-b006-1054b52bf74f</t>
+  </si>
+  <si>
+    <t>2080/5/17</t>
+  </si>
+  <si>
+    <t>e45d919b-33c6-455e-bd5c-39a66e0712b5</t>
+  </si>
+  <si>
+    <t>STUDY</t>
+  </si>
+  <si>
+    <t>2080/2/17</t>
+  </si>
+  <si>
+    <t>cb7760ab-7f51-4eb6-8175-d75e468e3047</t>
+  </si>
+  <si>
+    <t>EDUCATIONAL</t>
+  </si>
+  <si>
+    <t>2082/3/5</t>
+  </si>
+  <si>
+    <t>e6acb156-dc10-4337-824b-b505cc3faa48</t>
+  </si>
+  <si>
+    <t>2082/2/10</t>
+  </si>
+  <si>
+    <t>9655a367-c3ca-45b3-ae1c-dd991cd80c36</t>
+  </si>
+  <si>
+    <t>BIDESA JANA KO LAGI</t>
+  </si>
+  <si>
+    <t>2082/8/7</t>
+  </si>
+  <si>
+    <t>aa23642e-a6b1-4acf-a16d-d214679fa5dc</t>
+  </si>
+  <si>
+    <t>BUSINESS KO LAGI</t>
+  </si>
+  <si>
+    <t>1 MONTH MA</t>
+  </si>
+  <si>
+    <t>2073/5/10</t>
+  </si>
+  <si>
+    <t>1 BARSA</t>
+  </si>
+  <si>
+    <t>18f347b3-0726-44fd-b3af-c76d39873cb2</t>
+  </si>
+  <si>
+    <t>SATHI</t>
+  </si>
+  <si>
+    <t>ec790fbe-7ec5-4a6b-a044-63256ae525e5</t>
+  </si>
+  <si>
+    <t>2082/4/1</t>
+  </si>
+  <si>
+    <t>bc5d3991-b39c-4923-b8c8-928ff6a0a825</t>
+  </si>
+  <si>
+    <t>UDDHOG CHALAUNE</t>
+  </si>
+  <si>
+    <t>2070/1/1</t>
+  </si>
+  <si>
+    <t>3YEARS</t>
+  </si>
+  <si>
+    <t>2070/2/1</t>
+  </si>
+  <si>
+    <t>2074/6/10</t>
+  </si>
+  <si>
     <t>cd2c84ce-f139-46c4-b537-88a54c79ebb7</t>
   </si>
   <si>
     <t>BIDESH JANE KO LAGI DEYAKO</t>
   </si>
   <si>
-    <t>bc5d3991-b39c-4923-b8c8-928ff6a0a825</t>
-  </si>
-  <si>
-    <t>UDDHOG CHALAUNE</t>
-  </si>
-  <si>
-    <t>3YEARS</t>
-  </si>
-  <si>
-    <t>1b161143-dbb1-4f3b-b07f-05936f5ce755</t>
-  </si>
-  <si>
-    <t>XORA BIDESH  PATHAUNW KO LAGI</t>
-  </si>
-  <si>
-    <t>5a56b014-dc70-4061-b579-f4a5705a2030</t>
-  </si>
-  <si>
-    <t>b5e64397-6e9e-40ae-b8d5-96e9255760c4</t>
-  </si>
-  <si>
-    <t>INTEREST</t>
-  </si>
-  <si>
-    <t>0cd46ce2-b6f1-44ea-8289-926c5a818471</t>
-  </si>
-  <si>
-    <t>CHHIMEKI LAI BIDESH JANA KO LAGI</t>
-  </si>
-  <si>
-    <t>38e316e0-eff7-4fdd-9971-133c46a26264</t>
-  </si>
-  <si>
-    <t>AAMAJU LAI GHAR BANAUDA DIYAKO</t>
-  </si>
-  <si>
-    <t>JAHILE SAKX TAHILE</t>
-  </si>
-  <si>
-    <t>DIDI KO XORA BIDESH PATHAUNA</t>
-  </si>
-  <si>
-    <t>JAHILE HUNX</t>
-  </si>
-  <si>
-    <t>b69e1a3d-6b54-4639-b7ff-0d7b99e297cf</t>
-  </si>
-  <si>
-    <t>a2c587c5-6357-4455-8518-2961125a430b</t>
-  </si>
-  <si>
-    <t>BAINILAI BAHIRA PATHAUNA</t>
-  </si>
-  <si>
-    <t>RIN TIRNA LAI</t>
-  </si>
-  <si>
-    <t>BAIDSHIK ROJGAAR</t>
-  </si>
-  <si>
-    <t>9362ff65-4ee6-4764-9ac4-e5a5fa7b6586</t>
-  </si>
-  <si>
-    <t>f4192c28-aea9-4c73-ba57-45ec56d598f2</t>
-  </si>
-  <si>
-    <t>BAIDESIK YATRA</t>
-  </si>
-  <si>
-    <t>3bd809ac-6aae-442c-9057-e349d18822e4</t>
-  </si>
-  <si>
-    <t>BYAPAR</t>
-  </si>
-  <si>
-    <t>1c4b61da-32e4-4c65-877e-9d4cd943b81f</t>
-  </si>
-  <si>
-    <t>f1b4db85-846c-42d3-b1c7-7bd644e8b4d9</t>
-  </si>
-  <si>
-    <t>BAIDESIK</t>
-  </si>
-  <si>
-    <t>952f0c33-e251-4cef-9557-3867db9ff3e6</t>
-  </si>
-  <si>
-    <t>3aa9d2cc-03ae-4ccc-9ccd-776b35db43a7</t>
-  </si>
-  <si>
-    <t>aa4dc137-e941-4837-ab35-eaf47bdd2a64</t>
-  </si>
-  <si>
-    <t>JAHILE SAKCHHA</t>
-  </si>
-  <si>
-    <t>669f0633-444a-408e-b356-a34e7bdc4aab</t>
-  </si>
-  <si>
-    <t>XEMIKILAI BIRAMI HUDA</t>
-  </si>
-  <si>
-    <t>1 MAHINA BHITRA MA</t>
-  </si>
-  <si>
-    <t>56453207-4d3d-4ebd-923e-df5005f48f32</t>
-  </si>
-  <si>
-    <t>GAU KO VAUJU LAI</t>
-  </si>
-  <si>
-    <t>JAHILE SAKCH</t>
-  </si>
-  <si>
-    <t>279e7337-4bb3-4954-9559-97bd14925fb9</t>
-  </si>
-  <si>
-    <t>MAITI GHAR TIRA</t>
-  </si>
-  <si>
-    <t>XIMIKI LAI BIDESH JAN KO LAGI</t>
-  </si>
-  <si>
-    <t>0d33c29d-c199-4470-b682-1637a95fd13f</t>
-  </si>
-  <si>
-    <t>3 YEAR</t>
-  </si>
-  <si>
-    <t>5ff8e763-c6b4-4f22-a85e-ad5a606ed179</t>
-  </si>
-  <si>
-    <t>GHARAISHI KHARCHA KO LAGI</t>
-  </si>
-  <si>
-    <t>0251dd88-0808-4850-af25-895508d530e9</t>
-  </si>
-  <si>
-    <t>AUSADHI UPCHARKO LAGI</t>
-  </si>
-  <si>
-    <t>6b128734-48e4-4d59-b538-9c76a75585ef</t>
-  </si>
-  <si>
-    <t>7d0e35ea-15d2-4e80-8dd3-27dede3247de</t>
-  </si>
-  <si>
-    <t>BIDESHJANA VANERA</t>
-  </si>
-  <si>
-    <t>c71f4fa4-740b-4d00-ada8-5e5a0a81512e</t>
-  </si>
-  <si>
-    <t>BUSINESS GARNA</t>
-  </si>
-  <si>
-    <t>98afab77-920a-476f-9ab6-cb8bb69dfd94</t>
-  </si>
-  <si>
-    <t>GHAR BANAUNA LAGI</t>
-  </si>
-  <si>
-    <t>278928d7-c501-4bd4-ab21-97071e3b55ac</t>
-  </si>
-  <si>
-    <t>GHARBAARI PRAYOJAN KO LAGI</t>
-  </si>
-  <si>
-    <t>4293996c-58df-4fcb-9ce7-09bbadab789c</t>
-  </si>
-  <si>
-    <t>GHAR KHARCHA KO LAGI DEKO</t>
-  </si>
-  <si>
-    <t>bcec5310-7a57-4aa0-b614-c2c00f41732d</t>
-  </si>
-  <si>
-    <t>c2d301a1-3cae-446e-850c-8670132903d4</t>
-  </si>
-  <si>
-    <t>CHHIMEKI LAI</t>
-  </si>
-  <si>
-    <t>3d83cc67-1308-4834-b27d-4e687936f59c</t>
-  </si>
-  <si>
-    <t>ec790fbe-7ec5-4a6b-a044-63256ae525e5</t>
+    <t>2077/1/1</t>
   </si>
   <si>
     <t>4e38e751-154c-4c2d-8eb9-3995dd4293ae</t>
@@ -2401,18 +2689,27 @@
     <t>GHAR BANAUNA LAI</t>
   </si>
   <si>
+    <t>2081/5/5</t>
+  </si>
+  <si>
     <t>58499b69-d22b-4d9e-8246-5a42ac197e8b</t>
   </si>
   <si>
     <t>KAJKRIYA GARNALAI</t>
   </si>
   <si>
+    <t>2077/8/5</t>
+  </si>
+  <si>
     <t>196d4f18-28bc-4994-aa48-ea4085fd66cd</t>
   </si>
   <si>
     <t>BIDESHA JANA KO LAGI</t>
   </si>
   <si>
+    <t>2077/7/5</t>
+  </si>
+  <si>
     <t>c6c0d4b5-5fe9-48e6-bbcd-ce96d947fef5</t>
   </si>
   <si>
@@ -2425,9 +2722,15 @@
     <t>DOJER KINNA</t>
   </si>
   <si>
+    <t>2081/1/7</t>
+  </si>
+  <si>
     <t>f540c823-0a38-45f7-a2ab-f89ed4b46343</t>
   </si>
   <si>
+    <t>2081/7/5</t>
+  </si>
+  <si>
     <t>2a844aeb-4585-4e4d-b317-1294ddfe704c</t>
   </si>
   <si>
@@ -2437,6 +2740,9 @@
     <t>7203e045-085b-41a9-9d44-63b26a486ec4</t>
   </si>
   <si>
+    <t>2081/4/8</t>
+  </si>
+  <si>
     <t>10fb58ef-6769-42c6-bdf3-9be1963f6b8e</t>
   </si>
   <si>
@@ -2446,7 +2752,55 @@
     <t>42d3c76e-729a-4c29-85ae-c28639fed3e0</t>
   </si>
   <si>
+    <t>ba1cb7c9-949b-4e5f-913f-761518313453</t>
+  </si>
+  <si>
+    <t>2081/12/15</t>
+  </si>
+  <si>
     <t>76564c5a-a00a-427d-93bd-3d3243904019</t>
+  </si>
+  <si>
+    <t>1dc3e920-9583-4d07-8674-bcf3a6d56e61</t>
+  </si>
+  <si>
+    <t>AROUND 1,50,000 RUPEES HAVE YET TO BE COLLECTED FOR GOODS BORROWED FROM THE STORE BY CUSTOMERS ON VARIOUS DATES BUT HAVE NOT YET BEEN REPAID.</t>
+  </si>
+  <si>
+    <t>2078/5/8</t>
+  </si>
+  <si>
+    <t>CUSTOMERS HAVE NOT YET PAID EVEN THOUGH THEY SHOULD BE PAID BY NOW.</t>
+  </si>
+  <si>
+    <t>0fca0068-42ad-4561-be14-55f9ad1277a4</t>
+  </si>
+  <si>
+    <t>GHAR BANAUNA DIYAKO</t>
+  </si>
+  <si>
+    <t>2082/2/1</t>
+  </si>
+  <si>
+    <t>392df692-ecd5-4396-946b-190695aca413</t>
+  </si>
+  <si>
+    <t>BIDESH JSAJA KO LAGI DIYA KO</t>
+  </si>
+  <si>
+    <t>2081/9/19</t>
+  </si>
+  <si>
+    <t>e09c6472-4839-481d-94ab-f2e02d628041</t>
+  </si>
+  <si>
+    <t>GHAR LOAN</t>
+  </si>
+  <si>
+    <t>2082/7/3</t>
+  </si>
+  <si>
+    <t>2082/3/9</t>
   </si>
 </sst>
 </file>
@@ -2492,11 +2846,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2801,7 +3153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U314"/>
+  <dimension ref="A1:U340"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -2813,7 +3165,7 @@
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="167.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -17908,78 +18260,78 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>11304</v>
+        <v>11286</v>
       </c>
       <c r="B244" t="s">
         <v>714</v>
       </c>
       <c r="C244">
-        <v>3115</v>
+        <v>4102</v>
       </c>
       <c r="D244">
-        <v>31304</v>
+        <v>40504</v>
       </c>
       <c r="E244">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F244">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G244" t="s">
-        <v>503</v>
+        <v>172</v>
       </c>
       <c r="H244" t="s">
         <v>35</v>
       </c>
       <c r="I244">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="J244">
         <v>1</v>
       </c>
       <c r="K244" t="s">
-        <v>479</v>
+        <v>715</v>
       </c>
       <c r="L244">
-        <v>54754</v>
+        <v>54665</v>
       </c>
       <c r="M244">
         <v>1</v>
       </c>
-      <c r="N244" s="2">
-        <v>66320</v>
+      <c r="N244" t="s">
+        <v>716</v>
       </c>
       <c r="O244">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P244">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="Q244">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R244">
-        <v>120000</v>
-      </c>
-      <c r="S244">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="S244" t="s">
+        <v>717</v>
       </c>
       <c r="T244">
         <v>3</v>
       </c>
       <c r="U244">
-        <v>100000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>11309</v>
+        <v>11304</v>
       </c>
       <c r="B245" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C245">
-        <v>3215</v>
+        <v>3115</v>
       </c>
       <c r="D245">
         <v>31304</v>
@@ -17988,7 +18340,7 @@
         <v>4</v>
       </c>
       <c r="F245">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G245" t="s">
         <v>503</v>
@@ -18003,45 +18355,45 @@
         <v>1</v>
       </c>
       <c r="K245" t="s">
-        <v>99</v>
+        <v>479</v>
       </c>
       <c r="L245">
-        <v>54765</v>
+        <v>54754</v>
       </c>
       <c r="M245">
         <v>1</v>
       </c>
-      <c r="N245" s="2">
-        <v>66322</v>
+      <c r="N245" t="s">
+        <v>719</v>
       </c>
       <c r="O245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P245">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="Q245">
         <v>24</v>
       </c>
       <c r="R245">
-        <v>72000</v>
-      </c>
-      <c r="S245" t="s">
-        <v>716</v>
+        <v>120000</v>
+      </c>
+      <c r="S245">
+        <v>2</v>
       </c>
       <c r="T245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U245">
-        <v>48000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>11315</v>
+        <v>11309</v>
       </c>
       <c r="B246" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C246">
         <v>3215</v>
@@ -18062,51 +18414,51 @@
         <v>35</v>
       </c>
       <c r="I246">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J246">
         <v>1</v>
       </c>
-      <c r="K246">
-        <v>1</v>
+      <c r="K246" t="s">
+        <v>99</v>
       </c>
       <c r="L246">
-        <v>54783</v>
+        <v>54765</v>
       </c>
       <c r="M246">
         <v>1</v>
       </c>
-      <c r="N246" s="2">
-        <v>64438</v>
+      <c r="N246" t="s">
+        <v>721</v>
       </c>
       <c r="O246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P246">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R246">
-        <v>0</v>
-      </c>
-      <c r="S246">
-        <v>1</v>
+        <v>72000</v>
+      </c>
+      <c r="S246" t="s">
+        <v>722</v>
       </c>
       <c r="T246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>11317</v>
+        <v>11315</v>
       </c>
       <c r="B247" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="C247">
         <v>3215</v>
@@ -18118,7 +18470,7 @@
         <v>4</v>
       </c>
       <c r="F247">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G247" t="s">
         <v>503</v>
@@ -18132,49 +18484,49 @@
       <c r="J247">
         <v>1</v>
       </c>
-      <c r="K247" t="s">
-        <v>719</v>
+      <c r="K247">
+        <v>1</v>
       </c>
       <c r="L247">
-        <v>54792</v>
+        <v>54783</v>
       </c>
       <c r="M247">
         <v>1</v>
       </c>
-      <c r="N247" s="2">
-        <v>65168</v>
+      <c r="N247" t="s">
+        <v>724</v>
       </c>
       <c r="O247">
         <v>4</v>
       </c>
       <c r="P247">
-        <v>250000</v>
+        <v>2000000</v>
       </c>
       <c r="Q247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R247">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="S247">
         <v>1</v>
       </c>
       <c r="T247">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U247">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>11337</v>
+        <v>11317</v>
       </c>
       <c r="B248" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C248">
-        <v>3115</v>
+        <v>3215</v>
       </c>
       <c r="D248">
         <v>31304</v>
@@ -18183,7 +18535,7 @@
         <v>4</v>
       </c>
       <c r="F248">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G248" t="s">
         <v>503</v>
@@ -18192,60 +18544,63 @@
         <v>35</v>
       </c>
       <c r="I248">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="J248">
         <v>1</v>
       </c>
       <c r="K248" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="L248">
-        <v>54886</v>
+        <v>54792</v>
       </c>
       <c r="M248">
         <v>1</v>
       </c>
-      <c r="N248" s="2">
-        <v>64651</v>
+      <c r="N248" t="s">
+        <v>727</v>
       </c>
       <c r="O248">
         <v>4</v>
       </c>
       <c r="P248">
-        <v>1200000</v>
+        <v>250000</v>
       </c>
       <c r="Q248">
-        <v>18</v>
-      </c>
-      <c r="S248" t="s">
-        <v>557</v>
+        <v>1</v>
+      </c>
+      <c r="R248">
+        <v>18000</v>
+      </c>
+      <c r="S248">
+        <v>1</v>
       </c>
       <c r="T248">
         <v>2</v>
       </c>
       <c r="U248">
-        <v>400000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>11338</v>
+        <v>11357</v>
       </c>
       <c r="B249" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="C249">
-        <v>3115</v>
+        <v>3485</v>
       </c>
       <c r="D249">
-        <v>31304</v>
+        <v>30608</v>
       </c>
       <c r="E249">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F249">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G249" t="s">
         <v>503</v>
@@ -18254,63 +18609,60 @@
         <v>35</v>
       </c>
       <c r="I249">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="J249">
         <v>1</v>
       </c>
       <c r="K249" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="L249">
-        <v>54889</v>
+        <v>54977</v>
       </c>
       <c r="M249">
         <v>2</v>
       </c>
-      <c r="N249" s="2">
-        <v>62094</v>
+      <c r="N249" t="s">
+        <v>312</v>
       </c>
       <c r="O249">
         <v>4</v>
       </c>
       <c r="P249">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="Q249">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="R249">
-        <v>192000</v>
-      </c>
-      <c r="S249" t="s">
-        <v>724</v>
+        <v>0</v>
+      </c>
+      <c r="S249">
+        <v>0</v>
       </c>
       <c r="T249">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>11338</v>
+        <v>11382</v>
       </c>
       <c r="B250" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="C250">
-        <v>3115</v>
-      </c>
-      <c r="D250">
-        <v>31304</v>
+        <v>3608</v>
       </c>
       <c r="E250">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F250">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G250" t="s">
         <v>503</v>
@@ -18319,37 +18671,37 @@
         <v>35</v>
       </c>
       <c r="I250">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="J250">
         <v>1</v>
       </c>
       <c r="K250" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="L250">
-        <v>54889</v>
+        <v>55079</v>
       </c>
       <c r="M250">
-        <v>2</v>
-      </c>
-      <c r="N250" s="2">
-        <v>62125</v>
+        <v>1</v>
+      </c>
+      <c r="N250" t="s">
+        <v>701</v>
       </c>
       <c r="O250">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P250">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="Q250">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R250">
-        <v>72000</v>
-      </c>
-      <c r="S250" t="s">
-        <v>196</v>
+        <v>0</v>
+      </c>
+      <c r="S250">
+        <v>1</v>
       </c>
       <c r="T250">
         <v>3</v>
@@ -18360,22 +18712,22 @@
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>11338</v>
+        <v>11398</v>
       </c>
       <c r="B251" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="C251">
-        <v>3115</v>
+        <v>3608</v>
       </c>
       <c r="D251">
-        <v>31304</v>
+        <v>30608</v>
       </c>
       <c r="E251">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F251">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G251" t="s">
         <v>503</v>
@@ -18384,63 +18736,63 @@
         <v>35</v>
       </c>
       <c r="I251">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="J251">
         <v>1</v>
       </c>
       <c r="K251" t="s">
-        <v>255</v>
+        <v>732</v>
       </c>
       <c r="L251">
-        <v>54889</v>
+        <v>55141</v>
       </c>
       <c r="M251">
-        <v>2</v>
-      </c>
-      <c r="N251" s="2">
-        <v>63715</v>
+        <v>1</v>
+      </c>
+      <c r="N251" t="s">
+        <v>733</v>
       </c>
       <c r="O251">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P251">
-        <v>1000000</v>
+        <v>150000</v>
       </c>
       <c r="Q251">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R251">
-        <v>240000</v>
-      </c>
-      <c r="S251" t="s">
-        <v>196</v>
+        <v>0</v>
+      </c>
+      <c r="S251">
+        <v>4</v>
       </c>
       <c r="T251">
         <v>2</v>
       </c>
       <c r="U251">
-        <v>800000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>11357</v>
+        <v>11414</v>
       </c>
       <c r="B252" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="C252">
-        <v>3422</v>
+        <v>1102</v>
       </c>
       <c r="D252">
-        <v>30608</v>
+        <v>10304</v>
       </c>
       <c r="E252">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F252">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G252" t="s">
         <v>503</v>
@@ -18449,60 +18801,63 @@
         <v>35</v>
       </c>
       <c r="I252">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="J252">
         <v>1</v>
       </c>
       <c r="K252" t="s">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="L252">
-        <v>54977</v>
+        <v>55204</v>
       </c>
       <c r="M252">
-        <v>2</v>
-      </c>
-      <c r="N252" s="2">
-        <v>66328</v>
+        <v>3</v>
+      </c>
+      <c r="N252" t="s">
+        <v>735</v>
       </c>
       <c r="O252">
         <v>4</v>
       </c>
       <c r="P252">
-        <v>400000</v>
+        <v>25000</v>
       </c>
       <c r="Q252">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R252">
         <v>0</v>
       </c>
       <c r="S252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T252">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U252">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>11382</v>
+        <v>11482</v>
       </c>
       <c r="B253" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="C253">
-        <v>3608</v>
+        <v>2105</v>
+      </c>
+      <c r="D253">
+        <v>20302</v>
       </c>
       <c r="E253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F253">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G253" t="s">
         <v>503</v>
@@ -18511,22 +18866,22 @@
         <v>35</v>
       </c>
       <c r="I253">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="J253">
         <v>1</v>
       </c>
       <c r="K253" t="s">
-        <v>325</v>
+        <v>209</v>
       </c>
       <c r="L253">
-        <v>55079</v>
+        <v>55501</v>
       </c>
       <c r="M253">
         <v>1</v>
       </c>
-      <c r="N253" s="2">
-        <v>66672</v>
+      <c r="N253" t="s">
+        <v>514</v>
       </c>
       <c r="O253">
         <v>4</v>
@@ -18540,8 +18895,8 @@
       <c r="R253">
         <v>0</v>
       </c>
-      <c r="S253">
-        <v>1</v>
+      <c r="S253" t="s">
+        <v>247</v>
       </c>
       <c r="T253">
         <v>3</v>
@@ -18552,22 +18907,22 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>11398</v>
+        <v>11488</v>
       </c>
       <c r="B254" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="C254">
-        <v>3608</v>
+        <v>2205</v>
       </c>
       <c r="D254">
-        <v>30608</v>
+        <v>20302</v>
       </c>
       <c r="E254">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F254">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G254" t="s">
         <v>503</v>
@@ -18576,22 +18931,22 @@
         <v>35</v>
       </c>
       <c r="I254">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J254">
         <v>1</v>
       </c>
       <c r="K254" t="s">
-        <v>729</v>
+        <v>214</v>
       </c>
       <c r="L254">
-        <v>55141</v>
+        <v>55536</v>
       </c>
       <c r="M254">
         <v>1</v>
       </c>
-      <c r="N254" s="2">
-        <v>65845</v>
+      <c r="N254" t="s">
+        <v>738</v>
       </c>
       <c r="O254">
         <v>4</v>
@@ -18600,19 +18955,19 @@
         <v>150000</v>
       </c>
       <c r="Q254">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R254">
         <v>0</v>
       </c>
       <c r="S254">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T254">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U254">
-        <v>100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
@@ -18620,7 +18975,7 @@
         <v>11496</v>
       </c>
       <c r="B255" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="C255">
         <v>3113</v>
@@ -18647,7 +19002,7 @@
         <v>1</v>
       </c>
       <c r="K255" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="L255">
         <v>55580</v>
@@ -18655,8 +19010,8 @@
       <c r="M255">
         <v>1</v>
       </c>
-      <c r="N255" s="2">
-        <v>66477</v>
+      <c r="N255" t="s">
+        <v>489</v>
       </c>
       <c r="O255">
         <v>4</v>
@@ -18684,8 +19039,8 @@
       <c r="A256">
         <v>11505</v>
       </c>
-      <c r="B256" s="3" t="s">
-        <v>732</v>
+      <c r="B256" t="s">
+        <v>741</v>
       </c>
       <c r="C256">
         <v>3213</v>
@@ -18712,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="K256" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="L256">
         <v>55628</v>
@@ -18720,8 +19075,8 @@
       <c r="M256">
         <v>1</v>
       </c>
-      <c r="N256" s="2">
-        <v>65594</v>
+      <c r="N256" t="s">
+        <v>743</v>
       </c>
       <c r="O256">
         <v>5</v>
@@ -18736,7 +19091,7 @@
         <v>0</v>
       </c>
       <c r="S256" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="T256">
         <v>3</v>
@@ -18749,8 +19104,8 @@
       <c r="A257">
         <v>11505</v>
       </c>
-      <c r="B257" s="3" t="s">
-        <v>732</v>
+      <c r="B257" t="s">
+        <v>741</v>
       </c>
       <c r="C257">
         <v>3213</v>
@@ -18777,7 +19132,7 @@
         <v>1</v>
       </c>
       <c r="K257" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="L257">
         <v>55628</v>
@@ -18785,8 +19140,8 @@
       <c r="M257">
         <v>1</v>
       </c>
-      <c r="N257" s="2">
-        <v>66478</v>
+      <c r="N257" t="s">
+        <v>746</v>
       </c>
       <c r="O257">
         <v>5</v>
@@ -18801,7 +19156,7 @@
         <v>0</v>
       </c>
       <c r="S257" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="T257">
         <v>3</v>
@@ -18815,7 +19170,7 @@
         <v>11533</v>
       </c>
       <c r="B258" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="C258">
         <v>3113</v>
@@ -18850,8 +19205,8 @@
       <c r="M258">
         <v>3</v>
       </c>
-      <c r="N258" s="2">
-        <v>66173</v>
+      <c r="N258" t="s">
+        <v>749</v>
       </c>
       <c r="O258">
         <v>4</v>
@@ -18874,7 +19229,7 @@
         <v>11533</v>
       </c>
       <c r="B259" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="C259">
         <v>3113</v>
@@ -18909,8 +19264,8 @@
       <c r="M259">
         <v>3</v>
       </c>
-      <c r="N259" s="2">
-        <v>66416</v>
+      <c r="N259" t="s">
+        <v>750</v>
       </c>
       <c r="O259">
         <v>4</v>
@@ -18933,7 +19288,7 @@
         <v>11533</v>
       </c>
       <c r="B260" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="C260">
         <v>3113</v>
@@ -18968,8 +19323,8 @@
       <c r="M260">
         <v>3</v>
       </c>
-      <c r="N260" s="2">
-        <v>66597</v>
+      <c r="N260" t="s">
+        <v>751</v>
       </c>
       <c r="O260">
         <v>4</v>
@@ -18992,7 +19347,7 @@
         <v>11553</v>
       </c>
       <c r="B261" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="C261">
         <v>3113</v>
@@ -19019,7 +19374,7 @@
         <v>1</v>
       </c>
       <c r="K261" t="s">
-        <v>739</v>
+        <v>753</v>
       </c>
       <c r="L261">
         <v>55880</v>
@@ -19027,8 +19382,8 @@
       <c r="M261">
         <v>1</v>
       </c>
-      <c r="N261" s="2">
-        <v>66438</v>
+      <c r="N261" t="s">
+        <v>754</v>
       </c>
       <c r="O261">
         <v>5</v>
@@ -19057,7 +19412,7 @@
         <v>11553</v>
       </c>
       <c r="B262" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="C262">
         <v>3113</v>
@@ -19084,7 +19439,7 @@
         <v>1</v>
       </c>
       <c r="K262" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="L262">
         <v>55880</v>
@@ -19092,8 +19447,8 @@
       <c r="M262">
         <v>1</v>
       </c>
-      <c r="N262" s="2">
-        <v>66244</v>
+      <c r="N262" t="s">
+        <v>756</v>
       </c>
       <c r="P262">
         <v>100000</v>
@@ -19119,7 +19474,7 @@
         <v>11553</v>
       </c>
       <c r="B263" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="C263">
         <v>3113</v>
@@ -19146,7 +19501,7 @@
         <v>1</v>
       </c>
       <c r="K263" t="s">
-        <v>741</v>
+        <v>757</v>
       </c>
       <c r="L263">
         <v>55880</v>
@@ -19154,8 +19509,8 @@
       <c r="M263">
         <v>1</v>
       </c>
-      <c r="N263" s="2">
-        <v>66465</v>
+      <c r="N263" t="s">
+        <v>486</v>
       </c>
       <c r="O263">
         <v>5</v>
@@ -19184,7 +19539,7 @@
         <v>11556</v>
       </c>
       <c r="B264" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="C264">
         <v>3213</v>
@@ -19219,8 +19574,8 @@
       <c r="M264">
         <v>1</v>
       </c>
-      <c r="N264" s="2">
-        <v>66300</v>
+      <c r="N264" t="s">
+        <v>759</v>
       </c>
       <c r="O264">
         <v>4</v>
@@ -19243,22 +19598,22 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>11563</v>
+        <v>11615</v>
       </c>
       <c r="B265" t="s">
-        <v>722</v>
+        <v>760</v>
       </c>
       <c r="C265">
-        <v>3115</v>
+        <v>2205</v>
       </c>
       <c r="D265">
-        <v>31304</v>
+        <v>20302</v>
       </c>
       <c r="E265">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F265">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G265" t="s">
         <v>503</v>
@@ -19267,37 +19622,37 @@
         <v>35</v>
       </c>
       <c r="I265">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J265">
         <v>1</v>
       </c>
       <c r="K265" t="s">
-        <v>723</v>
+        <v>761</v>
       </c>
       <c r="L265">
-        <v>55930</v>
+        <v>56186</v>
       </c>
       <c r="M265">
-        <v>2</v>
-      </c>
-      <c r="N265" s="2">
-        <v>62094</v>
+        <v>1</v>
+      </c>
+      <c r="N265" t="s">
+        <v>762</v>
       </c>
       <c r="O265">
         <v>4</v>
       </c>
       <c r="P265">
-        <v>800000</v>
+        <v>3000000</v>
       </c>
       <c r="Q265">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R265">
-        <v>192000</v>
-      </c>
-      <c r="S265" t="s">
-        <v>724</v>
+        <v>0</v>
+      </c>
+      <c r="S265">
+        <v>5</v>
       </c>
       <c r="T265">
         <v>3</v>
@@ -19308,22 +19663,22 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>11563</v>
+        <v>11620</v>
       </c>
       <c r="B266" t="s">
-        <v>722</v>
+        <v>763</v>
       </c>
       <c r="C266">
-        <v>3115</v>
+        <v>2105</v>
       </c>
       <c r="D266">
-        <v>31304</v>
+        <v>20302</v>
       </c>
       <c r="E266">
         <v>4</v>
       </c>
       <c r="F266">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G266" t="s">
         <v>503</v>
@@ -19332,37 +19687,37 @@
         <v>35</v>
       </c>
       <c r="I266">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J266">
         <v>1</v>
       </c>
       <c r="K266" t="s">
-        <v>255</v>
+        <v>764</v>
       </c>
       <c r="L266">
-        <v>55930</v>
+        <v>56221</v>
       </c>
       <c r="M266">
-        <v>2</v>
-      </c>
-      <c r="N266" s="2">
-        <v>62125</v>
+        <v>1</v>
+      </c>
+      <c r="N266" t="s">
+        <v>765</v>
       </c>
       <c r="O266">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P266">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q266">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R266">
-        <v>72000</v>
-      </c>
-      <c r="S266" t="s">
-        <v>196</v>
+        <v>0</v>
+      </c>
+      <c r="S266">
+        <v>2</v>
       </c>
       <c r="T266">
         <v>3</v>
@@ -19373,22 +19728,22 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>11563</v>
+        <v>11647</v>
       </c>
       <c r="B267" t="s">
-        <v>722</v>
+        <v>766</v>
       </c>
       <c r="C267">
-        <v>3115</v>
+        <v>2600</v>
       </c>
       <c r="D267">
-        <v>31304</v>
+        <v>20315</v>
       </c>
       <c r="E267">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F267">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G267" t="s">
         <v>503</v>
@@ -19397,63 +19752,63 @@
         <v>35</v>
       </c>
       <c r="I267">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J267">
         <v>1</v>
       </c>
       <c r="K267" t="s">
-        <v>255</v>
+        <v>767</v>
       </c>
       <c r="L267">
-        <v>55930</v>
+        <v>56315</v>
       </c>
       <c r="M267">
-        <v>2</v>
-      </c>
-      <c r="N267" s="2">
-        <v>63715</v>
+        <v>3</v>
+      </c>
+      <c r="N267" t="s">
+        <v>768</v>
       </c>
       <c r="O267">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P267">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="Q267">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R267">
-        <v>240000</v>
-      </c>
-      <c r="S267" t="s">
-        <v>196</v>
+        <v>0</v>
+      </c>
+      <c r="S267">
+        <v>0</v>
       </c>
       <c r="T267">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U267">
-        <v>800000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>11564</v>
+        <v>11734</v>
       </c>
       <c r="B268" t="s">
-        <v>720</v>
+        <v>769</v>
       </c>
       <c r="C268">
-        <v>3115</v>
+        <v>2600</v>
       </c>
       <c r="D268">
-        <v>31304</v>
+        <v>20315</v>
       </c>
       <c r="E268">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F268">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G268" t="s">
         <v>503</v>
@@ -19462,40 +19817,43 @@
         <v>35</v>
       </c>
       <c r="I268">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J268">
         <v>1</v>
       </c>
       <c r="K268" t="s">
-        <v>721</v>
+        <v>245</v>
       </c>
       <c r="L268">
-        <v>55938</v>
+        <v>56713</v>
       </c>
       <c r="M268">
-        <v>1</v>
-      </c>
-      <c r="N268" s="2">
-        <v>64651</v>
+        <v>2</v>
+      </c>
+      <c r="N268" t="s">
+        <v>770</v>
       </c>
       <c r="O268">
         <v>4</v>
       </c>
       <c r="P268">
-        <v>1200000</v>
+        <v>500000</v>
       </c>
       <c r="Q268">
-        <v>18</v>
-      </c>
-      <c r="S268" t="s">
-        <v>557</v>
+        <v>12</v>
+      </c>
+      <c r="R268">
+        <v>0</v>
+      </c>
+      <c r="S268">
+        <v>2</v>
       </c>
       <c r="T268">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U268">
-        <v>400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
@@ -19503,7 +19861,7 @@
         <v>11736</v>
       </c>
       <c r="B269" t="s">
-        <v>743</v>
+        <v>771</v>
       </c>
       <c r="C269">
         <v>1207</v>
@@ -19530,7 +19888,7 @@
         <v>1</v>
       </c>
       <c r="K269" t="s">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="L269">
         <v>56723</v>
@@ -19538,8 +19896,8 @@
       <c r="M269">
         <v>2</v>
       </c>
-      <c r="N269" s="2">
-        <v>66267</v>
+      <c r="N269" t="s">
+        <v>412</v>
       </c>
       <c r="O269">
         <v>5</v>
@@ -19568,7 +19926,7 @@
         <v>11737</v>
       </c>
       <c r="B270" t="s">
-        <v>745</v>
+        <v>773</v>
       </c>
       <c r="C270">
         <v>1207</v>
@@ -19595,7 +19953,7 @@
         <v>1</v>
       </c>
       <c r="K270" t="s">
-        <v>746</v>
+        <v>774</v>
       </c>
       <c r="O270">
         <v>4</v>
@@ -19621,7 +19979,7 @@
         <v>11743</v>
       </c>
       <c r="B271" t="s">
-        <v>747</v>
+        <v>775</v>
       </c>
       <c r="C271">
         <v>1107</v>
@@ -19648,7 +20006,7 @@
         <v>1</v>
       </c>
       <c r="K271" t="s">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="L271">
         <v>56757</v>
@@ -19656,8 +20014,8 @@
       <c r="M271">
         <v>3</v>
       </c>
-      <c r="N271" s="2">
-        <v>66446</v>
+      <c r="N271" t="s">
+        <v>776</v>
       </c>
       <c r="O271">
         <v>4</v>
@@ -19686,7 +20044,7 @@
         <v>11746</v>
       </c>
       <c r="B272" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="C272">
         <v>1107</v>
@@ -19713,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="K272" t="s">
-        <v>749</v>
+        <v>778</v>
       </c>
       <c r="L272">
         <v>56771</v>
@@ -19721,8 +20079,8 @@
       <c r="M272">
         <v>1</v>
       </c>
-      <c r="N272" s="2">
-        <v>66267</v>
+      <c r="N272" t="s">
+        <v>412</v>
       </c>
       <c r="O272">
         <v>5</v>
@@ -19751,7 +20109,7 @@
         <v>11747</v>
       </c>
       <c r="B273" t="s">
-        <v>750</v>
+        <v>779</v>
       </c>
       <c r="C273">
         <v>1107</v>
@@ -19778,7 +20136,7 @@
         <v>1</v>
       </c>
       <c r="K273" t="s">
-        <v>749</v>
+        <v>778</v>
       </c>
       <c r="L273">
         <v>56778</v>
@@ -19786,8 +20144,8 @@
       <c r="M273">
         <v>3</v>
       </c>
-      <c r="N273" s="2">
-        <v>65837</v>
+      <c r="N273" t="s">
+        <v>780</v>
       </c>
       <c r="O273">
         <v>4</v>
@@ -19816,7 +20174,7 @@
         <v>11747</v>
       </c>
       <c r="B274" t="s">
-        <v>750</v>
+        <v>779</v>
       </c>
       <c r="C274">
         <v>1107</v>
@@ -19878,7 +20236,7 @@
         <v>11748</v>
       </c>
       <c r="B275" t="s">
-        <v>751</v>
+        <v>781</v>
       </c>
       <c r="C275">
         <v>1107</v>
@@ -19905,7 +20263,7 @@
         <v>1</v>
       </c>
       <c r="K275" t="s">
-        <v>746</v>
+        <v>774</v>
       </c>
       <c r="L275">
         <v>56783</v>
@@ -19913,8 +20271,8 @@
       <c r="M275">
         <v>2</v>
       </c>
-      <c r="N275" s="2">
-        <v>66090</v>
+      <c r="N275" t="s">
+        <v>782</v>
       </c>
       <c r="O275">
         <v>5</v>
@@ -19940,22 +20298,22 @@
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>11883</v>
+        <v>11749</v>
       </c>
       <c r="B276" t="s">
-        <v>752</v>
+        <v>783</v>
       </c>
       <c r="C276">
-        <v>4207</v>
+        <v>5306</v>
       </c>
       <c r="D276">
-        <v>40806</v>
+        <v>51106</v>
       </c>
       <c r="E276">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F276">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G276" t="s">
         <v>503</v>
@@ -19964,60 +20322,60 @@
         <v>35</v>
       </c>
       <c r="I276">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J276">
         <v>1</v>
       </c>
-      <c r="K276" t="s">
-        <v>495</v>
-      </c>
       <c r="L276">
-        <v>57568</v>
+        <v>56786</v>
       </c>
       <c r="M276">
-        <v>2</v>
-      </c>
-      <c r="N276" s="2">
-        <v>65108</v>
+        <v>3</v>
+      </c>
+      <c r="N276" t="s">
+        <v>784</v>
       </c>
       <c r="O276">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P276">
-        <v>60000</v>
-      </c>
-      <c r="Q276">
-        <v>0</v>
-      </c>
-      <c r="R276">
-        <v>0</v>
-      </c>
-      <c r="S276" t="s">
-        <v>753</v>
+        <v>600000</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>161</v>
+      </c>
+      <c r="R276" t="s">
+        <v>161</v>
+      </c>
+      <c r="S276">
+        <v>2082</v>
       </c>
       <c r="T276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>11896</v>
+        <v>11762</v>
       </c>
       <c r="B277" t="s">
-        <v>754</v>
+        <v>785</v>
       </c>
       <c r="C277">
-        <v>4107</v>
+        <v>5511</v>
+      </c>
+      <c r="D277">
+        <v>51106</v>
       </c>
       <c r="E277">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F277">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G277" t="s">
         <v>503</v>
@@ -20026,54 +20384,51 @@
         <v>35</v>
       </c>
       <c r="I277">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J277">
         <v>1</v>
       </c>
-      <c r="K277" t="s">
-        <v>755</v>
-      </c>
       <c r="L277">
-        <v>57645</v>
+        <v>56848</v>
       </c>
       <c r="M277">
         <v>1</v>
       </c>
-      <c r="N277" s="2">
-        <v>64745</v>
+      <c r="N277" t="s">
+        <v>786</v>
       </c>
       <c r="O277">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P277">
-        <v>400000</v>
-      </c>
-      <c r="Q277">
-        <v>0</v>
-      </c>
-      <c r="R277">
-        <v>0</v>
+        <v>30000</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>161</v>
+      </c>
+      <c r="R277" t="s">
+        <v>161</v>
       </c>
       <c r="S277" t="s">
-        <v>756</v>
+        <v>667</v>
       </c>
       <c r="T277">
         <v>3</v>
       </c>
-      <c r="U277">
-        <v>0</v>
+      <c r="U277" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>11901</v>
+        <v>11819</v>
       </c>
       <c r="B278" t="s">
-        <v>757</v>
+        <v>787</v>
       </c>
       <c r="C278">
-        <v>4207</v>
+        <v>4107</v>
       </c>
       <c r="D278">
         <v>40806</v>
@@ -20082,7 +20437,7 @@
         <v>14</v>
       </c>
       <c r="F278">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G278" t="s">
         <v>503</v>
@@ -20091,63 +20446,63 @@
         <v>35</v>
       </c>
       <c r="I278">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J278">
         <v>1</v>
       </c>
       <c r="K278" t="s">
-        <v>758</v>
+        <v>99</v>
       </c>
       <c r="L278">
-        <v>57680</v>
+        <v>57186</v>
       </c>
       <c r="M278">
-        <v>3</v>
-      </c>
-      <c r="N278" s="2">
-        <v>65806</v>
+        <v>2</v>
+      </c>
+      <c r="N278" t="s">
+        <v>48</v>
       </c>
       <c r="O278">
         <v>4</v>
       </c>
       <c r="P278">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="Q278">
         <v>24</v>
       </c>
       <c r="R278">
-        <v>8400</v>
+        <v>12000</v>
       </c>
       <c r="S278" t="s">
-        <v>759</v>
+        <v>788</v>
       </c>
       <c r="T278">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>11903</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>760</v>
+        <v>11823</v>
+      </c>
+      <c r="B279" t="s">
+        <v>789</v>
       </c>
       <c r="C279">
-        <v>4207</v>
+        <v>5406</v>
       </c>
       <c r="D279">
-        <v>40806</v>
+        <v>51106</v>
       </c>
       <c r="E279">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F279">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="G279" t="s">
         <v>503</v>
@@ -20156,51 +20511,48 @@
         <v>35</v>
       </c>
       <c r="I279">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J279">
         <v>1</v>
       </c>
-      <c r="K279" t="s">
-        <v>761</v>
-      </c>
       <c r="L279">
-        <v>57685</v>
+        <v>57212</v>
       </c>
       <c r="M279">
-        <v>1</v>
-      </c>
-      <c r="N279" s="2">
-        <v>65107</v>
+        <v>3</v>
+      </c>
+      <c r="N279" t="s">
+        <v>790</v>
       </c>
       <c r="O279">
         <v>5</v>
       </c>
       <c r="P279">
-        <v>300000</v>
-      </c>
-      <c r="Q279">
-        <v>0</v>
-      </c>
-      <c r="R279">
-        <v>0</v>
-      </c>
-      <c r="S279">
-        <v>1</v>
+        <v>700000</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>161</v>
+      </c>
+      <c r="R279" t="s">
+        <v>161</v>
+      </c>
+      <c r="S279" t="s">
+        <v>791</v>
       </c>
       <c r="T279">
         <v>3</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>11903</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>760</v>
+        <v>11883</v>
+      </c>
+      <c r="B280" t="s">
+        <v>792</v>
       </c>
       <c r="C280">
         <v>4207</v>
@@ -20212,7 +20564,7 @@
         <v>14</v>
       </c>
       <c r="F280">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G280" t="s">
         <v>503</v>
@@ -20227,31 +20579,31 @@
         <v>1</v>
       </c>
       <c r="K280" t="s">
-        <v>762</v>
+        <v>495</v>
       </c>
       <c r="L280">
-        <v>57685</v>
+        <v>57568</v>
       </c>
       <c r="M280">
-        <v>1</v>
-      </c>
-      <c r="N280" s="2">
-        <v>66326</v>
+        <v>2</v>
+      </c>
+      <c r="N280" t="s">
+        <v>793</v>
       </c>
       <c r="O280">
         <v>4</v>
       </c>
       <c r="P280">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="Q280">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R280">
-        <v>2000</v>
-      </c>
-      <c r="S280">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S280" t="s">
+        <v>794</v>
       </c>
       <c r="T280">
         <v>3</v>
@@ -20262,22 +20614,19 @@
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>11911</v>
+        <v>11896</v>
       </c>
       <c r="B281" t="s">
-        <v>763</v>
+        <v>795</v>
       </c>
       <c r="C281">
-        <v>7102</v>
-      </c>
-      <c r="D281">
-        <v>70210</v>
+        <v>4107</v>
       </c>
       <c r="E281">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F281">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G281" t="s">
         <v>503</v>
@@ -20286,37 +20635,37 @@
         <v>35</v>
       </c>
       <c r="I281">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="J281">
         <v>1</v>
       </c>
       <c r="K281" t="s">
-        <v>53</v>
+        <v>796</v>
       </c>
       <c r="L281">
-        <v>57724</v>
+        <v>57645</v>
       </c>
       <c r="M281">
         <v>1</v>
       </c>
-      <c r="N281" s="2">
-        <v>66177</v>
+      <c r="N281" t="s">
+        <v>797</v>
       </c>
       <c r="O281">
         <v>4</v>
       </c>
       <c r="P281">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="Q281">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R281">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="S281" t="s">
-        <v>764</v>
+        <v>798</v>
       </c>
       <c r="T281">
         <v>3</v>
@@ -20327,22 +20676,22 @@
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>11915</v>
+        <v>11901</v>
       </c>
       <c r="B282" t="s">
-        <v>765</v>
+        <v>799</v>
       </c>
       <c r="C282">
-        <v>7103</v>
+        <v>4207</v>
       </c>
       <c r="D282">
-        <v>70403</v>
+        <v>40806</v>
       </c>
       <c r="E282">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F282">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G282" t="s">
         <v>503</v>
@@ -20351,37 +20700,37 @@
         <v>35</v>
       </c>
       <c r="I282">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="J282">
         <v>1</v>
       </c>
       <c r="K282" t="s">
-        <v>766</v>
+        <v>800</v>
       </c>
       <c r="L282">
-        <v>57741</v>
+        <v>57680</v>
       </c>
       <c r="M282">
-        <v>5</v>
-      </c>
-      <c r="N282" s="2">
-        <v>66250</v>
+        <v>3</v>
+      </c>
+      <c r="N282" t="s">
+        <v>801</v>
       </c>
       <c r="O282">
         <v>4</v>
       </c>
       <c r="P282">
-        <v>400000</v>
+        <v>35000</v>
       </c>
       <c r="Q282">
         <v>24</v>
       </c>
       <c r="R282">
-        <v>24000</v>
+        <v>8400</v>
       </c>
       <c r="S282" t="s">
-        <v>93</v>
+        <v>802</v>
       </c>
       <c r="T282">
         <v>3</v>
@@ -20392,22 +20741,22 @@
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>11917</v>
+        <v>11903</v>
       </c>
       <c r="B283" t="s">
-        <v>767</v>
+        <v>803</v>
       </c>
       <c r="C283">
-        <v>7103</v>
+        <v>4207</v>
       </c>
       <c r="D283">
-        <v>70403</v>
+        <v>40806</v>
       </c>
       <c r="E283">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F283">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G283" t="s">
         <v>503</v>
@@ -20416,28 +20765,28 @@
         <v>35</v>
       </c>
       <c r="I283">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="J283">
         <v>1</v>
       </c>
       <c r="K283" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="L283">
-        <v>57748</v>
+        <v>57685</v>
       </c>
       <c r="M283">
         <v>1</v>
       </c>
-      <c r="N283" s="2">
-        <v>66271</v>
+      <c r="N283" t="s">
+        <v>805</v>
       </c>
       <c r="O283">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P283">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -20445,8 +20794,8 @@
       <c r="R283">
         <v>0</v>
       </c>
-      <c r="S283" t="s">
-        <v>764</v>
+      <c r="S283">
+        <v>1</v>
       </c>
       <c r="T283">
         <v>3</v>
@@ -20457,22 +20806,22 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>11920</v>
+        <v>11903</v>
       </c>
       <c r="B284" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="C284">
-        <v>7203</v>
+        <v>4207</v>
       </c>
       <c r="D284">
-        <v>70403</v>
+        <v>40806</v>
       </c>
       <c r="E284">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F284">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G284" t="s">
         <v>503</v>
@@ -20481,22 +20830,22 @@
         <v>35</v>
       </c>
       <c r="I284">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="J284">
         <v>1</v>
       </c>
       <c r="K284" t="s">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="L284">
-        <v>57761</v>
+        <v>57685</v>
       </c>
       <c r="M284">
         <v>1</v>
       </c>
-      <c r="N284" s="2">
-        <v>66268</v>
+      <c r="N284" t="s">
+        <v>807</v>
       </c>
       <c r="O284">
         <v>4</v>
@@ -20508,36 +20857,36 @@
         <v>24</v>
       </c>
       <c r="R284">
-        <v>24000</v>
-      </c>
-      <c r="S284" t="s">
-        <v>557</v>
+        <v>2000</v>
+      </c>
+      <c r="S284">
+        <v>1</v>
       </c>
       <c r="T284">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U284">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>11921</v>
+        <v>11911</v>
       </c>
       <c r="B285" t="s">
-        <v>770</v>
+        <v>808</v>
       </c>
       <c r="C285">
-        <v>7103</v>
+        <v>7102</v>
       </c>
       <c r="D285">
-        <v>70403</v>
+        <v>70210</v>
       </c>
       <c r="E285">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F285">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G285" t="s">
         <v>503</v>
@@ -20552,54 +20901,57 @@
         <v>1</v>
       </c>
       <c r="K285" t="s">
-        <v>771</v>
+        <v>53</v>
       </c>
       <c r="L285">
-        <v>57766</v>
+        <v>57724</v>
       </c>
       <c r="M285">
         <v>1</v>
       </c>
-      <c r="N285" s="2">
-        <v>66205</v>
+      <c r="N285" t="s">
+        <v>414</v>
       </c>
       <c r="O285">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P285">
-        <v>60000</v>
+        <v>200000</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="S285" t="s">
-        <v>93</v>
+        <v>809</v>
       </c>
       <c r="T285">
         <v>3</v>
+      </c>
+      <c r="U285">
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>11936</v>
+        <v>11915</v>
       </c>
       <c r="B286" t="s">
-        <v>772</v>
+        <v>810</v>
       </c>
       <c r="C286">
-        <v>3677</v>
+        <v>7103</v>
       </c>
       <c r="D286">
-        <v>30608</v>
+        <v>70403</v>
       </c>
       <c r="E286">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F286">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G286" t="s">
         <v>503</v>
@@ -20608,22 +20960,22 @@
         <v>35</v>
       </c>
       <c r="I286">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="J286">
         <v>1</v>
       </c>
       <c r="K286" t="s">
-        <v>773</v>
+        <v>811</v>
       </c>
       <c r="L286">
-        <v>57839</v>
+        <v>57741</v>
       </c>
       <c r="M286">
-        <v>2</v>
-      </c>
-      <c r="N286" s="2">
-        <v>66512</v>
+        <v>5</v>
+      </c>
+      <c r="N286" t="s">
+        <v>812</v>
       </c>
       <c r="O286">
         <v>4</v>
@@ -20632,13 +20984,13 @@
         <v>400000</v>
       </c>
       <c r="Q286">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="S286" t="s">
-        <v>294</v>
+        <v>93</v>
       </c>
       <c r="T286">
         <v>3</v>
@@ -20649,22 +21001,22 @@
     </row>
     <row r="287" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>11963</v>
+        <v>11916</v>
       </c>
       <c r="B287" t="s">
-        <v>774</v>
+        <v>813</v>
       </c>
       <c r="C287">
-        <v>4107</v>
+        <v>7203</v>
       </c>
       <c r="D287">
-        <v>40806</v>
+        <v>70403</v>
       </c>
       <c r="E287">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F287">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G287" t="s">
         <v>503</v>
@@ -20673,63 +21025,63 @@
         <v>35</v>
       </c>
       <c r="I287">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="J287">
         <v>1</v>
       </c>
       <c r="K287" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="L287">
-        <v>57992</v>
+        <v>57743</v>
       </c>
       <c r="M287">
         <v>1</v>
       </c>
-      <c r="N287" s="2">
-        <v>65806</v>
+      <c r="N287" t="s">
+        <v>535</v>
       </c>
       <c r="O287">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P287">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q287">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="R287">
-        <v>20000</v>
-      </c>
-      <c r="S287">
-        <v>1</v>
+        <v>7200</v>
+      </c>
+      <c r="S287" t="s">
+        <v>93</v>
       </c>
       <c r="T287">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U287">
-        <v>60000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>11963</v>
+        <v>11917</v>
       </c>
       <c r="B288" t="s">
-        <v>774</v>
+        <v>814</v>
       </c>
       <c r="C288">
-        <v>4107</v>
+        <v>7103</v>
       </c>
       <c r="D288">
-        <v>40806</v>
+        <v>70403</v>
       </c>
       <c r="E288">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F288">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G288" t="s">
         <v>503</v>
@@ -20738,28 +21090,28 @@
         <v>35</v>
       </c>
       <c r="I288">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="J288">
         <v>1</v>
       </c>
       <c r="K288" t="s">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="L288">
-        <v>57992</v>
+        <v>57748</v>
       </c>
       <c r="M288">
         <v>1</v>
       </c>
-      <c r="N288" s="2">
-        <v>66348</v>
+      <c r="N288" t="s">
+        <v>735</v>
       </c>
       <c r="O288">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P288">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -20767,34 +21119,34 @@
       <c r="R288">
         <v>0</v>
       </c>
-      <c r="S288">
-        <v>1</v>
+      <c r="S288" t="s">
+        <v>809</v>
       </c>
       <c r="T288">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U288">
-        <v>200000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>11963</v>
+        <v>11920</v>
       </c>
       <c r="B289" t="s">
-        <v>774</v>
+        <v>816</v>
       </c>
       <c r="C289">
-        <v>4107</v>
+        <v>7203</v>
       </c>
       <c r="D289">
-        <v>40806</v>
+        <v>70403</v>
       </c>
       <c r="E289">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F289">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G289" t="s">
         <v>503</v>
@@ -20803,63 +21155,63 @@
         <v>35</v>
       </c>
       <c r="I289">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="J289">
         <v>1</v>
       </c>
       <c r="K289" t="s">
-        <v>532</v>
+        <v>811</v>
       </c>
       <c r="L289">
-        <v>57992</v>
+        <v>57761</v>
       </c>
       <c r="M289">
         <v>1</v>
       </c>
-      <c r="N289" s="2">
-        <v>65654</v>
+      <c r="N289" t="s">
+        <v>817</v>
       </c>
       <c r="O289">
         <v>4</v>
       </c>
       <c r="P289">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="Q289">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="R289">
-        <v>7200</v>
-      </c>
-      <c r="S289">
-        <v>1</v>
+        <v>24000</v>
+      </c>
+      <c r="S289" t="s">
+        <v>557</v>
       </c>
       <c r="T289">
         <v>2</v>
       </c>
       <c r="U289">
-        <v>35000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="290" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>11971</v>
+        <v>11921</v>
       </c>
       <c r="B290" t="s">
-        <v>776</v>
+        <v>818</v>
       </c>
       <c r="C290">
-        <v>4207</v>
+        <v>7103</v>
       </c>
       <c r="D290">
-        <v>40806</v>
+        <v>70403</v>
       </c>
       <c r="E290">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F290">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G290" t="s">
         <v>503</v>
@@ -20868,28 +21220,28 @@
         <v>35</v>
       </c>
       <c r="I290">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="J290">
         <v>1</v>
       </c>
       <c r="K290" t="s">
-        <v>313</v>
+        <v>819</v>
       </c>
       <c r="L290">
-        <v>58034</v>
+        <v>57766</v>
       </c>
       <c r="M290">
-        <v>4</v>
-      </c>
-      <c r="N290" s="2">
-        <v>66185</v>
+        <v>1</v>
+      </c>
+      <c r="N290" t="s">
+        <v>820</v>
       </c>
       <c r="O290">
         <v>5</v>
       </c>
       <c r="P290">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -20897,34 +21249,31 @@
       <c r="R290">
         <v>0</v>
       </c>
-      <c r="S290">
-        <v>1</v>
+      <c r="S290" t="s">
+        <v>93</v>
       </c>
       <c r="T290">
         <v>3</v>
-      </c>
-      <c r="U290">
-        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>11971</v>
+        <v>11936</v>
       </c>
       <c r="B291" t="s">
-        <v>776</v>
+        <v>821</v>
       </c>
       <c r="C291">
-        <v>4207</v>
+        <v>3677</v>
       </c>
       <c r="D291">
-        <v>40806</v>
+        <v>30608</v>
       </c>
       <c r="E291">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F291">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="G291" t="s">
         <v>503</v>
@@ -20933,37 +21282,37 @@
         <v>35</v>
       </c>
       <c r="I291">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="J291">
         <v>1</v>
       </c>
       <c r="K291" t="s">
-        <v>777</v>
+        <v>822</v>
       </c>
       <c r="L291">
-        <v>58034</v>
+        <v>57839</v>
       </c>
       <c r="M291">
-        <v>4</v>
-      </c>
-      <c r="N291" s="2">
-        <v>66597</v>
+        <v>2</v>
+      </c>
+      <c r="N291" t="s">
+        <v>823</v>
       </c>
       <c r="O291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P291">
-        <v>50000</v>
+        <v>400000</v>
       </c>
       <c r="Q291">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R291">
         <v>0</v>
       </c>
-      <c r="S291">
-        <v>1</v>
+      <c r="S291" t="s">
+        <v>294</v>
       </c>
       <c r="T291">
         <v>3</v>
@@ -20974,13 +21323,13 @@
     </row>
     <row r="292" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>11971</v>
+        <v>11963</v>
       </c>
       <c r="B292" t="s">
-        <v>776</v>
+        <v>824</v>
       </c>
       <c r="C292">
-        <v>4207</v>
+        <v>4107</v>
       </c>
       <c r="D292">
         <v>40806</v>
@@ -20989,7 +21338,7 @@
         <v>14</v>
       </c>
       <c r="F292">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G292" t="s">
         <v>503</v>
@@ -21004,57 +21353,57 @@
         <v>1</v>
       </c>
       <c r="K292" t="s">
-        <v>313</v>
+        <v>532</v>
       </c>
       <c r="L292">
-        <v>58034</v>
+        <v>57992</v>
       </c>
       <c r="M292">
-        <v>4</v>
-      </c>
-      <c r="N292" s="2">
-        <v>65750</v>
+        <v>1</v>
+      </c>
+      <c r="N292" t="s">
+        <v>801</v>
       </c>
       <c r="O292">
         <v>5</v>
       </c>
       <c r="P292">
-        <v>10000</v>
+        <v>200000</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="S292">
         <v>1</v>
       </c>
       <c r="T292">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="293" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>12106</v>
+        <v>11963</v>
       </c>
       <c r="B293" t="s">
-        <v>778</v>
+        <v>824</v>
       </c>
       <c r="C293">
-        <v>1207</v>
+        <v>4107</v>
       </c>
       <c r="D293">
-        <v>11102</v>
+        <v>40806</v>
       </c>
       <c r="E293">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F293">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="G293" t="s">
         <v>503</v>
@@ -21063,63 +21412,63 @@
         <v>35</v>
       </c>
       <c r="I293">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="J293">
         <v>1</v>
       </c>
       <c r="K293" t="s">
-        <v>779</v>
+        <v>825</v>
       </c>
       <c r="L293">
-        <v>58733</v>
+        <v>57992</v>
       </c>
       <c r="M293">
         <v>1</v>
       </c>
-      <c r="N293" s="2">
-        <v>66551</v>
+      <c r="N293" t="s">
+        <v>826</v>
       </c>
       <c r="O293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P293">
+        <v>400000</v>
+      </c>
+      <c r="Q293">
+        <v>0</v>
+      </c>
+      <c r="R293">
+        <v>0</v>
+      </c>
+      <c r="S293">
+        <v>1</v>
+      </c>
+      <c r="T293">
+        <v>2</v>
+      </c>
+      <c r="U293">
         <v>200000</v>
-      </c>
-      <c r="Q293">
-        <v>24</v>
-      </c>
-      <c r="R293">
-        <v>2</v>
-      </c>
-      <c r="S293">
-        <v>0</v>
-      </c>
-      <c r="T293">
-        <v>3</v>
-      </c>
-      <c r="U293">
-        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>12134</v>
+        <v>11963</v>
       </c>
       <c r="B294" t="s">
-        <v>780</v>
+        <v>824</v>
       </c>
       <c r="C294">
-        <v>2616</v>
+        <v>4107</v>
       </c>
       <c r="D294">
-        <v>20501</v>
+        <v>40806</v>
       </c>
       <c r="E294">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F294">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="G294" t="s">
         <v>503</v>
@@ -21128,63 +21477,63 @@
         <v>35</v>
       </c>
       <c r="I294">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J294">
         <v>1</v>
       </c>
       <c r="K294" t="s">
-        <v>214</v>
+        <v>532</v>
       </c>
       <c r="L294">
-        <v>58878</v>
+        <v>57992</v>
       </c>
       <c r="M294">
         <v>1</v>
       </c>
-      <c r="N294" s="2">
-        <v>66631</v>
+      <c r="N294" t="s">
+        <v>827</v>
       </c>
       <c r="O294">
         <v>4</v>
       </c>
       <c r="P294">
-        <v>150000</v>
+        <v>60000</v>
       </c>
       <c r="Q294">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="R294">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="S294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T294">
         <v>2</v>
       </c>
       <c r="U294">
-        <v>10000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="295" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>12207</v>
+        <v>11971</v>
       </c>
       <c r="B295" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="C295">
-        <v>7102</v>
+        <v>4207</v>
       </c>
       <c r="D295">
-        <v>70210</v>
+        <v>40806</v>
       </c>
       <c r="E295">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F295">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G295" t="s">
         <v>503</v>
@@ -21193,63 +21542,63 @@
         <v>35</v>
       </c>
       <c r="I295">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="J295">
         <v>1</v>
       </c>
       <c r="K295" t="s">
-        <v>782</v>
+        <v>313</v>
       </c>
       <c r="L295">
-        <v>59217</v>
+        <v>58034</v>
       </c>
       <c r="M295">
-        <v>1</v>
-      </c>
-      <c r="N295" s="2">
-        <v>65809</v>
+        <v>4</v>
+      </c>
+      <c r="N295" t="s">
+        <v>205</v>
       </c>
       <c r="O295">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P295">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="Q295">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R295">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T295">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U295">
-        <v>100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>12256</v>
+        <v>11971</v>
       </c>
       <c r="B296" t="s">
-        <v>783</v>
+        <v>828</v>
       </c>
       <c r="C296">
-        <v>7305</v>
+        <v>4207</v>
       </c>
       <c r="D296">
-        <v>70502</v>
+        <v>40806</v>
       </c>
       <c r="E296">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F296">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G296" t="s">
         <v>503</v>
@@ -21258,37 +21607,37 @@
         <v>35</v>
       </c>
       <c r="I296">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="J296">
         <v>1</v>
       </c>
       <c r="K296" t="s">
-        <v>766</v>
+        <v>829</v>
       </c>
       <c r="L296">
-        <v>59452</v>
+        <v>58034</v>
       </c>
       <c r="M296">
-        <v>1</v>
-      </c>
-      <c r="N296" s="2">
-        <v>65876</v>
+        <v>4</v>
+      </c>
+      <c r="N296" t="s">
+        <v>751</v>
       </c>
       <c r="O296">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P296">
-        <v>250000</v>
+        <v>50000</v>
       </c>
       <c r="Q296">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R296">
-        <v>60000</v>
-      </c>
-      <c r="S296" t="s">
-        <v>93</v>
+        <v>0</v>
+      </c>
+      <c r="S296">
+        <v>1</v>
       </c>
       <c r="T296">
         <v>3</v>
@@ -21299,22 +21648,22 @@
     </row>
     <row r="297" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>13509</v>
+        <v>11971</v>
       </c>
       <c r="B297" t="s">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="C297">
-        <v>3416</v>
+        <v>4207</v>
       </c>
       <c r="D297">
-        <v>30610</v>
+        <v>40806</v>
       </c>
       <c r="E297">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F297">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G297" t="s">
         <v>503</v>
@@ -21323,28 +21672,28 @@
         <v>35</v>
       </c>
       <c r="I297">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J297">
         <v>1</v>
       </c>
       <c r="K297" t="s">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="L297">
-        <v>5948366</v>
+        <v>58034</v>
       </c>
       <c r="M297">
-        <v>1</v>
-      </c>
-      <c r="N297" s="2">
-        <v>66567</v>
+        <v>4</v>
+      </c>
+      <c r="N297" t="s">
+        <v>448</v>
       </c>
       <c r="O297">
         <v>5</v>
       </c>
       <c r="P297">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -21353,30 +21702,33 @@
         <v>0</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T297">
         <v>3</v>
+      </c>
+      <c r="U297">
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>13553</v>
+        <v>11992</v>
       </c>
       <c r="B298" t="s">
-        <v>722</v>
+        <v>830</v>
       </c>
       <c r="C298">
-        <v>3115</v>
+        <v>4107</v>
       </c>
       <c r="D298">
-        <v>31304</v>
+        <v>40806</v>
       </c>
       <c r="E298">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F298">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G298" t="s">
         <v>503</v>
@@ -21391,57 +21743,54 @@
         <v>1</v>
       </c>
       <c r="K298" t="s">
-        <v>723</v>
+        <v>255</v>
       </c>
       <c r="L298">
-        <v>5948594</v>
+        <v>58136</v>
       </c>
       <c r="M298">
-        <v>2</v>
-      </c>
-      <c r="N298" s="2">
-        <v>62094</v>
+        <v>1</v>
+      </c>
+      <c r="N298" t="s">
+        <v>776</v>
       </c>
       <c r="O298">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P298">
-        <v>800000</v>
+        <v>50000</v>
       </c>
       <c r="Q298">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R298">
-        <v>192000</v>
+        <v>0</v>
       </c>
       <c r="S298" t="s">
-        <v>724</v>
+        <v>307</v>
       </c>
       <c r="T298">
         <v>3</v>
-      </c>
-      <c r="U298">
-        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>13553</v>
+        <v>12106</v>
       </c>
       <c r="B299" t="s">
-        <v>722</v>
+        <v>831</v>
       </c>
       <c r="C299">
-        <v>3115</v>
+        <v>1207</v>
       </c>
       <c r="D299">
-        <v>31304</v>
+        <v>11102</v>
       </c>
       <c r="E299">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F299">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G299" t="s">
         <v>503</v>
@@ -21450,37 +21799,37 @@
         <v>35</v>
       </c>
       <c r="I299">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="J299">
         <v>1</v>
       </c>
       <c r="K299" t="s">
-        <v>255</v>
+        <v>832</v>
       </c>
       <c r="L299">
-        <v>5948594</v>
+        <v>58733</v>
       </c>
       <c r="M299">
-        <v>2</v>
-      </c>
-      <c r="N299" s="2">
-        <v>62125</v>
+        <v>1</v>
+      </c>
+      <c r="N299" t="s">
+        <v>833</v>
       </c>
       <c r="O299">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P299">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q299">
         <v>24</v>
       </c>
       <c r="R299">
-        <v>72000</v>
-      </c>
-      <c r="S299" t="s">
-        <v>196</v>
+        <v>2</v>
+      </c>
+      <c r="S299">
+        <v>0</v>
       </c>
       <c r="T299">
         <v>3</v>
@@ -21491,22 +21840,22 @@
     </row>
     <row r="300" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>13553</v>
+        <v>12134</v>
       </c>
       <c r="B300" t="s">
-        <v>722</v>
+        <v>834</v>
       </c>
       <c r="C300">
-        <v>3115</v>
+        <v>2616</v>
       </c>
       <c r="D300">
-        <v>31304</v>
+        <v>20501</v>
       </c>
       <c r="E300">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F300">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G300" t="s">
         <v>503</v>
@@ -21515,63 +21864,63 @@
         <v>35</v>
       </c>
       <c r="I300">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="J300">
         <v>1</v>
       </c>
       <c r="K300" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="L300">
-        <v>5948594</v>
+        <v>58878</v>
       </c>
       <c r="M300">
-        <v>2</v>
-      </c>
-      <c r="N300" s="2">
-        <v>63715</v>
+        <v>1</v>
+      </c>
+      <c r="N300" t="s">
+        <v>835</v>
       </c>
       <c r="O300">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P300">
-        <v>1000000</v>
+        <v>150000</v>
       </c>
       <c r="Q300">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R300">
-        <v>240000</v>
-      </c>
-      <c r="S300" t="s">
-        <v>196</v>
+        <v>0</v>
+      </c>
+      <c r="S300">
+        <v>2</v>
       </c>
       <c r="T300">
         <v>2</v>
       </c>
       <c r="U300">
-        <v>800000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="301" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>13554</v>
+        <v>12207</v>
       </c>
       <c r="B301" t="s">
-        <v>720</v>
+        <v>836</v>
       </c>
       <c r="C301">
-        <v>3115</v>
+        <v>7102</v>
       </c>
       <c r="D301">
-        <v>31304</v>
+        <v>70210</v>
       </c>
       <c r="E301">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F301">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G301" t="s">
         <v>503</v>
@@ -21580,60 +21929,63 @@
         <v>35</v>
       </c>
       <c r="I301">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="J301">
         <v>1</v>
       </c>
       <c r="K301" t="s">
-        <v>721</v>
+        <v>837</v>
       </c>
       <c r="L301">
-        <v>5948602</v>
+        <v>59217</v>
       </c>
       <c r="M301">
         <v>1</v>
       </c>
-      <c r="N301" s="2">
-        <v>64651</v>
+      <c r="N301" t="s">
+        <v>360</v>
       </c>
       <c r="O301">
         <v>4</v>
       </c>
       <c r="P301">
-        <v>1200000</v>
+        <v>200000</v>
       </c>
       <c r="Q301">
-        <v>18</v>
-      </c>
-      <c r="S301" t="s">
-        <v>557</v>
+        <v>24</v>
+      </c>
+      <c r="R301">
+        <v>24</v>
+      </c>
+      <c r="S301">
+        <v>0</v>
       </c>
       <c r="T301">
         <v>2</v>
       </c>
       <c r="U301">
-        <v>400000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="302" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>13572</v>
+        <v>12212</v>
       </c>
       <c r="B302" t="s">
-        <v>785</v>
+        <v>838</v>
       </c>
       <c r="C302">
-        <v>2106</v>
+        <v>2601</v>
       </c>
       <c r="D302">
-        <v>20514</v>
+        <v>20315</v>
       </c>
       <c r="E302">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F302">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G302" t="s">
         <v>503</v>
@@ -21642,37 +21994,37 @@
         <v>35</v>
       </c>
       <c r="I302">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J302">
         <v>1</v>
       </c>
       <c r="K302" t="s">
-        <v>786</v>
+        <v>652</v>
       </c>
       <c r="L302">
-        <v>5948691</v>
+        <v>59236</v>
       </c>
       <c r="M302">
-        <v>12</v>
-      </c>
-      <c r="N302" s="2">
-        <v>66540</v>
+        <v>2</v>
+      </c>
+      <c r="N302" t="s">
+        <v>839</v>
       </c>
       <c r="O302">
         <v>4</v>
       </c>
       <c r="P302">
-        <v>150000</v>
+        <v>25</v>
       </c>
       <c r="Q302">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R302">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S302">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T302">
         <v>3</v>
@@ -21683,22 +22035,19 @@
     </row>
     <row r="303" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>13573</v>
+        <v>12219</v>
       </c>
       <c r="B303" t="s">
-        <v>787</v>
+        <v>840</v>
       </c>
       <c r="C303">
-        <v>2206</v>
-      </c>
-      <c r="D303">
-        <v>20514</v>
+        <v>3630</v>
       </c>
       <c r="E303">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F303">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G303" t="s">
         <v>503</v>
@@ -21707,63 +22056,54 @@
         <v>35</v>
       </c>
       <c r="I303">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="J303">
         <v>1</v>
       </c>
       <c r="K303" t="s">
-        <v>788</v>
+        <v>841</v>
       </c>
       <c r="L303">
-        <v>5948692</v>
+        <v>59275</v>
       </c>
       <c r="M303">
         <v>1</v>
       </c>
-      <c r="N303" s="2">
-        <v>66236</v>
-      </c>
       <c r="O303">
         <v>4</v>
       </c>
       <c r="P303">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="Q303">
-        <v>24</v>
+        <v>5000</v>
       </c>
       <c r="R303">
         <v>0</v>
       </c>
-      <c r="S303">
-        <v>1</v>
-      </c>
       <c r="T303">
         <v>3</v>
-      </c>
-      <c r="U303">
-        <v>0</v>
       </c>
     </row>
     <row r="304" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>13575</v>
+        <v>12256</v>
       </c>
       <c r="B304" t="s">
-        <v>789</v>
+        <v>842</v>
       </c>
       <c r="C304">
-        <v>2106</v>
+        <v>7305</v>
       </c>
       <c r="D304">
-        <v>20514</v>
+        <v>70502</v>
       </c>
       <c r="E304">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F304">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G304" t="s">
         <v>503</v>
@@ -21772,63 +22112,63 @@
         <v>35</v>
       </c>
       <c r="I304">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="J304">
         <v>1</v>
       </c>
       <c r="K304" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="L304">
-        <v>5948706</v>
+        <v>59452</v>
       </c>
       <c r="M304">
         <v>1</v>
       </c>
-      <c r="N304" s="2">
-        <v>64867</v>
+      <c r="N304" t="s">
+        <v>843</v>
       </c>
       <c r="O304">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P304">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="Q304">
         <v>24</v>
       </c>
       <c r="R304">
-        <v>0</v>
-      </c>
-      <c r="S304">
-        <v>1</v>
+        <v>60000</v>
+      </c>
+      <c r="S304" t="s">
+        <v>93</v>
       </c>
       <c r="T304">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U304">
-        <v>36000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>13578</v>
+        <v>12279</v>
       </c>
       <c r="B305" t="s">
-        <v>791</v>
+        <v>844</v>
       </c>
       <c r="C305">
-        <v>2206</v>
+        <v>5109</v>
       </c>
       <c r="D305">
-        <v>20514</v>
+        <v>51105</v>
       </c>
       <c r="E305">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F305">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G305" t="s">
         <v>503</v>
@@ -21837,63 +22177,63 @@
         <v>35</v>
       </c>
       <c r="I305">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J305">
         <v>1</v>
       </c>
       <c r="K305" t="s">
-        <v>792</v>
+        <v>209</v>
       </c>
       <c r="L305">
-        <v>5948721</v>
+        <v>59561</v>
       </c>
       <c r="M305">
-        <v>1</v>
-      </c>
-      <c r="N305" s="2">
-        <v>64836</v>
+        <v>3</v>
+      </c>
+      <c r="N305" t="s">
+        <v>845</v>
       </c>
       <c r="O305">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P305">
-        <v>360000</v>
+        <v>200000</v>
       </c>
       <c r="Q305">
         <v>24</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S305">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T305">
         <v>2</v>
       </c>
       <c r="U305">
-        <v>40000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="306" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>13589</v>
+        <v>12321</v>
       </c>
       <c r="B306" t="s">
-        <v>793</v>
+        <v>846</v>
       </c>
       <c r="C306">
-        <v>3504</v>
+        <v>5111</v>
       </c>
       <c r="D306">
-        <v>30602</v>
+        <v>51108</v>
       </c>
       <c r="E306">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F306">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G306" t="s">
         <v>503</v>
@@ -21902,60 +22242,63 @@
         <v>35</v>
       </c>
       <c r="I306">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="J306">
         <v>1</v>
       </c>
       <c r="K306" t="s">
-        <v>794</v>
+        <v>847</v>
       </c>
       <c r="L306">
-        <v>5948774</v>
+        <v>59758</v>
       </c>
       <c r="M306">
-        <v>1</v>
-      </c>
-      <c r="N306" s="2">
-        <v>66481</v>
+        <v>2</v>
+      </c>
+      <c r="N306" t="s">
+        <v>848</v>
       </c>
       <c r="O306">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P306">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="Q306">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R306">
         <v>0</v>
       </c>
       <c r="S306">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T306">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U306">
-        <v>50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>13601</v>
+        <v>12355</v>
       </c>
       <c r="B307" t="s">
-        <v>795</v>
+        <v>849</v>
       </c>
       <c r="C307">
-        <v>3603</v>
+        <v>1416</v>
+      </c>
+      <c r="D307">
+        <v>11101</v>
       </c>
       <c r="E307">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F307">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G307" t="s">
         <v>503</v>
@@ -21970,28 +22313,28 @@
         <v>1</v>
       </c>
       <c r="K307" t="s">
-        <v>796</v>
+        <v>428</v>
       </c>
       <c r="L307">
-        <v>5948829</v>
+        <v>59928</v>
       </c>
       <c r="M307">
         <v>1</v>
       </c>
-      <c r="N307" s="2">
-        <v>65471</v>
-      </c>
       <c r="O307">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P307">
-        <v>250000</v>
+        <v>20000</v>
       </c>
       <c r="Q307">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R307">
         <v>0</v>
+      </c>
+      <c r="S307" t="s">
+        <v>78</v>
       </c>
       <c r="T307">
         <v>3</v>
@@ -22002,19 +22345,22 @@
     </row>
     <row r="308" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>13601</v>
+        <v>12359</v>
       </c>
       <c r="B308" t="s">
-        <v>795</v>
+        <v>850</v>
       </c>
       <c r="C308">
-        <v>3603</v>
+        <v>1316</v>
+      </c>
+      <c r="D308">
+        <v>11101</v>
       </c>
       <c r="E308">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F308">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G308" t="s">
         <v>503</v>
@@ -22029,31 +22375,31 @@
         <v>1</v>
       </c>
       <c r="K308" t="s">
-        <v>749</v>
+        <v>778</v>
       </c>
       <c r="L308">
-        <v>5948829</v>
+        <v>59944</v>
       </c>
       <c r="M308">
-        <v>1</v>
-      </c>
-      <c r="N308" s="2">
-        <v>66118</v>
+        <v>2</v>
+      </c>
+      <c r="N308" t="s">
+        <v>851</v>
       </c>
       <c r="O308">
         <v>5</v>
       </c>
       <c r="P308">
-        <v>140000</v>
+        <v>120000</v>
       </c>
       <c r="Q308">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R308">
         <v>0</v>
       </c>
       <c r="S308">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T308">
         <v>3</v>
@@ -22064,19 +22410,22 @@
     </row>
     <row r="309" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>13603</v>
+        <v>12359</v>
       </c>
       <c r="B309" t="s">
-        <v>797</v>
+        <v>850</v>
       </c>
       <c r="C309">
-        <v>3676</v>
+        <v>1316</v>
+      </c>
+      <c r="D309">
+        <v>11101</v>
       </c>
       <c r="E309">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F309">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G309" t="s">
         <v>503</v>
@@ -22091,31 +22440,28 @@
         <v>1</v>
       </c>
       <c r="K309" t="s">
-        <v>749</v>
+        <v>699</v>
       </c>
       <c r="L309">
-        <v>5948837</v>
+        <v>59944</v>
       </c>
       <c r="M309">
         <v>2</v>
-      </c>
-      <c r="N309" s="2">
-        <v>66297</v>
       </c>
       <c r="O309">
         <v>5</v>
       </c>
       <c r="P309">
-        <v>200000</v>
+        <v>25000</v>
       </c>
       <c r="Q309">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R309">
         <v>0</v>
       </c>
-      <c r="S309" t="s">
-        <v>294</v>
+      <c r="S309">
+        <v>1</v>
       </c>
       <c r="T309">
         <v>3</v>
@@ -22126,22 +22472,22 @@
     </row>
     <row r="310" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>13647</v>
+        <v>12361</v>
       </c>
       <c r="B310" t="s">
-        <v>798</v>
+        <v>852</v>
       </c>
       <c r="C310">
-        <v>6310</v>
+        <v>1316</v>
       </c>
       <c r="D310">
-        <v>61006</v>
+        <v>11101</v>
       </c>
       <c r="E310">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F310">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G310" t="s">
         <v>503</v>
@@ -22150,63 +22496,60 @@
         <v>35</v>
       </c>
       <c r="I310">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="J310">
         <v>1</v>
       </c>
       <c r="K310" t="s">
-        <v>799</v>
+        <v>853</v>
       </c>
       <c r="L310">
-        <v>5949020</v>
+        <v>59954</v>
       </c>
       <c r="M310">
         <v>1</v>
       </c>
-      <c r="N310" s="2">
-        <v>66364</v>
+      <c r="N310" t="s">
+        <v>854</v>
       </c>
       <c r="O310">
         <v>4</v>
       </c>
       <c r="P310">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="Q310">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R310">
-        <v>24000</v>
-      </c>
-      <c r="S310" t="s">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="T310">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U310">
-        <v>25000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>13721</v>
+        <v>12364</v>
       </c>
       <c r="B311" t="s">
-        <v>800</v>
+        <v>855</v>
       </c>
       <c r="C311">
-        <v>6408</v>
+        <v>1316</v>
       </c>
       <c r="D311">
-        <v>60608</v>
+        <v>11101</v>
       </c>
       <c r="E311">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F311">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G311" t="s">
         <v>503</v>
@@ -22215,37 +22558,37 @@
         <v>35</v>
       </c>
       <c r="I311">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="J311">
         <v>1</v>
       </c>
       <c r="K311" t="s">
-        <v>766</v>
+        <v>856</v>
       </c>
       <c r="L311">
-        <v>5949340</v>
+        <v>59966</v>
       </c>
       <c r="M311">
         <v>1</v>
       </c>
-      <c r="N311" s="2">
-        <v>66209</v>
+      <c r="N311" t="s">
+        <v>857</v>
       </c>
       <c r="O311">
         <v>4</v>
       </c>
       <c r="P311">
-        <v>100000</v>
+        <v>25000</v>
       </c>
       <c r="Q311">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R311">
-        <v>24000</v>
-      </c>
-      <c r="S311" t="s">
-        <v>764</v>
+        <v>0</v>
+      </c>
+      <c r="S311">
+        <v>1</v>
       </c>
       <c r="T311">
         <v>3</v>
@@ -22256,22 +22599,22 @@
     </row>
     <row r="312" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>13743</v>
+        <v>12367</v>
       </c>
       <c r="B312" t="s">
-        <v>801</v>
+        <v>858</v>
       </c>
       <c r="C312">
-        <v>3542</v>
+        <v>1417</v>
       </c>
       <c r="D312">
-        <v>30802</v>
+        <v>11307</v>
       </c>
       <c r="E312">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F312">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G312" t="s">
         <v>503</v>
@@ -22280,57 +22623,63 @@
         <v>35</v>
       </c>
       <c r="I312">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="J312">
         <v>1</v>
       </c>
       <c r="K312" t="s">
-        <v>802</v>
+        <v>778</v>
       </c>
       <c r="L312">
-        <v>5949430</v>
+        <v>59975</v>
       </c>
       <c r="M312">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N312" t="s">
+        <v>859</v>
       </c>
       <c r="O312">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P312">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="Q312">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R312">
         <v>0</v>
       </c>
       <c r="S312">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T312">
         <v>3</v>
+      </c>
+      <c r="U312">
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>13779</v>
+        <v>12418</v>
       </c>
       <c r="B313" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="C313">
-        <v>6316</v>
+        <v>2500</v>
       </c>
       <c r="D313">
-        <v>61006</v>
+        <v>20315</v>
       </c>
       <c r="E313">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F313">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G313" t="s">
         <v>503</v>
@@ -22339,60 +22688,63 @@
         <v>35</v>
       </c>
       <c r="I313">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="J313">
         <v>1</v>
       </c>
       <c r="K313" t="s">
-        <v>255</v>
+        <v>861</v>
       </c>
       <c r="L313">
-        <v>5949559</v>
+        <v>60208</v>
       </c>
       <c r="M313">
-        <v>1</v>
-      </c>
-      <c r="N313" s="2">
-        <v>65876</v>
+        <v>2</v>
+      </c>
+      <c r="N313" t="s">
+        <v>862</v>
       </c>
       <c r="O313">
         <v>4</v>
       </c>
       <c r="P313">
-        <v>200000</v>
+        <v>75000</v>
       </c>
       <c r="Q313">
         <v>24</v>
       </c>
       <c r="R313">
-        <v>48000</v>
-      </c>
-      <c r="S313" t="s">
-        <v>93</v>
+        <v>0</v>
+      </c>
+      <c r="S313">
+        <v>1</v>
       </c>
       <c r="T313">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U313">
-        <v>50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>14006</v>
+        <v>12434</v>
       </c>
       <c r="B314" t="s">
-        <v>804</v>
+        <v>863</v>
       </c>
       <c r="C314">
-        <v>3646</v>
+        <v>3411</v>
+      </c>
+      <c r="D314">
+        <v>31304</v>
       </c>
       <c r="E314">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F314">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G314" t="s">
         <v>503</v>
@@ -22401,10 +22753,1664 @@
         <v>35</v>
       </c>
       <c r="I314">
+        <v>25</v>
+      </c>
+      <c r="J314">
+        <v>1</v>
+      </c>
+      <c r="K314" t="s">
+        <v>864</v>
+      </c>
+      <c r="L314">
+        <v>60283</v>
+      </c>
+      <c r="M314">
+        <v>2</v>
+      </c>
+      <c r="N314" t="s">
+        <v>338</v>
+      </c>
+      <c r="O314">
+        <v>4</v>
+      </c>
+      <c r="P314">
+        <v>500000</v>
+      </c>
+      <c r="Q314">
+        <v>24</v>
+      </c>
+      <c r="R314">
+        <v>0</v>
+      </c>
+      <c r="S314" t="s">
+        <v>865</v>
+      </c>
+      <c r="T314">
+        <v>2</v>
+      </c>
+      <c r="U314">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="315" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>12434</v>
+      </c>
+      <c r="B315" t="s">
+        <v>863</v>
+      </c>
+      <c r="C315">
+        <v>3411</v>
+      </c>
+      <c r="D315">
+        <v>31304</v>
+      </c>
+      <c r="E315">
+        <v>2</v>
+      </c>
+      <c r="F315">
+        <v>31</v>
+      </c>
+      <c r="G315" t="s">
+        <v>503</v>
+      </c>
+      <c r="H315" t="s">
+        <v>35</v>
+      </c>
+      <c r="I315">
+        <v>25</v>
+      </c>
+      <c r="J315">
+        <v>1</v>
+      </c>
+      <c r="K315" t="s">
+        <v>225</v>
+      </c>
+      <c r="L315">
+        <v>60283</v>
+      </c>
+      <c r="M315">
+        <v>2</v>
+      </c>
+      <c r="N315" t="s">
+        <v>866</v>
+      </c>
+      <c r="O315">
+        <v>4</v>
+      </c>
+      <c r="P315">
+        <v>250000</v>
+      </c>
+      <c r="Q315">
+        <v>10</v>
+      </c>
+      <c r="R315">
+        <v>0</v>
+      </c>
+      <c r="S315" t="s">
+        <v>867</v>
+      </c>
+      <c r="T315">
+        <v>2</v>
+      </c>
+      <c r="U315">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="316" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>12482</v>
+      </c>
+      <c r="B316" t="s">
+        <v>868</v>
+      </c>
+      <c r="C316">
+        <v>3530</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>31</v>
+      </c>
+      <c r="G316" t="s">
+        <v>503</v>
+      </c>
+      <c r="H316" t="s">
+        <v>35</v>
+      </c>
+      <c r="I316">
+        <v>56</v>
+      </c>
+      <c r="J316">
+        <v>1</v>
+      </c>
+      <c r="K316" t="s">
+        <v>869</v>
+      </c>
+      <c r="L316">
+        <v>60524</v>
+      </c>
+      <c r="M316">
+        <v>1</v>
+      </c>
+      <c r="O316">
+        <v>4</v>
+      </c>
+      <c r="P316">
+        <v>200000</v>
+      </c>
+      <c r="Q316">
+        <v>3</v>
+      </c>
+      <c r="R316">
+        <v>3</v>
+      </c>
+      <c r="S316">
+        <v>5</v>
+      </c>
+      <c r="T316">
+        <v>2</v>
+      </c>
+      <c r="U316">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="317" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>13509</v>
+      </c>
+      <c r="B317" t="s">
+        <v>870</v>
+      </c>
+      <c r="C317">
+        <v>3416</v>
+      </c>
+      <c r="D317">
+        <v>30610</v>
+      </c>
+      <c r="E317">
+        <v>3</v>
+      </c>
+      <c r="F317">
+        <v>44</v>
+      </c>
+      <c r="G317" t="s">
+        <v>503</v>
+      </c>
+      <c r="H317" t="s">
+        <v>35</v>
+      </c>
+      <c r="I317">
+        <v>51</v>
+      </c>
+      <c r="J317">
+        <v>1</v>
+      </c>
+      <c r="K317" t="s">
+        <v>255</v>
+      </c>
+      <c r="L317">
+        <v>5948366</v>
+      </c>
+      <c r="M317">
+        <v>1</v>
+      </c>
+      <c r="N317" t="s">
+        <v>871</v>
+      </c>
+      <c r="O317">
+        <v>5</v>
+      </c>
+      <c r="P317">
+        <v>100000</v>
+      </c>
+      <c r="Q317">
+        <v>0</v>
+      </c>
+      <c r="R317">
+        <v>0</v>
+      </c>
+      <c r="S317">
+        <v>0</v>
+      </c>
+      <c r="T317">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>13553</v>
+      </c>
+      <c r="B318" t="s">
+        <v>872</v>
+      </c>
+      <c r="C318">
+        <v>3115</v>
+      </c>
+      <c r="D318">
+        <v>31304</v>
+      </c>
+      <c r="E318">
+        <v>4</v>
+      </c>
+      <c r="F318">
+        <v>13</v>
+      </c>
+      <c r="G318" t="s">
+        <v>503</v>
+      </c>
+      <c r="H318" t="s">
+        <v>35</v>
+      </c>
+      <c r="I318">
+        <v>51</v>
+      </c>
+      <c r="J318">
+        <v>1</v>
+      </c>
+      <c r="K318" t="s">
+        <v>873</v>
+      </c>
+      <c r="L318">
+        <v>5948594</v>
+      </c>
+      <c r="M318">
+        <v>2</v>
+      </c>
+      <c r="N318" t="s">
+        <v>874</v>
+      </c>
+      <c r="O318">
+        <v>4</v>
+      </c>
+      <c r="P318">
+        <v>800000</v>
+      </c>
+      <c r="Q318">
+        <v>24</v>
+      </c>
+      <c r="R318">
+        <v>192000</v>
+      </c>
+      <c r="S318" t="s">
+        <v>875</v>
+      </c>
+      <c r="T318">
+        <v>3</v>
+      </c>
+      <c r="U318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>13553</v>
+      </c>
+      <c r="B319" t="s">
+        <v>872</v>
+      </c>
+      <c r="C319">
+        <v>3115</v>
+      </c>
+      <c r="D319">
+        <v>31304</v>
+      </c>
+      <c r="E319">
+        <v>4</v>
+      </c>
+      <c r="F319">
+        <v>13</v>
+      </c>
+      <c r="G319" t="s">
+        <v>503</v>
+      </c>
+      <c r="H319" t="s">
+        <v>35</v>
+      </c>
+      <c r="I319">
+        <v>51</v>
+      </c>
+      <c r="J319">
+        <v>1</v>
+      </c>
+      <c r="K319" t="s">
+        <v>255</v>
+      </c>
+      <c r="L319">
+        <v>5948594</v>
+      </c>
+      <c r="M319">
+        <v>2</v>
+      </c>
+      <c r="N319" t="s">
+        <v>876</v>
+      </c>
+      <c r="O319">
+        <v>5</v>
+      </c>
+      <c r="P319">
+        <v>300000</v>
+      </c>
+      <c r="Q319">
+        <v>24</v>
+      </c>
+      <c r="R319">
+        <v>72000</v>
+      </c>
+      <c r="S319" t="s">
+        <v>196</v>
+      </c>
+      <c r="T319">
+        <v>3</v>
+      </c>
+      <c r="U319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>13553</v>
+      </c>
+      <c r="B320" t="s">
+        <v>872</v>
+      </c>
+      <c r="C320">
+        <v>3115</v>
+      </c>
+      <c r="D320">
+        <v>31304</v>
+      </c>
+      <c r="E320">
+        <v>4</v>
+      </c>
+      <c r="F320">
+        <v>13</v>
+      </c>
+      <c r="G320" t="s">
+        <v>503</v>
+      </c>
+      <c r="H320" t="s">
+        <v>35</v>
+      </c>
+      <c r="I320">
+        <v>51</v>
+      </c>
+      <c r="J320">
+        <v>1</v>
+      </c>
+      <c r="K320" t="s">
+        <v>255</v>
+      </c>
+      <c r="L320">
+        <v>5948594</v>
+      </c>
+      <c r="M320">
+        <v>2</v>
+      </c>
+      <c r="N320" t="s">
+        <v>877</v>
+      </c>
+      <c r="O320">
+        <v>5</v>
+      </c>
+      <c r="P320">
+        <v>1000000</v>
+      </c>
+      <c r="Q320">
+        <v>24</v>
+      </c>
+      <c r="R320">
+        <v>240000</v>
+      </c>
+      <c r="S320" t="s">
+        <v>196</v>
+      </c>
+      <c r="T320">
+        <v>2</v>
+      </c>
+      <c r="U320">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="321" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>13554</v>
+      </c>
+      <c r="B321" t="s">
+        <v>878</v>
+      </c>
+      <c r="C321">
+        <v>3115</v>
+      </c>
+      <c r="D321">
+        <v>31304</v>
+      </c>
+      <c r="E321">
+        <v>4</v>
+      </c>
+      <c r="F321">
+        <v>12</v>
+      </c>
+      <c r="G321" t="s">
+        <v>503</v>
+      </c>
+      <c r="H321" t="s">
+        <v>35</v>
+      </c>
+      <c r="I321">
+        <v>51</v>
+      </c>
+      <c r="J321">
+        <v>1</v>
+      </c>
+      <c r="K321" t="s">
+        <v>879</v>
+      </c>
+      <c r="L321">
+        <v>5948602</v>
+      </c>
+      <c r="M321">
+        <v>1</v>
+      </c>
+      <c r="N321" t="s">
+        <v>880</v>
+      </c>
+      <c r="O321">
+        <v>4</v>
+      </c>
+      <c r="P321">
+        <v>1200000</v>
+      </c>
+      <c r="Q321">
+        <v>18</v>
+      </c>
+      <c r="S321" t="s">
+        <v>557</v>
+      </c>
+      <c r="T321">
+        <v>2</v>
+      </c>
+      <c r="U321">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="322" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>13572</v>
+      </c>
+      <c r="B322" t="s">
+        <v>881</v>
+      </c>
+      <c r="C322">
+        <v>2106</v>
+      </c>
+      <c r="D322">
+        <v>20514</v>
+      </c>
+      <c r="E322">
+        <v>6</v>
+      </c>
+      <c r="F322">
+        <v>46</v>
+      </c>
+      <c r="G322" t="s">
+        <v>503</v>
+      </c>
+      <c r="H322" t="s">
+        <v>35</v>
+      </c>
+      <c r="I322">
+        <v>24</v>
+      </c>
+      <c r="J322">
+        <v>1</v>
+      </c>
+      <c r="K322" t="s">
+        <v>882</v>
+      </c>
+      <c r="L322">
+        <v>5948691</v>
+      </c>
+      <c r="M322">
+        <v>12</v>
+      </c>
+      <c r="N322" t="s">
+        <v>857</v>
+      </c>
+      <c r="O322">
+        <v>4</v>
+      </c>
+      <c r="P322">
+        <v>150000</v>
+      </c>
+      <c r="Q322">
+        <v>24</v>
+      </c>
+      <c r="R322">
+        <v>24</v>
+      </c>
+      <c r="S322">
+        <v>2</v>
+      </c>
+      <c r="T322">
+        <v>3</v>
+      </c>
+      <c r="U322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>13573</v>
+      </c>
+      <c r="B323" t="s">
+        <v>883</v>
+      </c>
+      <c r="C323">
+        <v>2206</v>
+      </c>
+      <c r="D323">
+        <v>20514</v>
+      </c>
+      <c r="E323">
+        <v>6</v>
+      </c>
+      <c r="F323">
+        <v>47</v>
+      </c>
+      <c r="G323" t="s">
+        <v>503</v>
+      </c>
+      <c r="H323" t="s">
+        <v>35</v>
+      </c>
+      <c r="I323">
+        <v>24</v>
+      </c>
+      <c r="J323">
+        <v>1</v>
+      </c>
+      <c r="K323" t="s">
+        <v>884</v>
+      </c>
+      <c r="L323">
+        <v>5948692</v>
+      </c>
+      <c r="M323">
+        <v>1</v>
+      </c>
+      <c r="N323" t="s">
+        <v>885</v>
+      </c>
+      <c r="O323">
+        <v>4</v>
+      </c>
+      <c r="P323">
+        <v>200000</v>
+      </c>
+      <c r="Q323">
+        <v>24</v>
+      </c>
+      <c r="R323">
+        <v>0</v>
+      </c>
+      <c r="S323">
+        <v>1</v>
+      </c>
+      <c r="T323">
+        <v>3</v>
+      </c>
+      <c r="U323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>13575</v>
+      </c>
+      <c r="B324" t="s">
+        <v>886</v>
+      </c>
+      <c r="C324">
+        <v>2106</v>
+      </c>
+      <c r="D324">
+        <v>20514</v>
+      </c>
+      <c r="E324">
+        <v>2</v>
+      </c>
+      <c r="F324">
+        <v>49</v>
+      </c>
+      <c r="G324" t="s">
+        <v>503</v>
+      </c>
+      <c r="H324" t="s">
+        <v>35</v>
+      </c>
+      <c r="I324">
+        <v>24</v>
+      </c>
+      <c r="J324">
+        <v>1</v>
+      </c>
+      <c r="K324" t="s">
+        <v>887</v>
+      </c>
+      <c r="L324">
+        <v>5948706</v>
+      </c>
+      <c r="M324">
+        <v>1</v>
+      </c>
+      <c r="N324" t="s">
+        <v>888</v>
+      </c>
+      <c r="O324">
+        <v>4</v>
+      </c>
+      <c r="P324">
+        <v>100000</v>
+      </c>
+      <c r="Q324">
+        <v>24</v>
+      </c>
+      <c r="R324">
+        <v>0</v>
+      </c>
+      <c r="S324">
+        <v>1</v>
+      </c>
+      <c r="T324">
+        <v>2</v>
+      </c>
+      <c r="U324">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="325" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>13578</v>
+      </c>
+      <c r="B325" t="s">
+        <v>889</v>
+      </c>
+      <c r="C325">
+        <v>2206</v>
+      </c>
+      <c r="D325">
+        <v>20514</v>
+      </c>
+      <c r="E325">
+        <v>2</v>
+      </c>
+      <c r="F325">
+        <v>52</v>
+      </c>
+      <c r="G325" t="s">
+        <v>503</v>
+      </c>
+      <c r="H325" t="s">
+        <v>35</v>
+      </c>
+      <c r="I325">
+        <v>24</v>
+      </c>
+      <c r="J325">
+        <v>1</v>
+      </c>
+      <c r="K325" t="s">
+        <v>890</v>
+      </c>
+      <c r="L325">
+        <v>5948721</v>
+      </c>
+      <c r="M325">
+        <v>1</v>
+      </c>
+      <c r="N325" t="s">
+        <v>891</v>
+      </c>
+      <c r="O325">
+        <v>4</v>
+      </c>
+      <c r="P325">
+        <v>360000</v>
+      </c>
+      <c r="Q325">
+        <v>24</v>
+      </c>
+      <c r="R325">
+        <v>0</v>
+      </c>
+      <c r="S325">
+        <v>4</v>
+      </c>
+      <c r="T325">
+        <v>2</v>
+      </c>
+      <c r="U325">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="326" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>13589</v>
+      </c>
+      <c r="B326" t="s">
+        <v>892</v>
+      </c>
+      <c r="C326">
+        <v>3504</v>
+      </c>
+      <c r="D326">
+        <v>30602</v>
+      </c>
+      <c r="E326">
+        <v>6</v>
+      </c>
+      <c r="F326">
+        <v>86</v>
+      </c>
+      <c r="G326" t="s">
+        <v>503</v>
+      </c>
+      <c r="H326" t="s">
+        <v>35</v>
+      </c>
+      <c r="I326">
+        <v>93</v>
+      </c>
+      <c r="J326">
+        <v>1</v>
+      </c>
+      <c r="K326" t="s">
+        <v>893</v>
+      </c>
+      <c r="L326">
+        <v>5948774</v>
+      </c>
+      <c r="M326">
+        <v>1</v>
+      </c>
+      <c r="N326" t="s">
+        <v>48</v>
+      </c>
+      <c r="O326">
+        <v>4</v>
+      </c>
+      <c r="P326">
+        <v>150000</v>
+      </c>
+      <c r="Q326">
+        <v>24</v>
+      </c>
+      <c r="R326">
+        <v>0</v>
+      </c>
+      <c r="S326">
+        <v>2</v>
+      </c>
+      <c r="T326">
+        <v>2</v>
+      </c>
+      <c r="U326">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="327" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>13601</v>
+      </c>
+      <c r="B327" t="s">
+        <v>894</v>
+      </c>
+      <c r="C327">
+        <v>3603</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>67</v>
+      </c>
+      <c r="G327" t="s">
+        <v>503</v>
+      </c>
+      <c r="H327" t="s">
+        <v>35</v>
+      </c>
+      <c r="I327">
+        <v>11</v>
+      </c>
+      <c r="J327">
+        <v>1</v>
+      </c>
+      <c r="K327" t="s">
+        <v>895</v>
+      </c>
+      <c r="L327">
+        <v>5948829</v>
+      </c>
+      <c r="M327">
+        <v>1</v>
+      </c>
+      <c r="N327" t="s">
+        <v>450</v>
+      </c>
+      <c r="O327">
+        <v>3</v>
+      </c>
+      <c r="P327">
+        <v>250000</v>
+      </c>
+      <c r="Q327">
+        <v>12</v>
+      </c>
+      <c r="R327">
+        <v>0</v>
+      </c>
+      <c r="T327">
+        <v>3</v>
+      </c>
+      <c r="U327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>13601</v>
+      </c>
+      <c r="B328" t="s">
+        <v>894</v>
+      </c>
+      <c r="C328">
+        <v>3603</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>67</v>
+      </c>
+      <c r="G328" t="s">
+        <v>503</v>
+      </c>
+      <c r="H328" t="s">
+        <v>35</v>
+      </c>
+      <c r="I328">
+        <v>11</v>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328" t="s">
+        <v>778</v>
+      </c>
+      <c r="L328">
+        <v>5948829</v>
+      </c>
+      <c r="M328">
+        <v>1</v>
+      </c>
+      <c r="N328" t="s">
+        <v>896</v>
+      </c>
+      <c r="O328">
+        <v>5</v>
+      </c>
+      <c r="P328">
+        <v>140000</v>
+      </c>
+      <c r="Q328">
+        <v>0</v>
+      </c>
+      <c r="R328">
+        <v>0</v>
+      </c>
+      <c r="S328">
+        <v>2</v>
+      </c>
+      <c r="T328">
+        <v>3</v>
+      </c>
+      <c r="U328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>13603</v>
+      </c>
+      <c r="B329" t="s">
+        <v>897</v>
+      </c>
+      <c r="C329">
+        <v>3676</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>69</v>
+      </c>
+      <c r="G329" t="s">
+        <v>503</v>
+      </c>
+      <c r="H329" t="s">
+        <v>35</v>
+      </c>
+      <c r="I329">
+        <v>11</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329" t="s">
+        <v>778</v>
+      </c>
+      <c r="L329">
+        <v>5948837</v>
+      </c>
+      <c r="M329">
+        <v>2</v>
+      </c>
+      <c r="N329" t="s">
+        <v>898</v>
+      </c>
+      <c r="O329">
+        <v>5</v>
+      </c>
+      <c r="P329">
+        <v>200000</v>
+      </c>
+      <c r="Q329">
+        <v>12</v>
+      </c>
+      <c r="R329">
+        <v>0</v>
+      </c>
+      <c r="S329" t="s">
+        <v>294</v>
+      </c>
+      <c r="T329">
+        <v>3</v>
+      </c>
+      <c r="U329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>13647</v>
+      </c>
+      <c r="B330" t="s">
+        <v>899</v>
+      </c>
+      <c r="C330">
+        <v>6310</v>
+      </c>
+      <c r="D330">
+        <v>61006</v>
+      </c>
+      <c r="E330">
+        <v>1</v>
+      </c>
+      <c r="F330">
+        <v>41</v>
+      </c>
+      <c r="G330" t="s">
+        <v>503</v>
+      </c>
+      <c r="H330" t="s">
+        <v>35</v>
+      </c>
+      <c r="I330">
+        <v>71</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330" t="s">
+        <v>900</v>
+      </c>
+      <c r="L330">
+        <v>5949020</v>
+      </c>
+      <c r="M330">
+        <v>1</v>
+      </c>
+      <c r="N330" t="s">
+        <v>622</v>
+      </c>
+      <c r="O330">
+        <v>4</v>
+      </c>
+      <c r="P330">
+        <v>100000</v>
+      </c>
+      <c r="Q330">
+        <v>24</v>
+      </c>
+      <c r="R330">
+        <v>24000</v>
+      </c>
+      <c r="S330" t="s">
+        <v>93</v>
+      </c>
+      <c r="T330">
+        <v>2</v>
+      </c>
+      <c r="U330">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="331" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>13721</v>
+      </c>
+      <c r="B331" t="s">
+        <v>901</v>
+      </c>
+      <c r="C331">
+        <v>6408</v>
+      </c>
+      <c r="D331">
+        <v>60608</v>
+      </c>
+      <c r="E331">
+        <v>1</v>
+      </c>
+      <c r="F331">
+        <v>50</v>
+      </c>
+      <c r="G331" t="s">
+        <v>503</v>
+      </c>
+      <c r="H331" t="s">
+        <v>35</v>
+      </c>
+      <c r="I331">
+        <v>71</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331" t="s">
+        <v>811</v>
+      </c>
+      <c r="L331">
+        <v>5949340</v>
+      </c>
+      <c r="M331">
+        <v>1</v>
+      </c>
+      <c r="N331" t="s">
+        <v>902</v>
+      </c>
+      <c r="O331">
+        <v>4</v>
+      </c>
+      <c r="P331">
+        <v>100000</v>
+      </c>
+      <c r="Q331">
+        <v>24</v>
+      </c>
+      <c r="R331">
+        <v>24000</v>
+      </c>
+      <c r="S331" t="s">
+        <v>809</v>
+      </c>
+      <c r="T331">
+        <v>3</v>
+      </c>
+      <c r="U331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>13743</v>
+      </c>
+      <c r="B332" t="s">
+        <v>903</v>
+      </c>
+      <c r="C332">
+        <v>3542</v>
+      </c>
+      <c r="D332">
+        <v>30802</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>44</v>
+      </c>
+      <c r="G332" t="s">
+        <v>503</v>
+      </c>
+      <c r="H332" t="s">
+        <v>35</v>
+      </c>
+      <c r="I332">
+        <v>56</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332" t="s">
+        <v>904</v>
+      </c>
+      <c r="L332">
+        <v>5949430</v>
+      </c>
+      <c r="M332">
+        <v>3</v>
+      </c>
+      <c r="O332">
+        <v>4</v>
+      </c>
+      <c r="P332">
+        <v>800000</v>
+      </c>
+      <c r="Q332">
+        <v>0</v>
+      </c>
+      <c r="R332">
+        <v>0</v>
+      </c>
+      <c r="S332">
+        <v>0</v>
+      </c>
+      <c r="T332">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>13779</v>
+      </c>
+      <c r="B333" t="s">
+        <v>905</v>
+      </c>
+      <c r="C333">
+        <v>6316</v>
+      </c>
+      <c r="D333">
+        <v>61006</v>
+      </c>
+      <c r="E333">
+        <v>4</v>
+      </c>
+      <c r="F333">
+        <v>46</v>
+      </c>
+      <c r="G333" t="s">
+        <v>503</v>
+      </c>
+      <c r="H333" t="s">
+        <v>35</v>
+      </c>
+      <c r="I333">
+        <v>71</v>
+      </c>
+      <c r="J333">
+        <v>1</v>
+      </c>
+      <c r="K333" t="s">
+        <v>255</v>
+      </c>
+      <c r="L333">
+        <v>5949559</v>
+      </c>
+      <c r="M333">
+        <v>1</v>
+      </c>
+      <c r="N333" t="s">
+        <v>843</v>
+      </c>
+      <c r="O333">
+        <v>4</v>
+      </c>
+      <c r="P333">
+        <v>200000</v>
+      </c>
+      <c r="Q333">
+        <v>24</v>
+      </c>
+      <c r="R333">
+        <v>48000</v>
+      </c>
+      <c r="S333" t="s">
+        <v>93</v>
+      </c>
+      <c r="T333">
+        <v>2</v>
+      </c>
+      <c r="U333">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="334" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>13979</v>
+      </c>
+      <c r="B334" t="s">
+        <v>906</v>
+      </c>
+      <c r="C334">
+        <v>5611</v>
+      </c>
+      <c r="E334">
+        <v>5</v>
+      </c>
+      <c r="F334">
+        <v>47</v>
+      </c>
+      <c r="G334" t="s">
+        <v>503</v>
+      </c>
+      <c r="H334" t="s">
+        <v>35</v>
+      </c>
+      <c r="I334">
+        <v>53</v>
+      </c>
+      <c r="J334">
+        <v>1</v>
+      </c>
+      <c r="K334" t="s">
+        <v>399</v>
+      </c>
+      <c r="L334">
+        <v>5950405</v>
+      </c>
+      <c r="M334">
+        <v>1</v>
+      </c>
+      <c r="N334" t="s">
+        <v>907</v>
+      </c>
+      <c r="O334">
+        <v>4</v>
+      </c>
+      <c r="P334">
+        <v>100000</v>
+      </c>
+      <c r="Q334">
+        <v>12</v>
+      </c>
+      <c r="R334">
+        <v>12000</v>
+      </c>
+      <c r="S334">
+        <v>2</v>
+      </c>
+      <c r="T334">
+        <v>3</v>
+      </c>
+      <c r="U334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>14006</v>
+      </c>
+      <c r="B335" t="s">
+        <v>908</v>
+      </c>
+      <c r="C335">
+        <v>3646</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>53</v>
+      </c>
+      <c r="G335" t="s">
+        <v>503</v>
+      </c>
+      <c r="H335" t="s">
+        <v>35</v>
+      </c>
+      <c r="I335">
         <v>58</v>
       </c>
-      <c r="J314">
-        <v>2</v>
+      <c r="J335">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>14027</v>
+      </c>
+      <c r="B336" t="s">
+        <v>909</v>
+      </c>
+      <c r="C336">
+        <v>5106</v>
+      </c>
+      <c r="D336">
+        <v>50903</v>
+      </c>
+      <c r="E336">
+        <v>7</v>
+      </c>
+      <c r="F336">
+        <v>64</v>
+      </c>
+      <c r="G336" t="s">
+        <v>503</v>
+      </c>
+      <c r="H336" t="s">
+        <v>35</v>
+      </c>
+      <c r="I336">
+        <v>51</v>
+      </c>
+      <c r="J336">
+        <v>1</v>
+      </c>
+      <c r="K336" t="s">
+        <v>910</v>
+      </c>
+      <c r="L336">
+        <v>5950614</v>
+      </c>
+      <c r="M336">
+        <v>1</v>
+      </c>
+      <c r="N336" t="s">
+        <v>911</v>
+      </c>
+      <c r="O336">
+        <v>2</v>
+      </c>
+      <c r="P336">
+        <v>150000</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>161</v>
+      </c>
+      <c r="R336" t="s">
+        <v>161</v>
+      </c>
+      <c r="S336" t="s">
+        <v>912</v>
+      </c>
+      <c r="T336">
+        <v>3</v>
+      </c>
+      <c r="U336" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="337" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>14034</v>
+      </c>
+      <c r="B337" t="s">
+        <v>913</v>
+      </c>
+      <c r="C337">
+        <v>4207</v>
+      </c>
+      <c r="D337">
+        <v>40806</v>
+      </c>
+      <c r="E337">
+        <v>14</v>
+      </c>
+      <c r="F337">
+        <v>37</v>
+      </c>
+      <c r="G337" t="s">
+        <v>503</v>
+      </c>
+      <c r="H337" t="s">
+        <v>35</v>
+      </c>
+      <c r="I337">
+        <v>26</v>
+      </c>
+      <c r="J337">
+        <v>1</v>
+      </c>
+      <c r="K337" t="s">
+        <v>914</v>
+      </c>
+      <c r="L337">
+        <v>5950665</v>
+      </c>
+      <c r="M337">
+        <v>1</v>
+      </c>
+      <c r="N337" t="s">
+        <v>915</v>
+      </c>
+      <c r="O337">
+        <v>5</v>
+      </c>
+      <c r="P337">
+        <v>100000</v>
+      </c>
+      <c r="Q337">
+        <v>0</v>
+      </c>
+      <c r="R337">
+        <v>0</v>
+      </c>
+      <c r="S337" t="s">
+        <v>744</v>
+      </c>
+      <c r="T337">
+        <v>3</v>
+      </c>
+      <c r="U337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>14107</v>
+      </c>
+      <c r="B338" t="s">
+        <v>916</v>
+      </c>
+      <c r="C338">
+        <v>5111</v>
+      </c>
+      <c r="D338">
+        <v>51108</v>
+      </c>
+      <c r="E338">
+        <v>1</v>
+      </c>
+      <c r="F338">
+        <v>36</v>
+      </c>
+      <c r="G338" t="s">
+        <v>503</v>
+      </c>
+      <c r="H338" t="s">
+        <v>35</v>
+      </c>
+      <c r="I338">
+        <v>41</v>
+      </c>
+      <c r="J338">
+        <v>1</v>
+      </c>
+      <c r="K338" t="s">
+        <v>917</v>
+      </c>
+      <c r="L338">
+        <v>5951063</v>
+      </c>
+      <c r="M338">
+        <v>1</v>
+      </c>
+      <c r="N338" t="s">
+        <v>918</v>
+      </c>
+      <c r="O338">
+        <v>5</v>
+      </c>
+      <c r="P338">
+        <v>200000</v>
+      </c>
+      <c r="Q338">
+        <v>0</v>
+      </c>
+      <c r="R338">
+        <v>0</v>
+      </c>
+      <c r="S338" t="s">
+        <v>196</v>
+      </c>
+      <c r="T338">
+        <v>2</v>
+      </c>
+      <c r="U338">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="339" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>14294</v>
+      </c>
+      <c r="B339" t="s">
+        <v>919</v>
+      </c>
+      <c r="C339">
+        <v>6103</v>
+      </c>
+      <c r="D339">
+        <v>60602</v>
+      </c>
+      <c r="E339">
+        <v>1</v>
+      </c>
+      <c r="F339">
+        <v>43</v>
+      </c>
+      <c r="G339" t="s">
+        <v>503</v>
+      </c>
+      <c r="H339" t="s">
+        <v>35</v>
+      </c>
+      <c r="I339">
+        <v>61</v>
+      </c>
+      <c r="J339">
+        <v>1</v>
+      </c>
+      <c r="K339" t="s">
+        <v>920</v>
+      </c>
+      <c r="L339">
+        <v>5951910</v>
+      </c>
+      <c r="M339">
+        <v>2</v>
+      </c>
+      <c r="N339" t="s">
+        <v>921</v>
+      </c>
+      <c r="O339">
+        <v>5</v>
+      </c>
+      <c r="P339">
+        <v>210000</v>
+      </c>
+      <c r="Q339">
+        <v>0</v>
+      </c>
+      <c r="R339">
+        <v>0</v>
+      </c>
+      <c r="S339">
+        <v>0</v>
+      </c>
+      <c r="T339">
+        <v>3</v>
+      </c>
+      <c r="U339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>14294</v>
+      </c>
+      <c r="B340" t="s">
+        <v>919</v>
+      </c>
+      <c r="C340">
+        <v>6103</v>
+      </c>
+      <c r="D340">
+        <v>60602</v>
+      </c>
+      <c r="E340">
+        <v>1</v>
+      </c>
+      <c r="F340">
+        <v>43</v>
+      </c>
+      <c r="G340" t="s">
+        <v>503</v>
+      </c>
+      <c r="H340" t="s">
+        <v>35</v>
+      </c>
+      <c r="I340">
+        <v>61</v>
+      </c>
+      <c r="J340">
+        <v>1</v>
+      </c>
+      <c r="K340" t="s">
+        <v>99</v>
+      </c>
+      <c r="L340">
+        <v>5951910</v>
+      </c>
+      <c r="M340">
+        <v>2</v>
+      </c>
+      <c r="N340" t="s">
+        <v>922</v>
+      </c>
+      <c r="O340">
+        <v>5</v>
+      </c>
+      <c r="P340">
+        <v>50000</v>
+      </c>
+      <c r="Q340">
+        <v>24</v>
+      </c>
+      <c r="R340">
+        <v>0</v>
+      </c>
+      <c r="S340">
+        <v>1</v>
+      </c>
+      <c r="T340">
+        <v>3</v>
+      </c>
+      <c r="U340">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
